--- a/Simulados Faculdade.xlsx
+++ b/Simulados Faculdade.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="544">
   <si>
     <t>Matéria</t>
   </si>
@@ -606,13 +606,1368 @@
   <si>
     <t xml:space="preserve">Fazer um consenso entre os três Evangelhos sinóticos.
 </t>
+  </si>
+  <si>
+    <t>Como filho amado/único, Jesus encarna o verdadeiro Israel, na condição daquele que irá sofrer pelo povo, tal como um cordeiro pascal. Essa condição é indicada pela comparação de Jesus com o seguinte personagem da história de Israel:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Abraão</t>
+  </si>
+  <si>
+    <t>Isaque</t>
+  </si>
+  <si>
+    <t>Esaú</t>
+  </si>
+  <si>
+    <t>Ismael.</t>
+  </si>
+  <si>
+    <t>As marcas textuais do evangelho de Lucas revelam que as comunidades para as quais foi escrito eram predominantemente...
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Judaicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gentílicas.
+</t>
+  </si>
+  <si>
+    <t>Cristãs antigas.</t>
+  </si>
+  <si>
+    <t>Israelitas.</t>
+  </si>
+  <si>
+    <t>Qual é a mensagem Central do Evangelho de Marcos?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesus, o sucessor de João.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesus é o Messias, Filho de Deus.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesus, o Libertador.
+</t>
+  </si>
+  <si>
+    <t>Jesus, o Filho do homem.</t>
+  </si>
+  <si>
+    <t>A palavra parábola vem do grego parabole que significa, literalmente:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Comparação.</t>
+  </si>
+  <si>
+    <t>Lançar ao lado.</t>
+  </si>
+  <si>
+    <t>Enigma.</t>
+  </si>
+  <si>
+    <t>Provérbios.</t>
+  </si>
+  <si>
+    <t>Blasfemar contra o Espírito Santo que acompanhou o ministério de Jesus equivale a:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejeitar a mensagem do evangelho.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um ato contra o próprio reino satânico.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceitar entrar no reino de Deus.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ser condenado diretamente e sem perdão ao inferno.
+</t>
+  </si>
+  <si>
+    <t>Qual evangelho sinótico é considerado o mais antigo?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Mateus.</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>Marcos.</t>
+  </si>
+  <si>
+    <t>João</t>
+  </si>
+  <si>
+    <t>Na linguagem mais comum em manuais de exegese e hermenêutica bíblica os gêneros textuais são nomeados de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formas literárias.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos de expressão.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criações estilísticas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano de conteúdo.
+</t>
+  </si>
+  <si>
+    <t>Em Apocalipse 21:1-15, João expõe a visão do novo mundo baseado nas:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tradições veterotestamentárias.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na saciedade que põe fim a toda fome.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bem-aventuranças de Jesus.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vinda do reino.
+</t>
+  </si>
+  <si>
+    <t>Sinóticos deriva de duas palavras gregas que, literalmente, significam:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Harmonia</t>
+  </si>
+  <si>
+    <t>Biografia</t>
+  </si>
+  <si>
+    <t>Unidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visão comum.
+</t>
+  </si>
+  <si>
+    <t>Por que os escribas de Jerusalém acusaram Jesus de ser possesso por Belzebu?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque ele fazia milagres.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque comparavam Jesus a um ladrão.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque ele expulsava os demônios.
+</t>
+  </si>
+  <si>
+    <t>Porque achavam que ele praticava exorcismo.</t>
+  </si>
+  <si>
+    <t>A relação mais amistosa de Jesus com a tradição bíblica israelita é acentuada no Evangelho de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Mateus</t>
+  </si>
+  <si>
+    <t>Marcos</t>
+  </si>
+  <si>
+    <t>Qual é a primeira característica da identidade messiânica de Jesus?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foi ao deserto para ser tentado.
+</t>
+  </si>
+  <si>
+    <t>A escolha dos discípulos.</t>
+  </si>
+  <si>
+    <t>Sua fidelidade filial.</t>
+  </si>
+  <si>
+    <t>O batismo de Jesus.</t>
+  </si>
+  <si>
+    <t>Qual advérbio, típico do evangelho de Marcos, ressalta a dinamicidade dos eventos?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Perfeitamente</t>
+  </si>
+  <si>
+    <t>Certamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imediatamente.
+</t>
+  </si>
+  <si>
+    <t>Infelizmente.</t>
+  </si>
+  <si>
+    <t>Jesus caminha da Galileia ao Jordão, deste ao deserto, então, de volta à Galileia. O percurso geográfico de Jesus é o percurso marcado pela:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Solidariedade</t>
+  </si>
+  <si>
+    <t>Santidade</t>
+  </si>
+  <si>
+    <t>Impureza.</t>
+  </si>
+  <si>
+    <t>Desprezo</t>
+  </si>
+  <si>
+    <t>Qual é o primeiro ato solidário de Jesus com pessoas impuras e pecadoras que concretiza sua solidariedade com eles?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elege o novo Israel.
+</t>
+  </si>
+  <si>
+    <t>Derrota os inimigos do Pai.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ora e busca forças ao pai.
+</t>
+  </si>
+  <si>
+    <t>Batismo de Jesus.</t>
+  </si>
+  <si>
+    <t>Qual é o primeiro ato público relatado do ministério de Jesus?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A perícope do chamado.</t>
+  </si>
+  <si>
+    <t>Tentação de Jesus.</t>
+  </si>
+  <si>
+    <t>O batismo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pregação do reino de Deus.
+</t>
+  </si>
+  <si>
+    <t>A mensagem central do Evangelho de Lucas: Jesus é o Messias, Filho do Homem e Filho de Deus, é similar aos seguintes evangelhos:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Mateus e João.</t>
+  </si>
+  <si>
+    <t>Marcos e João.</t>
+  </si>
+  <si>
+    <t>Tomé e Mateus.</t>
+  </si>
+  <si>
+    <t>Marcos e Mateus.</t>
+  </si>
+  <si>
+    <t>Para quem era essencial a exigência da lei?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>Fariseus</t>
+  </si>
+  <si>
+    <t>Palestinos</t>
+  </si>
+  <si>
+    <t>Deus</t>
+  </si>
+  <si>
+    <t>O evangelho de Marcos provavelmente foi escrito nos primeiros anos da década de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Qual é o maior dos evangelhos?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Lucas.</t>
+  </si>
+  <si>
+    <t>João.</t>
+  </si>
+  <si>
+    <t>A função que coloca em destaque o código linguístico é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Metalinguagem.</t>
+  </si>
+  <si>
+    <t>Conativa.</t>
+  </si>
+  <si>
+    <t>Referencial</t>
+  </si>
+  <si>
+    <t>Fática</t>
+  </si>
+  <si>
+    <t>É um exemplo de oração coordena Sindética Aditiva, a seguinte oração:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Não só pulei como também corri.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nem pulei e nem dancei durante a festa.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprei um quilo de banana e fui trabalhar.
+</t>
+  </si>
+  <si>
+    <t>Todas as alternativas estão corretas.</t>
+  </si>
+  <si>
+    <t>Na frase: “ No coração da floresta existe um grande amor escondido”. É certo afirmar que é um exemplo de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metáfora.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metonímia.
+</t>
+  </si>
+  <si>
+    <t>Sinestesia</t>
+  </si>
+  <si>
+    <t>Não pode ser considerada uma comparação a seguinte frase:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O rio é a lágrima de um oceano.</t>
+  </si>
+  <si>
+    <t>O rio é tal qual a lágrima de um oceano.</t>
+  </si>
+  <si>
+    <t>O rio é como a lágrima de um oceano.</t>
+  </si>
+  <si>
+    <t>O rio é semelhante a lágrima de um oceano.</t>
+  </si>
+  <si>
+    <t>Marque a alternativa correta:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O adjetivo concorda em gênero com o substantivo a que se refere.</t>
+  </si>
+  <si>
+    <t>O adjetivo só concorda com o número a que se refere o substantivo.</t>
+  </si>
+  <si>
+    <t>O adjetivo só tem uma forma.</t>
+  </si>
+  <si>
+    <t>O adjetivo não sofre flexão de grau.</t>
+  </si>
+  <si>
+    <t>Artigo é palavra que antepomos ao substantivo para:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Determiná-lo, indicar seu gênero e número.</t>
+  </si>
+  <si>
+    <t>Indicar o tempo verbal.</t>
+  </si>
+  <si>
+    <t>Classificar os adjetivos.</t>
+  </si>
+  <si>
+    <t>Regulamentar o uso dos pronomes.</t>
+  </si>
+  <si>
+    <t>O verbo pode aparecer na voz ativa e passiva. Marque a frase em que ele aparece na voz passiva:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O carro foi roubado.</t>
+  </si>
+  <si>
+    <t>A obra foi feita por ela.</t>
+  </si>
+  <si>
+    <t>A menina cortou-se.</t>
+  </si>
+  <si>
+    <t>Esta função tem por objetivo colocar o receptor numa posição de destaque. É uma afirmação que cabe somente à função:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Poética.</t>
+  </si>
+  <si>
+    <t>Metalinguística.</t>
+  </si>
+  <si>
+    <t>Conativa</t>
+  </si>
+  <si>
+    <t>Assinale a frase em que há erro de regência verbal:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A nota precisa de referência.</t>
+  </si>
+  <si>
+    <t>O dono realizou o levantamento das necessidades da loja.</t>
+  </si>
+  <si>
+    <t>Os médicos assistiram o simpósio e acharam-no muito interessante.</t>
+  </si>
+  <si>
+    <t>É preciso que todos cumpram às diretrizes da escola.</t>
+  </si>
+  <si>
+    <t>No enunciado “Trata-se de uma notícia muito boa!” O artigo é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Definido plural.</t>
+  </si>
+  <si>
+    <t>Indefinido singular.</t>
+  </si>
+  <si>
+    <t>Definido singular.</t>
+  </si>
+  <si>
+    <t>Indefinido plural.</t>
+  </si>
+  <si>
+    <t>Filosofia da Religião</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas não descreve adequadamente a noção de sagrado?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrado diz respeito a algo espiritual e não se refere às coisas materiais e mundanas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrado é uma qualidade inerente à pessoa ou objeto sacralizado, o que significa que independe das pessoas ou situações.
+</t>
+  </si>
+  <si>
+    <t>O sagrado jamais se confunde com o profano, e isso significa que no mundo há coisas ou pessoas que são desde sempre sagradas e coisas ou pessoas que são desde sempre profanas.</t>
+  </si>
+  <si>
+    <t>Nenhuma das afirmativas descreve bem a noção de sagrado.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas expressa uma perspectiva metafísica da Teologia?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A Teologia é a guardião da são doutrina, o que significa que suas descrições da realidade e da pessoa de Deus precisam se ancorar na revelação divina para que tenha validade universal.</t>
+  </si>
+  <si>
+    <t>Deus é uma realidade que independe do modo como o compreendemos, e qualquer conhecimento que se construa sobre ele deve ser buscado a partir dessa realidade autônoma e não nas descrições humanas sobre ele.</t>
+  </si>
+  <si>
+    <t>Pode-se dizer que a Teologia é o estudo da pessoa de Deus e de suas relações para com os humanos, e isso significa que deve ser compreendida numa perspectiva universal, independente dos contextos interpretativos.</t>
+  </si>
+  <si>
+    <t>Todas as afirmativas expressam uma perspectiva metafísica da Teologia.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas expressa melhor o efeito que o sagrado nos provoca?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O sagrado sempre nos causa temor, pois é isso em relação ao qual mantemos certa distância.</t>
+  </si>
+  <si>
+    <t>O sagrado sempre suscita intimidade, pois é isso em relação ao qual nos sentimos atraídos.</t>
+  </si>
+  <si>
+    <t>O sagrado é ambíguo, porquanto ao mesmo tempo em que dele mantemos certa distância pelo temor que nos provoca, por ele também nos sentimos atraídos e somos seduzidos a certa intimidade.</t>
+  </si>
+  <si>
+    <t>Nenhuma das afirmativas acima descrevem o efeito que o sagrado nos provoca.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas caracteriza adequadamente o sagrado?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O sagrado não é uma qualidade inerente à pessoa ou objeto sacralizado, o que significa que depende do sujeito que o venera.</t>
+  </si>
+  <si>
+    <t>Todas as afirmativas caracterizam adequadamente o sagrado.</t>
+  </si>
+  <si>
+    <t>O sagrado pode se confundir com o profano, e isso significa que no mundo não há coisas ou pessoas que são desde sempre sagradas e coisas ou pessoas que são desde sempre profanas.</t>
+  </si>
+  <si>
+    <t>O sagrado é qualitativamente diferente do profano, e o que é sagrado para uns é profano para outros.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas descreve melhor a noção de sagrado?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O sagrado diz respeito a algo espiritual e não se refere às coisas materiais e mundanas.</t>
+  </si>
+  <si>
+    <t>O sagrado é uma qualidade inerente à pessoa ou objeto sacralizado, o que significa que independe das pessoas ou situações.</t>
+  </si>
+  <si>
+    <t>O sagrado é qualitativamente diferente do profano, mas não é uma qualidade inerente à pessoa ou objeto sacralizado, o que significa que depende do sujeito que o venera — o que é sagrado para uns é profano para outros.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes alternativas NÃO caracteriza o papel da teologia numa sociedade democrática?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A teologia deve contribuir positivamente para a participação efetiva e consciente de pessoas religiosas na democracia.</t>
+  </si>
+  <si>
+    <t>É importante que a teologia se apresente de forma plural, mas de modo que as suas diferentes vozes e perspectivas não sejam vistas como concorrentes, mas como parceiras de diálogo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A teologia precisa se apresentar como guardiã da democracia, defendendo-a dos fundamentalismos religiosos dos mais diversos tipos que ameaçam as sociedades contemporâneas.
+</t>
+  </si>
+  <si>
+    <t>A teologia deve se apresentar em sua unidade fundamental, de maneira que sua pluralidade de vozes ceda lugar a uma só voz (unidade), a fim de que possa afetar positivamente a sociedade democrática.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas expressa uma perspectiva pós-metafísica da Teologia?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Pode-se dizer que a Teologia é o estudo das descrições humanas sobre Deus e suas relações para com os humanos, e isso significa que deve ser compreendida numa perspectiva local, a partir dos contextos interpretativos.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas possibilita inferir que o autor de Eclesiastes dialoga criticamente com as filosofias (sabedorias) do mundo grego e também do mundo oriental mesopotâmico?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Os mesmos conteúdos tratados no livro de Eclesiastes também são objetos de reflexão filosófica pelo mundo grego e mesopotâmico nos tempos iniciais da dominação de Judá pelos helenistas.</t>
+  </si>
+  <si>
+    <t>Todas as alternativas são verdadeiras.</t>
+  </si>
+  <si>
+    <t>O conceito de nulidade reúne o discurso judaico do discurso filosófico pós-metafísico na medida em que propõe o fim do fundamentalismo, tanto religioso quanto filosófico.</t>
+  </si>
+  <si>
+    <t>Há uma lógica, filosófica ou teológica, que atravessa a lógica poética, a desloca, se sustenta nela, mas não corresponde ao seu projeto. Uma lógica eivada de contrapontos, tensões e contradições, que obrigam leitores de Eclesiastes a exercícios intelectuais desafiadores.</t>
+  </si>
+  <si>
+    <t>Como Rorty vê a tarefa da Filosofia da religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Discute a relação da filosofia com a religião sob a ótica da tradução. Para ele, nesse esforço dialogal, a prioridade deveria ser o delineamento dos espaços próprios das diferentes linguagens da religião e da ciência.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Filosofia da Religião deve, com o auxílio das ciências, investigar em que medida as religiões se alinham com a verdade, afinal, uma de suas tarefas consiste em se buscar essa verdade.
+</t>
+  </si>
+  <si>
+    <t>A Filosofia da Religião pressupõe que o valor das ideias resida em sua utilidade ou conveniência, e não em sua fidelidade a um ideal transcendente.</t>
+  </si>
+  <si>
+    <t>Nenhuma das alternativas disponíveis.</t>
+  </si>
+  <si>
+    <t>A abordagem filosófica sistemática da religião é um produto do pensamento moderno. Quanto a isso, qual das afirmativas abaixo não é verdadeira?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A antiguidade clássica não considerou o tema como um aspecto particular de investigação, numa perspectiva sistematizada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A antiguidade clássica, bem como o pensamento cristão medieval, também elaboraram reflexões concernentes ao tema da religião.
+</t>
+  </si>
+  <si>
+    <t>A antiguidade clássica, bem como o pensamento cristão medieval, não elaboraram reflexões concernentes ao tema da religião.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abordagem sistemática, torna-se importante e necessária em virtude do conflito instaurado entre o mundo moderno, cada vez mais interessado no processo de libertação do homem a partir da ótica iluminista, e as doutrinas e instituições religiosas derivadas da tradição judaico-cristãs.
+</t>
+  </si>
+  <si>
+    <t>Qual das seguintes alternativas corresponde a uma tarefa da teologia em tom pós-metafísico?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A partir do diálogo público, defender a sociedade — especialmente as vítimas do capitalismo voraz — da dominação sistêmica.</t>
+  </si>
+  <si>
+    <t>A partir do diálogo religioso intramuros, defender os interesses do cristianismo da dominação antirreligiosa.</t>
+  </si>
+  <si>
+    <t>Defender a sociedade dos interesses de grupos defensores do ateísmo ou de religiões não-cristãs que interferem nas decisões do Estado a favor do cristianismo.</t>
+  </si>
+  <si>
+    <t>Defender a fé dos ataques à fé cristã, normalmente realizados a partir de conceitos derivados da ciência ou  da filosofia.</t>
+  </si>
+  <si>
+    <t>Qual das afirmativas Não demonstra uma tarefa da filosofia na contemporaneidade?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Mediar hermeneuticamente entre diferentes linguagens e não recair na posição de substituta da religião.</t>
+  </si>
+  <si>
+    <t>Desenvolver a dimensão epistemológica do saber.</t>
+  </si>
+  <si>
+    <t>Apoiar o aperfeiçoamento da democracia.</t>
+  </si>
+  <si>
+    <t>Desenvolver a dimensão terapêutica da racionalidade.</t>
+  </si>
+  <si>
+    <t>Qual o papel da teologia em tom pós-metafísico, em sua vertente libertadora?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Defender os direitos das pessoas mais empobrecidas e vitimadas pela globalização geográfica e simbólica da ideologia do livre-mercado e sua profetiza, a tecnologia.</t>
+  </si>
+  <si>
+    <t>Lutar por uma compreensão teológica mais fundamentada da realidade da libertação espiritual proposta pelo cristianismo ao longo de sua história.</t>
+  </si>
+  <si>
+    <t>Auxiliar a prática pastoral, na medida em que esta se baseia no fato de que as pessoas estão cada vez mais como “ovelhas sem pastor” e, portanto, necessitam de libertação.</t>
+  </si>
+  <si>
+    <t>Qual o período da história em que a filosofia assumiu o papel normativo, outrora pertencente à teologia e às vertentes clássicas da filosofia?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Primeira parte da Modernidade.</t>
+  </si>
+  <si>
+    <t>Durante toda a Modernidade.</t>
+  </si>
+  <si>
+    <t>Na Pós-Modernidade.</t>
+  </si>
+  <si>
+    <t>Durante a Idade Média</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas NÃO expressa um dos três grandes momentos de conflitividade entre filosofia e religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Quando filósofos tiveram de disputar com sacerdotes e líderes religiosos o direito de dizer a verdadee o prestígio social proveniente desse direito.</t>
+  </si>
+  <si>
+    <t>Quando o Cristianismo se tornou a religião oficial do Império Romano e a Igreja assumiu o controle da produção do saber legítimo, resultando numa predominância da teologia sobre a filosofia.</t>
+  </si>
+  <si>
+    <t>A partir da Modernidade, em que os interesses teológicos na busca pela verdade predominaram sobre os interesses filosóficos.</t>
+  </si>
+  <si>
+    <t>A partir da Modernidade até nossos dias, com os movimentos de secularização da sociedade, e a paulatina ascensão da ciência sobre a filosofia e a teologia.</t>
+  </si>
+  <si>
+    <t>Como Habermas vê a tarefa da filosofia da religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Para ele, o valor das ideias reside em sua utilidade, ou conveniência, e não na sua fidelidade a um ideal transcendente.</t>
+  </si>
+  <si>
+    <t>A filosofia, em tom pós-metafísico, não pode mais desempenhar o papel de discurso fundacional, mas deve assumir o lugar de mediadora, intérprete entre diferentes formas do saber humano. A filosofia da religião deveria se esforçar, primeiro, para, em diálogo com as pessoas e comunidades de fé, traduzir conceitos religiosos em linguagem não-religiosa, aberta.</t>
+  </si>
+  <si>
+    <t>A filosofia da religião deve, com o auxílio das ciências, investigar em que medida as religiões se alinham com a verdade, afinal, uma de suas tarefas consiste em se buscar essa verdade.</t>
+  </si>
+  <si>
+    <t>Resgatar a boa tradição.</t>
+  </si>
+  <si>
+    <t>Qual dos seguintes paradoxos aproxima o livro de Eclesiastes da reflexão filosófica contemporânea?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Se queremos compreender o “céu”, precisamos compreender a “terra”.</t>
+  </si>
+  <si>
+    <t>Se queremos compreender a vida, precisamos nos encantar com a morte.</t>
+  </si>
+  <si>
+    <t>Se queremos compreender a alma, precisamos aceitar o corpo.</t>
+  </si>
+  <si>
+    <t>Se queremos compreender a libertação, precisamos compreender a dominação.</t>
+  </si>
+  <si>
+    <t>A antiguidade clássica, bem como o pensamento cristão medieval, também elaboraram reflexões concernentes ao tema da religião.</t>
+  </si>
+  <si>
+    <t>A antiguidade clássica também considerou o tema como um aspecto particular de investigação, numa perspectiva sistematizada.</t>
+  </si>
+  <si>
+    <t>Abordagem sistemática, torna-se importante e necessária em virtude do conflito instaurado entre o mundo moderno, cada vez mais interessado no processo de libertação do homem a partir da ótica iluminista, e as doutrinas e instituições religiosas derivadas da tradição judaico-cristãs.</t>
+  </si>
+  <si>
+    <t>Qual a diferença entre a abordagem filosófica da religião e a abordagem da Psicologia da Religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), o enfoque da Psicologia da Religião é mais descritivo, afinal, parte do pressuposto de que interpretar um fato religioso implica em se conhecê-lo.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Psicologia da Religião a religião é uma forma fundamental de coesão social, ou seja, o fenômeno religioso mostra a realidade social e é essencialmente comunitário.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Psicologia da Religião os fatos religiosos espelham a psique humana, o que significa dizer que sem o ser humano, não há experiência religiosa, afinal, o sentimento religioso é uma elaboração do eros básico do ser humano.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), a Psicologia da Religião estuda a intencionalidade dos fatos religiosos, os testemunhos do ser humano religioso e o que para ele significam tais fatos, o que significa que o interesse está no modo como esse fenômeno se manifesta e como é recebido por aqueles que são adeptos dessas instituições.</t>
+  </si>
+  <si>
+    <t>Qual a diferença entre a abordagem filosófica da religião e a abordagem da Sociologia da Religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), o enfoque da Sociologia da Religião é mais descritivo, afinal, parte do pressuposto de que interpretar um fato religioso implica em se conhecê-lo.
+</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Sociologia da Religião a religião é uma forma fundamental de coesão social, ou seja, o fenômeno religioso mostra a realidade social e é essencialmente comunitário.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Sociologia da Religião os fatos religiosos espelham a psique humana, o que significa dizer que sem o ser humano, não há experiência religiosa, afinal, o sentimento religioso é uma elaboração do eros básico do ser humano.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), a Sociologia da Religião estuda a intencionalidade dos fatos religiosos, os testemunhos do ser humano religioso e o que para ele significam tais fatos, o que significa que o interesse está no modo como esse fenômeno se manifesta e como é recebido por aqueles que são adeptos dessas instituições.</t>
+  </si>
+  <si>
+    <t>“Quando qualquer coisa da criação de Deus é usada de maneira que não possa ser oferecida a Deus como um culto e não possa ser um ato de justiça, o universo foi profanado, por que o universo foi instrumentalizado para qualquer outra coisa que não seja o culto devido ao seu Criador. Então, isso quer dizer que qualquer movimento que descaracterize o propósito da criação de todas as coisas é um movimento profano. E qualquer movimento que leve a criação ao seu propósito, que é prestar ao Criador o culto que lhe é devido, é um movimento sagrado” (Cf. http://bit.ly/2jYSYyQ).
+Considere o trecho de uma fala de Ariovaldo Ramos, acima descrita, e responda: qual das seguintes alternativas não reflete o que está sendo dito?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Todas as coisas devem ser sacralizadas a fim de que prestem testemunho de que Deus é o Criador de tudo.</t>
+  </si>
+  <si>
+    <t>Sagrado e profano são operações do olhar, o que significa que as mesmas coisas podem ser sagradas e profanas, dependendo de como sejam vistas por cada pessoa.</t>
+  </si>
+  <si>
+    <t>O profano é compreendido de maneira negativa, como aquilo que supostamente não é dedicado a Deus ou que sobrevive de forma a descaracterizar o propósito da criação, que é prestar culto ao seu Criador.</t>
+  </si>
+  <si>
+    <t>Nenhuma das alternativas anteriores.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes alternativas NÃO consiste numa sociedade pós-secular?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Uma sociedade na qual o discurso religioso, tanto quanto o discurso secular, tenham legitimidade na “arena pública”.</t>
+  </si>
+  <si>
+    <t>Uma sociedade na qual a consciência pública espelha muito mais um juízo normativo que tem consequências para o contato político entre cidadãos não-crentes e crentes.</t>
+  </si>
+  <si>
+    <t>Uma sociedade na qual não se tenta convencer a sociedade a destruir as crenças e instituições religiosas, nem mesmo impedir pessoas e instituições religiosas de participarem nos debates políticos nacionais.</t>
+  </si>
+  <si>
+    <t>Uma sociedade que legitima o secularismo e rejeita o fundamentalismo, enquanto perspectiva fundacional e antidemocrática.</t>
+  </si>
+  <si>
+    <t>Qual a diferença entre a abordagem filosófica da religião e a abordagem da Fenomenologia da Religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), o enfoque da Fenomenologia  da Religião é mais descritivo, afinal, parte do pressuposto de que interpretar um fato religioso implica em se conhecê-lo.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Fenomenologia  da Religião a religião é uma forma fundamental de coesão social, ou seja, o fenômeno religioso mostra a realidade social e é essencialmente comunitário.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Fenomenologia  da Religião os fatos religiosos espelham a psique humana, o que significa dizer que sem o ser humano, não há experiência religiosa, afinal, o sentimento religioso é uma elaboração do eros básico do ser humano.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), a Fenomenologia  da Religião estuda a intencionalidade dos fatos religiosos, os testemunhos do ser humano religioso e o que para ele significam tais fatos, o que significa que o interesse está no modo como esse fenômeno se manifesta e como é recebido por aqueles que são adeptos dessas instituições.</t>
+  </si>
+  <si>
+    <t>Contribuir para a integração dos saberes em face dos perigos da fragmentação do conhecimento e da cisão entre as diferentes dimensões da razão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defender a fé dos ataques à fé cristã, normalmente realizados a partir de conceitos derivados da ciência ou  da filosofia.
+</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas expressa um dos três grandes momentos de conflitividade entre filosofia e religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Quando cientistas tiveram de disputar com filósofos e líderes religiosos o direito de dizer a verdade e o prestígio social proveniente desse direito.</t>
+  </si>
+  <si>
+    <t>A Idade Média, caracterizada pelos movimentos de secularização da sociedade, e a paulatina ascensão da ciência sobre a filosofia e a teologia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defender a sociedade dos interesses, por vezes míopes, de instituições religiosas que interferem inadequadamente na discussão dos limites da ciência.
+</t>
+  </si>
+  <si>
+    <t>Interpretar os novos movimentos à luz dos clássicos e afirmar seu caráter de mestra e rainha do saber.</t>
+  </si>
+  <si>
+    <t>Em que termos Gianni Vattimo concebe a verdade revelada nas Escrituras?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Como a verdade do dogma, fruto da tradição.</t>
+  </si>
+  <si>
+    <t>Como a verdade da teologia, fruto da reflexão crítica.</t>
+  </si>
+  <si>
+    <t>Como a verdade da ciência, fruto da observação.</t>
+  </si>
+  <si>
+    <t>Como a verdade do amor, da caridade, fruto de um chamado à prática.</t>
+  </si>
+  <si>
+    <t>Por que se pode dizer que o sagrado é ambíguo?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrado é ambíguo, porquanto ao mesmo tempo em que dele mantemos certa distância pelo temor que nos provoca, por ele também nos sentimos atraídos e somos seduzidos a certa intimidade.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrado é ambíguo, porquanto se trata de objetos ou coisas que sempre trazem ambiguidade para aqueles que procuram entendê-lo.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrado é ambíguo porque pode estar no altar tanto do cristão, do budista, do muçulmano ou de qualquer outra religião.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrando, na realidade, não é ambíguo.
+</t>
+  </si>
+  <si>
+    <t>Psicologia Geral</t>
+  </si>
+  <si>
+    <t>A importância de Emil Kraepelin para o estudo das psicopatologias deve-se a que?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>As doenças mentais podem ser definidas a partir de desordens psíquicas em relação ao comportamento convencionado como padrão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Que a esquizofrenia não é uma coisa só, mas sim uma síndrome que supõe uma fragmentação e desorganização do funcionamento psicológico.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foi ele o responsável pela descrição e classificação dos transtornos mentais.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todas as respostas estão corretas.
+</t>
+  </si>
+  <si>
+    <t>Kurt Schneider os indivíduos do tipo “psicopatas fanáticos” são os que mais apresentam conteúdos e elementos religiosos em seu comportamento. Ele os divide em dois grupos que são:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fanáticos revolucionários e individualistas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fanático expansivos e discretos.
+</t>
+  </si>
+  <si>
+    <t>Fanáticos liberais e conservadores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fanáticos cultos e incultos.
+</t>
+  </si>
+  <si>
+    <t>São os precursores da psicologia moderna:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platão e Aristóteles.
+</t>
+  </si>
+  <si>
+    <t>Sócrates e Platão.</t>
+  </si>
+  <si>
+    <t>Aristóteles e Sócrates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma das respostas.
+</t>
+  </si>
+  <si>
+    <t>Psicopatologia pode ser entendida como:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A classificação dos transtornos mentais.
+</t>
+  </si>
+  <si>
+    <t>O estudo aplicado dos sintomas anormais demonstrados na vida do indivíduo.</t>
+  </si>
+  <si>
+    <t>Uma síndrome que aborda só um aspecto da saúde mental.</t>
+  </si>
+  <si>
+    <t>Todas as respostas estão incorretas.</t>
+  </si>
+  <si>
+    <t>Foi desenvolvida por Gerald Kleman e Myrna Weissmann nos anos 70:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Terapia Comportamental.</t>
+  </si>
+  <si>
+    <t>Terapia Cognitiva.</t>
+  </si>
+  <si>
+    <t>Terapia Familiar e de Casal.</t>
+  </si>
+  <si>
+    <t>Terapia interpessoal (TIP).</t>
+  </si>
+  <si>
+    <t>Foi quem criou os testes de inteligência estática, abrindo portas para os testes de QI do mundo moderno:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivan Pavlov.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Watson.
+</t>
+  </si>
+  <si>
+    <t>Alfred Binet.</t>
+  </si>
+  <si>
+    <t>Stanley Hall.</t>
+  </si>
+  <si>
+    <t>A quantos anos aproximadamente a psicologia é entendida como ciência?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130 anos.
+</t>
+  </si>
+  <si>
+    <t>90 anos.</t>
+  </si>
+  <si>
+    <t>100 anos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma das respostas.
+</t>
+  </si>
+  <si>
+    <t>É o conceito mais antigo da Psicologia:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanicista.
+</t>
+  </si>
+  <si>
+    <t>Organicista.</t>
+  </si>
+  <si>
+    <t>Estruturalista</t>
+  </si>
+  <si>
+    <t>Vitalista</t>
+  </si>
+  <si>
+    <t>Considerando o pensamento de Jung sobre o objetivo da religião é certo afirmar quer:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O objetivo maior da religião é  identificar-se com a psique universal.
+</t>
+  </si>
+  <si>
+    <t>O objetivo maior da religião é não submergindo a consciência num mar de esquecimento inconsciente.</t>
+  </si>
+  <si>
+    <t>O objetivo maior da religião é integrar a consciência pessoal, através de recursos supremos.</t>
+  </si>
+  <si>
+    <t>Todas as respostas estão corretas.</t>
+  </si>
+  <si>
+    <t>“Matéria e vida são da mesma essência e a análise dos elementos de um objeto animado ou inanimado nos leva à total explicação das manifestações do objeto.” Está frase deve ser associada a qual conceito:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conceito Mecanicista.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conceito Vitalista.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conceito Organicista.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhum dos Conceitos  Apontados.
+</t>
+  </si>
+  <si>
+    <t>Qual a importância da fala no método Psicanalítico adotado por Freud?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O que Freud observou é que no exercício da fala, os pacientes por vezes demonstravam inibição quanto a imagens e ideias que surgiam.</t>
+  </si>
+  <si>
+    <t>Facilita a indução a sonhos eróticos e de prazer.</t>
+  </si>
+  <si>
+    <t>É importante porque somente por meio da fala o paciente pode ser analisado.</t>
+  </si>
+  <si>
+    <t>Nenhuma das alternativas está correta.</t>
+  </si>
+  <si>
+    <t>Foi quem ampliou o conceito científico que envolvia questões de psiquiatria criminal, neuropatologia, hipnose, psicolopatologia do trabalho e psicose infantil como dementia precosíssima. Está se falando de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Freud.</t>
+  </si>
+  <si>
+    <t>Pinel.</t>
+  </si>
+  <si>
+    <t>De Sanctis.</t>
+  </si>
+  <si>
+    <t>Jung.</t>
+  </si>
+  <si>
+    <t>Os primeiros passos na direção do pensamento sobre o que poderia ser o mundo psicológico é atribuído a:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Sócrates</t>
+  </si>
+  <si>
+    <t>Platão.</t>
+  </si>
+  <si>
+    <t>Aristóteles.</t>
+  </si>
+  <si>
+    <t>Agostinho.</t>
+  </si>
+  <si>
+    <t>Tem seu fundamento nas teorias psicanalíticas da personalidade a seguinte terapia dinâmica:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Psicoterapia de Apoio.</t>
+  </si>
+  <si>
+    <t>Psicoterapia de Grupo.</t>
+  </si>
+  <si>
+    <t>Terapia Interpessoal.</t>
+  </si>
+  <si>
+    <t>Terapia comportamental.</t>
+  </si>
+  <si>
+    <t>Os fundadores da chamada psicologia experimental foram:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Wilhem Wundt , Ernst H.Weber, Gustav T. Fechner.</t>
+  </si>
+  <si>
+    <t>Pinel, Skinner e Ana Freud.</t>
+  </si>
+  <si>
+    <t>Platão, Sócrates e Aristóteles.</t>
+  </si>
+  <si>
+    <t>Nenhuma das respostas.</t>
+  </si>
+  <si>
+    <t>São Tomas de Aquino é influenciado em seu pensamento sobre essência e existência  por:  
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Sócrates.</t>
+  </si>
+  <si>
+    <t>Arquimedes</t>
+  </si>
+  <si>
+    <t>É o local em que se encontram as pulsões de vida e de morte:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>ID.</t>
+  </si>
+  <si>
+    <t>Ego.</t>
+  </si>
+  <si>
+    <t>Pré-consciente.</t>
+  </si>
+  <si>
+    <t>Consciente</t>
+  </si>
+  <si>
+    <t>Psicoterapias de apoio é apenas a que:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Está voltada primordialmente para o tratamento da depressão.</t>
+  </si>
+  <si>
+    <t>Tem como base o aprendizado como forma de entendimento da gênese dos sintomas, a manutenção e eliminação dos mesmos.</t>
+  </si>
+  <si>
+    <t>A intervenção do terapeuta é direta, funcionando como suporte, um ego auxiliar, e seu trabalho é focado na realidade atual do paciente.</t>
+  </si>
+  <si>
+    <t>São os três conceitos primordiais da psicologia:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Mecanicista, Filosofia e Estruturalista.</t>
+  </si>
+  <si>
+    <t>Organicista, Mecanicista e Vitalista.</t>
+  </si>
+  <si>
+    <t>Sensacionalista, Estruturalista, Fundamentalista.</t>
+  </si>
+  <si>
+    <t>“Essa teoria ocupa-se do ser humano como um todo e admite que qualquer evento psicológico é resultante de vários fatores e influenciam na conduta do indivíduo”. Esta frase faz parte do conceito:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Teoria Mecanicista.</t>
+  </si>
+  <si>
+    <t>Teoria Vitalista.</t>
+  </si>
+  <si>
+    <t>Teoria Organicista.</t>
+  </si>
+  <si>
+    <t>Teoria Analítica.</t>
+  </si>
+  <si>
+    <t>História e Cultura Helenística</t>
+  </si>
+  <si>
+    <t>Os gregos consideram a mensagem da cruz como loucura (1 Cor 1,22). De fato, quem poderia culpá-los, pois ninguém antes deles conhecera tão grande desenvolvimento cultural. Eles buscavam a sabedoria que traria sucesso na política, nos tribunais, na filosofia, no comércio, numa vida autárquica e, especialmente, a aprovação ou admiração de seus respectivos pares. A perspectiva de vida baseada nesses valores considera a “mensagem da cruz” uma afronta, pois a sabedoria humana considera loucura tudo o que é contrário a este modelo de vida. A “palavra da cruz” é também desprezada, pois a pessoa que Paulo proclamava havia aceitado um tipo de sofrimento e morte que eram considerados desonra e vergonha. A proclamação da “palavra da cruz” aos que buscavam honra e estima significava, portanto, uma grande afronta. Além disso, a renúncia à autarquia e a confiança posta inteiramente na ação de um “outro” significava a negação de tudo o que os gregos consideravam como caminho para o sucesso.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) Os gregos buscavam a sabedoria que traria sucesso na política, nos tribunais, na filosofia, no comércio, numa vida autárquica e, especialmente, a aprovação ou admiração de seus respectivos pares.
+( II ) A perspectiva de vida baseada nesses valores não considera a “mensagem da cruz” uma afronta, pois a sabedoria humana vê esta mensagem como adequada a este modelo de vida.
+( III ) A “palavra da cruz” é desprezada, pois a pessoa que Paulo proclamava havia aceitado um tipo de sofrimento e morte que eram considerados desonra e vergonha.
+( IV ) A renúncia à autarquia e a confiança posta na ação de um “outro” não significava a negação de tudo o que os gregos consideravam como caminho para o sucesso.
+Está correto o que se afirma em:
+Escolha uma opção</t>
+  </si>
+  <si>
+    <t>I e III apenas.</t>
+  </si>
+  <si>
+    <t>I e II apenas.</t>
+  </si>
+  <si>
+    <t>I, II e IV apenas.</t>
+  </si>
+  <si>
+    <t>II e IV apenas.</t>
+  </si>
+  <si>
+    <t>Através do processo de helenização, a língua e a cultura gregas se difundiram por todo o mundo mediterrâneo, especialmente graças às cidades fundadas por Alexandre e seus sucessores. Nestas cidades a civilização grega era implantada e se difundia pelo território ao seu derredor. O Judaísmo e o cristianismo nascente não podem ser entendidos de forma isolada do padrão cultural e religioso helenístico, mas o helenismo não pode ser visto como uma rua de mão única. A língua e a cultura gregas foram também influenciadas pelas culturas afro-asiáticas dos povos conquistados (desenvolveu-se o grego coinê, a forma da língua grega usada pela maioria da população, bem como no Novo Testamento), expandiram-se as religiões salvíficas de mistério (sincretismo de cultos afro-asiáticos com cultos greco-romanos), o Judaísmo ficou conhecido e era praticado em toda a região graças à dispersão de judeus (o que facilitou a expansão do Cristianismo).
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) O processo de helenização possibilitou a difusão da língua e a cultura gregas se difundiram por todo o mundo mediterrâneo, especialmente graças às cidades fundadas por Alexandre e seus sucessores.
+( II ) O helenismo é uma rua de mão única.
+( III ) Com o helenismo desenvolveu-se o grego coinê, a forma da língua grega usada pela maioria da população, bem como no Novo Testamento.
+( IV ) A dispersão dos judeus não facilitou o conhecimento do Judaísmo e não ajudou na expansão do Cristianismo.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>I, II e III apenas.</t>
+  </si>
+  <si>
+    <t>Um dos nomes mais conhecidos do Judaísmo fora de Israel é o de Filo, da cidade de Alexandria, um judeu que escreveu várias obras em que apresentou o Judaísmo ao mundo helênico. Filo lê a Escritura alegoricamente, associando-lhe significados que previamente não lhe diziam respeito. Ele compara a relação entre o sentido literal e o alegórico com a que existe entre o corpo e a alma, e o fato de que a alegoria quer alcançar algo invisível e mais elevado implica que este sentido não pode ser imediatamente acessível aos leitores. O intérprete experiente pode penetrar até este sentido mais elevado que Deus queria preservar do leitor comum, que fica preso no conteúdo literal. Para Filo, aqueles que “com base em pequenos indícios, conseguem entender o invisível através do visível” estão em condições de captar o sentido mais profundo das Escrituras.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) Filo, da cidade de Alexandria, escreveu várias obras em que apresentou o Judaísmo ao mundo helênico.
+( II ) A leitura alegórica da Escritura permite a Filo associar-lhe significados que previamente não lhe diziam respeito.
+( III ) Filo compara a relação entre o sentido literal e o alegórico com a que existe entre o corpo e a alma.
+( IV ) A leitura alegórica de Filo não procura apresentar o invisível através do visível.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+I, II e III apenas.
+</t>
+  </si>
+  <si>
+    <t>O exercício do senhorio de Cristo é totalmente distinto. É um senhorio que não conquista, mas reconcilia; não gera uniformidade, mas unidade. É um senhorio sem estratégias, mas com relacionamentos. Um senhorio cujo poder é exercido pelo Deus que faz a paz mediante a morte do seu próprio Filho, e não a dos seus inimigos. Na tradição judaico-cristã, a paz (shalom) é a plena harmonia que Deus estabelece na sua criação, com destaque para a justiça social, econômica e política que é a harmonia aplicada à convivência humana. Para restaurar a harmonia rompida da criação, Deus entrega Seu Filho à morte reconciliadora em benefício da criação alienada do Pai. Ou, nas palavras do próprio crucificado: “o Filho do Homem não veio para ser servido, mas para servir, e dar a sua vida em resgate de muitos” (Mc 10,45).
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) O senhorio de Cristo não significa conquista, mas reconciliação; não gera uniformidade, mas unidade.
+( II ) No senhorio de Cristo o poder é exercido pelo Deus que faz a paz mediante a morte do seu próprio Filho, e não a dos seus inimigos.
+( III ) Na tradição judaico-cristã, a paz (shalom), a plena harmonia que Deus estabelece na sua criação, não envolve a justiça social, econômica e política.
+( IV ) Para restaurar a harmonia rompida da criação, Deus entrega Seu Filho à morte reconciliadora em benefício da criação alienada do Pai.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A tecnologia de produção era precária, fortemente dependente da mão-de-obra, mas em comparação com períodos anteriores era mais adequada, na medida em que se usavam ferramentas de ferro (especialmente arados) que permitiam maior produtividade, de modo que se produzia suficientemente para a subsistência da população geral do Império. O problema maior era a distribuição desses produtos, de tal forma que os governantes romanos tinham um papel importante na distribuição do trigo como um dos meios de manter a tranquilidade nos seus domínios. Avanços mais significativos se deram na construção de estradas e aquedutos, bem como no desenvolvimento de formas mais seguras de navegação ao longo das diversas costas do Mediterrâneo. Tais avanços foram necessários em função de dois fatores principais: o comércio e a manutenção do controle militar (exércitos dependem de boas estradas para alcançar com rapidez regiões de guerra). Em parte isto nos ajuda a entender a importância do controle dos exércitos na tomada e manutenção do poder imperial. Também nos ajuda a entender a importância da pax romana (“paz romana”) como mecanismo ideológico de apoio para a manutenção da tranquilidade nos domínios imperiais.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) Embora a tecnologia de produção fosse precária, na medida em que se usavam ferramentas de ferro que permitiam maior produtividade, se produzia suficientemente para a subsistência da população geral do Império.
+( II ) A distribuição desses produtos era tranquila, não necessitando dos governantes romanos para a sua realização.
+( III ) Aconteceram avanços na construção de estradas e aquedutos e no desenvolvimento de formas mais seguras de navegação ao longo das diversas costas do Mediterrâneo.
+( IV ) A pax romana (“paz romana”) era um mecanismo ideológico de apoio para a manutenção da tranquilidade nos domínios imperiais.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>I, III e IV apenas.</t>
+  </si>
+  <si>
+    <t>O Cristianismo nasceu durante um período em que todo o mundo helenístico estava sob o domínio do Império Romano. O mundo helenístico se localizava no entorno do mar Mediterrâneo. A palavra “mediterrâneo” significa “entre terras”, e o Mar Mediterrâneo era chamado mare internum (latim). Do ponto de vista geográfico, o mundo mediterrâneo engloba três continentes: Europa, Ásia e África – o que acarreta uma grande diversidade cultural, étnica, política, econômica e religiosa. Não só o domínio imperial romano, mas, já antes dele, a conquista de partes significativas da Ásia e África por Alexandre, o Grande (séc. IV a.C.), produziu uma espécie de homogeneização cultural-religiosa através da difusão do helenismo.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) O Cristianismo nasceu durante um período em que todo o mundo helenístico estava sob o domínio do Império Romano.
+( II ) A palavra “mediterrâneo” significa “entre terras”, e o Mar Mediterrâneo era chamado mare internum.
+( III ) Do ponto de vista geográfico, o mundo mediterrâneo engloba os continentes: Europa, Ásia, África e América.
+( IV ) A conquista de partes significativas da Ásia e África por Alexandre, o Grande (séc. IV a.C.), não produziu uma espécie de homogeneização cultural-religiosa através da difusão do helenismo.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Para os saduceus, a pureza consistia na ausência, ou baixa presença, de defeitos ou máculas de tipo ritual (a presença dessas máculas definia a impureza). Havia máculas provisórias, que podiam ser eliminadas mediante sacrifícios e lavagens cerimoniais, e máculas permanentes que não podiam ser eliminadas. O critério de definição da pureza vinha da Torá sacerdotal, e aplicava ao mundo humano regras similares aplicadas ao mundo não-humano. Pessoas cuja mácula não podia ser eliminada estavam definitivamente afastadas de Deus e não poderiam participar da salvação do povo de Deus. Pessoas cuja mácula poderia ser removida deveriam se submeter às instruções sacerdotais para alcançar a purificação. Pessoas sem mácula eram aquelas que cumpriam rigorosamente as exigências da Torá sacerdotal e desfrutariam plenamente da salvação na era messiânica. Para os fariseus, que não negavam as noções de pureza sacerdotal, os sintomas mais importantes da pureza ou impureza tinham a ver com o cumprimento da Torá moral – especialmente a guarda do sábado, a ausência de contato com animais e/ou pessoas impuras, e a prática da piedade pessoal – especialmente a esmola, a oração e o jejum. Além das marcas da pureza vinculadas à ação humana, os fariseus também classificavam as pessoas em escalas de pureza conforme a sua condição física e de saúde (de modo similar à classificação dos saduceus). Assim, pessoas portadoras de deficiências físicas permanentes eram consideradas impuras (cegas, surdas, mudas, paralíticas, etc.); enquanto certas doenças mantinham as pessoas em situação de impureza até a sua cura (doenças da pele, especialmente aquelas cuja cura era desconhecida, eram as mais evidentes doenças relativas à impureza). Tanto para fariseus quanto para saduceus, as mulheres, pelo simples fato de serem mulheres, já estavam em condição pior do que os homens no quesito da pureza.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) Para os saduceus, a pureza não envolvia defeitos ou máculas de tipo ritual (a presença dessas máculas definia a impureza).
+( II ) O critério de definição da pureza dos saduceus vinha da Torá sacerdotal, e aplicava ao mundo humano regras similares aplicadas ao mundo não-humano.
+( III ) Para os fariseus, os sintomas mais importantes da pureza ou impureza tinham a ver com o cumprimento da Torá moral: a guarda do sábado, a ausência de contato com animais e/ou pessoas impuras, a prática da piedade pessoal.
+( IV ) Para fariseus e saduceus as mulheres tinham o mesmo valor que os homens no quesito da pureza.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>II e III apenas.</t>
+  </si>
+  <si>
+    <t>O dito de Jesus sobre odres novos e remendos novos é fundamental para entender o discurso do seu movimento. Não é possível criar um novo mundo sem rompermos com as amarras do velho mundo. O discurso do movimento de Jesus era um discurso de tipo profético-apocalíptico. Da profecia vem a intensa crítica contra toda forma de injustiça e dominação. Da apocalíptica vem a intensa expectativa de uma transformação radical da realidade social. De ambas vem a confiante certeza em Deus como o Senhor da história, que encaminhará essa transformação em conformidade com Sua vontade libertadora. É por isso que o tema central da mensagem de Jesus é o Reino de Deus. Jesus não prega a si mesmo como rei, fala de si mesmo como servo, como filho, como aquele que foi enviado pelo Pai para anunciar e concretizar a iminente chegada do Reino. Se Deus reina, não pode imperar a injustiça, a violência, a opressão. Se Deus reina, rompidos estão os grilhões da Lei e ativa a salvação pela graça.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) O dito de Jesus sobre odres novos e remendos novos é fundamental para entender o discurso do seu movimento, mas é possível criar um mundo novo sem rompermos com as amarras do velho mundo.
+( II ) A profecia crítica apenas pecados individuais e hipocrisia religiosa.
+( III ) A apocalíptica contém uma intensa expectativa de uma transformação radical da realidade social.
+( IV ) Jesus fala de si mesmo como servo, como filho, como aquele que foi enviado pelo Pai para anunciar e concretizar a iminente chegada do Reino.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>III e IV apenas.</t>
+  </si>
+  <si>
+    <t>Os essênios têm um papel peculiar no universo discursivo judaico, pois se constituía como uma cunha de oposição radical dentro do campo discursivo do Judaísmo Oficial. Eles não podem ser classificados exclusivamente como um grupo de resistência na medida em que não se opõem às características dominantes do discurso oficial. São, sim, um grupo de oposição, uma vez que disputa a legitimidade da liderança sacerdotal, bem como a legitimidade da interpretação da Torá – deste modo, ameaçam tanto a estabilidade política dos saduceus quanto a liderança teológica dos fariseus. Sua interpretação da Torá era peculiar, com três grandes ênfases: (a) um dualismo angelológico e moral, com características de determinismo; (b) um messianismo apocalíptico e guerreiro radical, que alimentava sonhos de libertação total da dominação imperial; (c) uma espiritualidade radical de seguimento das normas comunitárias e de afastamento da vida cotidiana, com vistas à plena consagração à vontade soberana do Senhor.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) Os essênios não podem ser classificados como um grupo de resistência na medida em que não se opõem às características dominantes do discurso oficial judaico.
+( II ) Uma das características da sua interpretação da Torá era um dualismo angelológico e moral, com características de determinismo.
+( III ) Um messianismo apocalíptico e guerreiro radical, que alimentava sonhos de libertação total da dominação imperial, não fazia parte da interpretação da Torá pelos essênios.
+( IV ) Os essênios estavam perfeitamente integrados na social e cultural judaica.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>“É sintomático e carregado de sentido que desde o início, das primeiras vezes em que a pax romana é mencionada, se fala do imperador como chefe militar. O altar da paz ao Imperador Augusto, construído no simbólico lugar do Campo de Marte, deus da guerra, na verdade dava sentido à história da violência calcada no sucesso do vencedor. Sobre ele, o holocausto que queimava a vítima totalmente e por inteiro, sublinhava o fato do preço da paz proclamada e celebrada: o sangue derramado. A pax romana, portanto, é paz querida politicamente pelo imperador e seus mais altos funcionários, e estabelecida e garantida militarmente pela intervenção das legiões. A guerra que leva à vitória forma o pressuposto do tempo feliz da paz, no qual o Imperador triunfa. E este tempo feliz continua a ser assegurado pelas legiões e suas armas. Esta paz que Roma traz é paz-de-vitória para os romanos; para os vencidos, paz de submissão. Em teoria uma relação de direito entre dois parceiros, a pax romana é na realidade uma ordem de dominação. Roma é o parceiro que, a partir de si mesmo, ordena a relação e propõe as condições que o não romano deve aceitar, confirmando sua submissão ao poderoso Império que o protegia contra os ataques de outros povos estrangeiros. Esta paz estabelecida e mantida, portanto, com meios militares, é acompanhada de rios de sangue e lágrimas de enormes dimensões. Na verdade, nesta época da história, o mundo conhecido tem paz porque “todo o orbe terrestre” é dominado por Roma.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) O altar da paz ao Imperador Augusto era muito mais a história da violência calcada no sucesso do vencedor.
+( II ) A pax romana (“paz romana”) era desejada politicamente pelo imperador e seus mais altos funcionários, mas estabelecida e garantida militarmente pela intervenção das legiões.
+( III ) A pax romana (“paz romana”) era a realidade da ordem de dominação do mundo da época por Roma.
+( IV ) Os povos conquistados aceitavam amigavelmente as propostas da paz por Roma.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -636,8 +1991,18 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF001A1E"/>
+      <name val="Poppins"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF8E662E"/>
+      <name val="Poppins"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -656,6 +2021,12 @@
         <bgColor rgb="FFE7F3F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFDC"/>
+        <bgColor rgb="FFFCEFDC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -663,7 +2034,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -689,7 +2060,13 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -746,6 +2123,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -990,7 +2371,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="18.0"/>
     <col customWidth="1" min="2" max="2" width="53.63"/>
-    <col customWidth="1" min="3" max="3" width="51.38"/>
+    <col customWidth="1" min="3" max="3" width="22.88"/>
     <col customWidth="1" min="4" max="4" width="46.0"/>
     <col customWidth="1" min="5" max="5" width="49.5"/>
     <col customWidth="1" min="6" max="6" width="29.88"/>
@@ -2341,13 +3722,27 @@
       <c r="Z32" s="5"/>
     </row>
     <row r="33">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="A33" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -2369,13 +3764,27 @@
       <c r="Z33" s="5"/>
     </row>
     <row r="34">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
+      <c r="A34" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
@@ -2397,13 +3806,27 @@
       <c r="Z34" s="5"/>
     </row>
     <row r="35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="A35" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
@@ -2425,13 +3848,27 @@
       <c r="Z35" s="5"/>
     </row>
     <row r="36">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
+      <c r="A36" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
@@ -2453,13 +3890,27 @@
       <c r="Z36" s="5"/>
     </row>
     <row r="37">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+      <c r="A37" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
@@ -2481,13 +3932,27 @@
       <c r="Z37" s="5"/>
     </row>
     <row r="38">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
+      <c r="A38" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
@@ -2509,13 +3974,27 @@
       <c r="Z38" s="5"/>
     </row>
     <row r="39">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
+      <c r="A39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
@@ -2537,13 +4016,27 @@
       <c r="Z39" s="5"/>
     </row>
     <row r="40">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
+      <c r="A40" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
@@ -2565,13 +4058,27 @@
       <c r="Z40" s="5"/>
     </row>
     <row r="41">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
+      <c r="A41" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -2593,13 +4100,27 @@
       <c r="Z41" s="5"/>
     </row>
     <row r="42">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
+      <c r="A42" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
@@ -2621,13 +4142,27 @@
       <c r="Z42" s="5"/>
     </row>
     <row r="43">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
+      <c r="A43" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
@@ -2649,13 +4184,27 @@
       <c r="Z43" s="5"/>
     </row>
     <row r="44">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
+      <c r="A44" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
@@ -2677,13 +4226,27 @@
       <c r="Z44" s="5"/>
     </row>
     <row r="45">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
+      <c r="A45" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
@@ -2705,13 +4268,27 @@
       <c r="Z45" s="5"/>
     </row>
     <row r="46">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
+      <c r="A46" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
@@ -2733,13 +4310,27 @@
       <c r="Z46" s="5"/>
     </row>
     <row r="47">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
+      <c r="A47" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
@@ -2761,13 +4352,27 @@
       <c r="Z47" s="5"/>
     </row>
     <row r="48">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
+      <c r="A48" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
@@ -2789,13 +4394,27 @@
       <c r="Z48" s="5"/>
     </row>
     <row r="49">
-      <c r="A49" s="5"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+      <c r="A49" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
@@ -2817,13 +4436,27 @@
       <c r="Z49" s="5"/>
     </row>
     <row r="50">
-      <c r="A50" s="5"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
+      <c r="A50" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
@@ -2845,13 +4478,27 @@
       <c r="Z50" s="5"/>
     </row>
     <row r="51">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
+      <c r="A51" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C51" s="6">
+        <v>80.0</v>
+      </c>
+      <c r="D51" s="6">
+        <v>90.0</v>
+      </c>
+      <c r="E51" s="6">
+        <v>50.0</v>
+      </c>
+      <c r="F51" s="6">
+        <v>70.0</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
@@ -2873,13 +4520,27 @@
       <c r="Z51" s="5"/>
     </row>
     <row r="52">
-      <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
+      <c r="A52" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
@@ -2901,13 +4562,27 @@
       <c r="Z52" s="5"/>
     </row>
     <row r="53">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
+      <c r="A53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
@@ -2929,13 +4604,27 @@
       <c r="Z53" s="5"/>
     </row>
     <row r="54">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
+      <c r="A54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
@@ -2957,13 +4646,27 @@
       <c r="Z54" s="5"/>
     </row>
     <row r="55">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
+      <c r="A55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
@@ -2985,13 +4688,27 @@
       <c r="Z55" s="5"/>
     </row>
     <row r="56">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
+      <c r="A56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
@@ -3013,13 +4730,27 @@
       <c r="Z56" s="5"/>
     </row>
     <row r="57">
-      <c r="A57" s="5"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
+      <c r="A57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
@@ -3041,13 +4772,27 @@
       <c r="Z57" s="5"/>
     </row>
     <row r="58">
-      <c r="A58" s="5"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
+      <c r="A58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
@@ -3069,13 +4814,27 @@
       <c r="Z58" s="5"/>
     </row>
     <row r="59">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
+      <c r="A59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
@@ -3097,13 +4856,27 @@
       <c r="Z59" s="5"/>
     </row>
     <row r="60">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
+      <c r="A60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
@@ -3125,13 +4898,27 @@
       <c r="Z60" s="5"/>
     </row>
     <row r="61">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
+      <c r="A61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
@@ -3153,13 +4940,27 @@
       <c r="Z61" s="5"/>
     </row>
     <row r="62">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
+      <c r="A62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
@@ -3181,13 +4982,27 @@
       <c r="Z62" s="5"/>
     </row>
     <row r="63">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
+      <c r="A63" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
@@ -3209,13 +5024,27 @@
       <c r="Z63" s="5"/>
     </row>
     <row r="64">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
+      <c r="A64" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
@@ -3237,13 +5066,27 @@
       <c r="Z64" s="5"/>
     </row>
     <row r="65">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
+      <c r="A65" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
@@ -3265,13 +5108,27 @@
       <c r="Z65" s="5"/>
     </row>
     <row r="66">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
+      <c r="A66" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
@@ -3293,13 +5150,27 @@
       <c r="Z66" s="5"/>
     </row>
     <row r="67">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
+      <c r="A67" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
@@ -3321,13 +5192,27 @@
       <c r="Z67" s="5"/>
     </row>
     <row r="68">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
+      <c r="A68" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
@@ -3349,13 +5234,27 @@
       <c r="Z68" s="5"/>
     </row>
     <row r="69">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
+      <c r="A69" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
@@ -3377,13 +5276,27 @@
       <c r="Z69" s="5"/>
     </row>
     <row r="70">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
+      <c r="A70" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
@@ -3405,13 +5318,27 @@
       <c r="Z70" s="5"/>
     </row>
     <row r="71">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
+      <c r="A71" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
@@ -3433,13 +5360,27 @@
       <c r="Z71" s="5"/>
     </row>
     <row r="72">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
+      <c r="A72" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
@@ -3461,13 +5402,27 @@
       <c r="Z72" s="5"/>
     </row>
     <row r="73">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
+      <c r="A73" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
@@ -3489,13 +5444,27 @@
       <c r="Z73" s="5"/>
     </row>
     <row r="74">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
+      <c r="A74" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
@@ -3517,13 +5486,27 @@
       <c r="Z74" s="5"/>
     </row>
     <row r="75">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
+      <c r="A75" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3545,13 +5528,27 @@
       <c r="Z75" s="5"/>
     </row>
     <row r="76">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
+      <c r="A76" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
@@ -3573,13 +5570,27 @@
       <c r="Z76" s="5"/>
     </row>
     <row r="77">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
+      <c r="A77" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
@@ -3601,13 +5612,27 @@
       <c r="Z77" s="5"/>
     </row>
     <row r="78">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
+      <c r="A78" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -3629,13 +5654,27 @@
       <c r="Z78" s="5"/>
     </row>
     <row r="79">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
+      <c r="A79" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
@@ -3657,13 +5696,27 @@
       <c r="Z79" s="5"/>
     </row>
     <row r="80">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
+      <c r="A80" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
@@ -3685,13 +5738,27 @@
       <c r="Z80" s="5"/>
     </row>
     <row r="81">
-      <c r="A81" s="5"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
+      <c r="A81" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
@@ -3713,13 +5780,27 @@
       <c r="Z81" s="5"/>
     </row>
     <row r="82">
-      <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
+      <c r="A82" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -3741,13 +5822,27 @@
       <c r="Z82" s="5"/>
     </row>
     <row r="83">
-      <c r="A83" s="5"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
+      <c r="A83" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
@@ -3769,13 +5864,27 @@
       <c r="Z83" s="5"/>
     </row>
     <row r="84">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
+      <c r="A84" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
@@ -3797,13 +5906,27 @@
       <c r="Z84" s="5"/>
     </row>
     <row r="85">
-      <c r="A85" s="5"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
+      <c r="A85" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
@@ -3825,13 +5948,27 @@
       <c r="Z85" s="5"/>
     </row>
     <row r="86">
-      <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5"/>
+      <c r="A86" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
@@ -3853,13 +5990,27 @@
       <c r="Z86" s="5"/>
     </row>
     <row r="87">
-      <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
+      <c r="A87" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
@@ -3881,13 +6032,27 @@
       <c r="Z87" s="5"/>
     </row>
     <row r="88">
-      <c r="A88" s="5"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
+      <c r="A88" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
@@ -3909,13 +6074,27 @@
       <c r="Z88" s="5"/>
     </row>
     <row r="89">
-      <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
+      <c r="A89" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
@@ -3937,13 +6116,27 @@
       <c r="Z89" s="5"/>
     </row>
     <row r="90">
-      <c r="A90" s="5"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
+      <c r="A90" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
@@ -3965,13 +6158,27 @@
       <c r="Z90" s="5"/>
     </row>
     <row r="91">
-      <c r="A91" s="5"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
+      <c r="A91" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
@@ -3993,13 +6200,27 @@
       <c r="Z91" s="5"/>
     </row>
     <row r="92">
-      <c r="A92" s="5"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
+      <c r="A92" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
@@ -4021,13 +6242,27 @@
       <c r="Z92" s="5"/>
     </row>
     <row r="93">
-      <c r="A93" s="5"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
+      <c r="A93" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
@@ -4049,13 +6284,27 @@
       <c r="Z93" s="5"/>
     </row>
     <row r="94">
-      <c r="A94" s="5"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="5"/>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
+      <c r="A94" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
@@ -4077,13 +6326,27 @@
       <c r="Z94" s="5"/>
     </row>
     <row r="95">
-      <c r="A95" s="5"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
+      <c r="A95" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
@@ -4105,13 +6368,27 @@
       <c r="Z95" s="5"/>
     </row>
     <row r="96">
-      <c r="A96" s="5"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
+      <c r="A96" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
@@ -4133,13 +6410,27 @@
       <c r="Z96" s="5"/>
     </row>
     <row r="97">
-      <c r="A97" s="5"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
+      <c r="A97" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
@@ -4161,13 +6452,27 @@
       <c r="Z97" s="5"/>
     </row>
     <row r="98">
-      <c r="A98" s="5"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
+      <c r="A98" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
@@ -4189,13 +6494,27 @@
       <c r="Z98" s="5"/>
     </row>
     <row r="99">
-      <c r="A99" s="5"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
+      <c r="A99" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
@@ -4217,13 +6536,27 @@
       <c r="Z99" s="5"/>
     </row>
     <row r="100">
-      <c r="A100" s="5"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
+      <c r="A100" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
@@ -4245,13 +6578,27 @@
       <c r="Z100" s="5"/>
     </row>
     <row r="101">
-      <c r="A101" s="5"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
+      <c r="A101" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
@@ -4273,13 +6620,27 @@
       <c r="Z101" s="5"/>
     </row>
     <row r="102">
-      <c r="A102" s="5"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="5"/>
-      <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
-      <c r="G102" s="5"/>
+      <c r="A102" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
@@ -4301,13 +6662,27 @@
       <c r="Z102" s="5"/>
     </row>
     <row r="103">
-      <c r="A103" s="5"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-      <c r="G103" s="5"/>
+      <c r="A103" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
@@ -4329,13 +6704,27 @@
       <c r="Z103" s="5"/>
     </row>
     <row r="104">
-      <c r="A104" s="5"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
+      <c r="A104" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
@@ -4357,13 +6746,27 @@
       <c r="Z104" s="5"/>
     </row>
     <row r="105">
-      <c r="A105" s="5"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="5"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
+      <c r="A105" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
@@ -4385,13 +6788,27 @@
       <c r="Z105" s="5"/>
     </row>
     <row r="106">
-      <c r="A106" s="5"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
+      <c r="A106" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
@@ -4413,13 +6830,27 @@
       <c r="Z106" s="5"/>
     </row>
     <row r="107">
-      <c r="A107" s="5"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
-      <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-      <c r="G107" s="5"/>
+      <c r="A107" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
@@ -4441,13 +6872,27 @@
       <c r="Z107" s="5"/>
     </row>
     <row r="108">
-      <c r="A108" s="5"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-      <c r="G108" s="5"/>
+      <c r="A108" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
@@ -4469,13 +6914,27 @@
       <c r="Z108" s="5"/>
     </row>
     <row r="109">
-      <c r="A109" s="5"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-      <c r="G109" s="5"/>
+      <c r="A109" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
@@ -4497,13 +6956,27 @@
       <c r="Z109" s="5"/>
     </row>
     <row r="110">
-      <c r="A110" s="5"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="5"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-      <c r="G110" s="5"/>
+      <c r="A110" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
@@ -4525,13 +6998,27 @@
       <c r="Z110" s="5"/>
     </row>
     <row r="111">
-      <c r="A111" s="5"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-      <c r="G111" s="5"/>
+      <c r="A111" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
@@ -4553,13 +7040,27 @@
       <c r="Z111" s="5"/>
     </row>
     <row r="112">
-      <c r="A112" s="5"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-      <c r="G112" s="5"/>
+      <c r="A112" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
@@ -4581,13 +7082,27 @@
       <c r="Z112" s="5"/>
     </row>
     <row r="113">
-      <c r="A113" s="5"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
-      <c r="G113" s="5"/>
+      <c r="A113" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
@@ -4609,13 +7124,27 @@
       <c r="Z113" s="5"/>
     </row>
     <row r="114">
-      <c r="A114" s="5"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
+      <c r="A114" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
@@ -4637,13 +7166,27 @@
       <c r="Z114" s="5"/>
     </row>
     <row r="115">
-      <c r="A115" s="5"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
-      <c r="G115" s="5"/>
+      <c r="A115" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
@@ -4665,13 +7208,27 @@
       <c r="Z115" s="5"/>
     </row>
     <row r="116">
-      <c r="A116" s="5"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-      <c r="G116" s="5"/>
+      <c r="A116" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
@@ -4693,13 +7250,27 @@
       <c r="Z116" s="5"/>
     </row>
     <row r="117">
-      <c r="A117" s="5"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
-      <c r="G117" s="5"/>
+      <c r="A117" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
@@ -4721,13 +7292,27 @@
       <c r="Z117" s="5"/>
     </row>
     <row r="118">
-      <c r="A118" s="5"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="5"/>
-      <c r="D118" s="5"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="5"/>
-      <c r="G118" s="5"/>
+      <c r="A118" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
@@ -4749,13 +7334,27 @@
       <c r="Z118" s="5"/>
     </row>
     <row r="119">
-      <c r="A119" s="5"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
-      <c r="G119" s="5"/>
+      <c r="A119" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
@@ -4777,13 +7376,27 @@
       <c r="Z119" s="5"/>
     </row>
     <row r="120">
-      <c r="A120" s="5"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="5"/>
-      <c r="G120" s="5"/>
+      <c r="A120" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
@@ -4805,13 +7418,27 @@
       <c r="Z120" s="5"/>
     </row>
     <row r="121">
-      <c r="A121" s="5"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="5"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
+      <c r="A121" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
@@ -4833,13 +7460,27 @@
       <c r="Z121" s="5"/>
     </row>
     <row r="122">
-      <c r="A122" s="5"/>
-      <c r="B122" s="5"/>
-      <c r="C122" s="5"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
-      <c r="G122" s="5"/>
+      <c r="A122" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>

--- a/Simulados Faculdade.xlsx
+++ b/Simulados Faculdade.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="591">
   <si>
     <t>Matéria</t>
   </si>
@@ -606,13 +606,1532 @@
   <si>
     <t xml:space="preserve">Fazer um consenso entre os três Evangelhos sinóticos.
 </t>
+  </si>
+  <si>
+    <t>Como filho amado/único, Jesus encarna o verdadeiro Israel, na condição daquele que irá sofrer pelo povo, tal como um cordeiro pascal. Essa condição é indicada pela comparação de Jesus com o seguinte personagem da história de Israel:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Abraão</t>
+  </si>
+  <si>
+    <t>Isaque</t>
+  </si>
+  <si>
+    <t>Esaú</t>
+  </si>
+  <si>
+    <t>Ismael.</t>
+  </si>
+  <si>
+    <t>As marcas textuais do evangelho de Lucas revelam que as comunidades para as quais foi escrito eram predominantemente...
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Judaicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gentílicas.
+</t>
+  </si>
+  <si>
+    <t>Cristãs antigas.</t>
+  </si>
+  <si>
+    <t>Israelitas.</t>
+  </si>
+  <si>
+    <t>Qual é a mensagem Central do Evangelho de Marcos?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesus, o sucessor de João.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesus é o Messias, Filho de Deus.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesus, o Libertador.
+</t>
+  </si>
+  <si>
+    <t>Jesus, o Filho do homem.</t>
+  </si>
+  <si>
+    <t>A palavra parábola vem do grego parabole que significa, literalmente:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Comparação.</t>
+  </si>
+  <si>
+    <t>Lançar ao lado.</t>
+  </si>
+  <si>
+    <t>Enigma.</t>
+  </si>
+  <si>
+    <t>Provérbios.</t>
+  </si>
+  <si>
+    <t>Blasfemar contra o Espírito Santo que acompanhou o ministério de Jesus equivale a:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejeitar a mensagem do evangelho.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um ato contra o próprio reino satânico.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceitar entrar no reino de Deus.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ser condenado diretamente e sem perdão ao inferno.
+</t>
+  </si>
+  <si>
+    <t>Qual evangelho sinótico é considerado o mais antigo?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Mateus.</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>Marcos.</t>
+  </si>
+  <si>
+    <t>João</t>
+  </si>
+  <si>
+    <t>Na linguagem mais comum em manuais de exegese e hermenêutica bíblica os gêneros textuais são nomeados de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formas literárias.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos de expressão.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criações estilísticas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano de conteúdo.
+</t>
+  </si>
+  <si>
+    <t>Em Apocalipse 21:1-15, João expõe a visão do novo mundo baseado nas:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tradições veterotestamentárias.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na saciedade que põe fim a toda fome.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bem-aventuranças de Jesus.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vinda do reino.
+</t>
+  </si>
+  <si>
+    <t>Sinóticos deriva de duas palavras gregas que, literalmente, significam:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Harmonia</t>
+  </si>
+  <si>
+    <t>Biografia</t>
+  </si>
+  <si>
+    <t>Unidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visão comum.
+</t>
+  </si>
+  <si>
+    <t>Por que os escribas de Jerusalém acusaram Jesus de ser possesso por Belzebu?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque ele fazia milagres.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque comparavam Jesus a um ladrão.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque ele expulsava os demônios.
+</t>
+  </si>
+  <si>
+    <t>Porque achavam que ele praticava exorcismo.</t>
+  </si>
+  <si>
+    <t>A relação mais amistosa de Jesus com a tradição bíblica israelita é acentuada no Evangelho de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Mateus</t>
+  </si>
+  <si>
+    <t>Marcos</t>
+  </si>
+  <si>
+    <t>Qual é a primeira característica da identidade messiânica de Jesus?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foi ao deserto para ser tentado.
+</t>
+  </si>
+  <si>
+    <t>A escolha dos discípulos.</t>
+  </si>
+  <si>
+    <t>Sua fidelidade filial.</t>
+  </si>
+  <si>
+    <t>O batismo de Jesus.</t>
+  </si>
+  <si>
+    <t>Qual advérbio, típico do evangelho de Marcos, ressalta a dinamicidade dos eventos?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Perfeitamente</t>
+  </si>
+  <si>
+    <t>Certamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imediatamente.
+</t>
+  </si>
+  <si>
+    <t>Infelizmente.</t>
+  </si>
+  <si>
+    <t>Jesus caminha da Galileia ao Jordão, deste ao deserto, então, de volta à Galileia. O percurso geográfico de Jesus é o percurso marcado pela:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Solidariedade</t>
+  </si>
+  <si>
+    <t>Santidade</t>
+  </si>
+  <si>
+    <t>Impureza.</t>
+  </si>
+  <si>
+    <t>Desprezo</t>
+  </si>
+  <si>
+    <t>Qual é o primeiro ato solidário de Jesus com pessoas impuras e pecadoras que concretiza sua solidariedade com eles?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elege o novo Israel.
+</t>
+  </si>
+  <si>
+    <t>Derrota os inimigos do Pai.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ora e busca forças ao pai.
+</t>
+  </si>
+  <si>
+    <t>Batismo de Jesus.</t>
+  </si>
+  <si>
+    <t>Qual é o primeiro ato público relatado do ministério de Jesus?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A perícope do chamado.</t>
+  </si>
+  <si>
+    <t>Tentação de Jesus.</t>
+  </si>
+  <si>
+    <t>O batismo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pregação do reino de Deus.
+</t>
+  </si>
+  <si>
+    <t>A mensagem central do Evangelho de Lucas: Jesus é o Messias, Filho do Homem e Filho de Deus, é similar aos seguintes evangelhos:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Mateus e João.</t>
+  </si>
+  <si>
+    <t>Marcos e João.</t>
+  </si>
+  <si>
+    <t>Tomé e Mateus.</t>
+  </si>
+  <si>
+    <t>Marcos e Mateus.</t>
+  </si>
+  <si>
+    <t>Para quem era essencial a exigência da lei?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>Fariseus</t>
+  </si>
+  <si>
+    <t>Palestinos</t>
+  </si>
+  <si>
+    <t>Deus</t>
+  </si>
+  <si>
+    <t>O evangelho de Marcos provavelmente foi escrito nos primeiros anos da década de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Qual é o maior dos evangelhos?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Lucas.</t>
+  </si>
+  <si>
+    <t>João.</t>
+  </si>
+  <si>
+    <t>A função que coloca em destaque o código linguístico é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Metalinguagem.</t>
+  </si>
+  <si>
+    <t>Conativa.</t>
+  </si>
+  <si>
+    <t>Referencial</t>
+  </si>
+  <si>
+    <t>Fática</t>
+  </si>
+  <si>
+    <t>É um exemplo de oração coordena Sindética Aditiva, a seguinte oração:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Não só pulei como também corri.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nem pulei e nem dancei durante a festa.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprei um quilo de banana e fui trabalhar.
+</t>
+  </si>
+  <si>
+    <t>Todas as alternativas estão corretas.</t>
+  </si>
+  <si>
+    <t>Na frase: “ No coração da floresta existe um grande amor escondido”. É certo afirmar que é um exemplo de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metáfora.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metonímia.
+</t>
+  </si>
+  <si>
+    <t>Sinestesia</t>
+  </si>
+  <si>
+    <t>Não pode ser considerada uma comparação a seguinte frase:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O rio é a lágrima de um oceano.</t>
+  </si>
+  <si>
+    <t>O rio é tal qual a lágrima de um oceano.</t>
+  </si>
+  <si>
+    <t>O rio é como a lágrima de um oceano.</t>
+  </si>
+  <si>
+    <t>O rio é semelhante a lágrima de um oceano.</t>
+  </si>
+  <si>
+    <t>Marque a alternativa correta:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O adjetivo concorda em gênero com o substantivo a que se refere.</t>
+  </si>
+  <si>
+    <t>O adjetivo só concorda com o número a que se refere o substantivo.</t>
+  </si>
+  <si>
+    <t>O adjetivo só tem uma forma.</t>
+  </si>
+  <si>
+    <t>O adjetivo não sofre flexão de grau.</t>
+  </si>
+  <si>
+    <t>Artigo é palavra que antepomos ao substantivo para:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Determiná-lo, indicar seu gênero e número.</t>
+  </si>
+  <si>
+    <t>Indicar o tempo verbal.</t>
+  </si>
+  <si>
+    <t>Classificar os adjetivos.</t>
+  </si>
+  <si>
+    <t>Regulamentar o uso dos pronomes.</t>
+  </si>
+  <si>
+    <t>O verbo pode aparecer na voz ativa e passiva. Marque a frase em que ele aparece na voz passiva:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O carro foi roubado.</t>
+  </si>
+  <si>
+    <t>A obra foi feita por ela.</t>
+  </si>
+  <si>
+    <t>A menina cortou-se.</t>
+  </si>
+  <si>
+    <t>Esta função tem por objetivo colocar o receptor numa posição de destaque. É uma afirmação que cabe somente à função:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Poética.</t>
+  </si>
+  <si>
+    <t>Metalinguística.</t>
+  </si>
+  <si>
+    <t>Conativa</t>
+  </si>
+  <si>
+    <t>Assinale a frase em que há erro de regência verbal:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A nota precisa de referência.</t>
+  </si>
+  <si>
+    <t>O dono realizou o levantamento das necessidades da loja.</t>
+  </si>
+  <si>
+    <t>Os médicos assistiram o simpósio e acharam-no muito interessante.</t>
+  </si>
+  <si>
+    <t>É preciso que todos cumpram às diretrizes da escola.</t>
+  </si>
+  <si>
+    <t>No enunciado “Trata-se de uma notícia muito boa!” O artigo é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Definido plural.</t>
+  </si>
+  <si>
+    <t>Indefinido singular.</t>
+  </si>
+  <si>
+    <t>Definido singular.</t>
+  </si>
+  <si>
+    <t>Indefinido plural.</t>
+  </si>
+  <si>
+    <t>Filosofia da Religião</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas não descreve adequadamente a noção de sagrado?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrado diz respeito a algo espiritual e não se refere às coisas materiais e mundanas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrado é uma qualidade inerente à pessoa ou objeto sacralizado, o que significa que independe das pessoas ou situações.
+</t>
+  </si>
+  <si>
+    <t>O sagrado jamais se confunde com o profano, e isso significa que no mundo há coisas ou pessoas que são desde sempre sagradas e coisas ou pessoas que são desde sempre profanas.</t>
+  </si>
+  <si>
+    <t>Nenhuma das afirmativas descreve bem a noção de sagrado.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas expressa uma perspectiva metafísica da Teologia?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A Teologia é a guardião da são doutrina, o que significa que suas descrições da realidade e da pessoa de Deus precisam se ancorar na revelação divina para que tenha validade universal.</t>
+  </si>
+  <si>
+    <t>Deus é uma realidade que independe do modo como o compreendemos, e qualquer conhecimento que se construa sobre ele deve ser buscado a partir dessa realidade autônoma e não nas descrições humanas sobre ele.</t>
+  </si>
+  <si>
+    <t>Pode-se dizer que a Teologia é o estudo da pessoa de Deus e de suas relações para com os humanos, e isso significa que deve ser compreendida numa perspectiva universal, independente dos contextos interpretativos.</t>
+  </si>
+  <si>
+    <t>Todas as afirmativas expressam uma perspectiva metafísica da Teologia.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas expressa melhor o efeito que o sagrado nos provoca?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O sagrado sempre nos causa temor, pois é isso em relação ao qual mantemos certa distância.</t>
+  </si>
+  <si>
+    <t>O sagrado sempre suscita intimidade, pois é isso em relação ao qual nos sentimos atraídos.</t>
+  </si>
+  <si>
+    <t>O sagrado é ambíguo, porquanto ao mesmo tempo em que dele mantemos certa distância pelo temor que nos provoca, por ele também nos sentimos atraídos e somos seduzidos a certa intimidade.</t>
+  </si>
+  <si>
+    <t>Nenhuma das afirmativas acima descrevem o efeito que o sagrado nos provoca.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas caracteriza adequadamente o sagrado?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O sagrado não é uma qualidade inerente à pessoa ou objeto sacralizado, o que significa que depende do sujeito que o venera.</t>
+  </si>
+  <si>
+    <t>Todas as afirmativas caracterizam adequadamente o sagrado.</t>
+  </si>
+  <si>
+    <t>O sagrado pode se confundir com o profano, e isso significa que no mundo não há coisas ou pessoas que são desde sempre sagradas e coisas ou pessoas que são desde sempre profanas.</t>
+  </si>
+  <si>
+    <t>O sagrado é qualitativamente diferente do profano, e o que é sagrado para uns é profano para outros.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas descreve melhor a noção de sagrado?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O sagrado diz respeito a algo espiritual e não se refere às coisas materiais e mundanas.</t>
+  </si>
+  <si>
+    <t>O sagrado é uma qualidade inerente à pessoa ou objeto sacralizado, o que significa que independe das pessoas ou situações.</t>
+  </si>
+  <si>
+    <t>O sagrado é qualitativamente diferente do profano, mas não é uma qualidade inerente à pessoa ou objeto sacralizado, o que significa que depende do sujeito que o venera — o que é sagrado para uns é profano para outros.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes alternativas NÃO caracteriza o papel da teologia numa sociedade democrática?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A teologia deve contribuir positivamente para a participação efetiva e consciente de pessoas religiosas na democracia.</t>
+  </si>
+  <si>
+    <t>É importante que a teologia se apresente de forma plural, mas de modo que as suas diferentes vozes e perspectivas não sejam vistas como concorrentes, mas como parceiras de diálogo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A teologia precisa se apresentar como guardiã da democracia, defendendo-a dos fundamentalismos religiosos dos mais diversos tipos que ameaçam as sociedades contemporâneas.
+</t>
+  </si>
+  <si>
+    <t>A teologia deve se apresentar em sua unidade fundamental, de maneira que sua pluralidade de vozes ceda lugar a uma só voz (unidade), a fim de que possa afetar positivamente a sociedade democrática.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas expressa uma perspectiva pós-metafísica da Teologia?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Pode-se dizer que a Teologia é o estudo das descrições humanas sobre Deus e suas relações para com os humanos, e isso significa que deve ser compreendida numa perspectiva local, a partir dos contextos interpretativos.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas possibilita inferir que o autor de Eclesiastes dialoga criticamente com as filosofias (sabedorias) do mundo grego e também do mundo oriental mesopotâmico?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Os mesmos conteúdos tratados no livro de Eclesiastes também são objetos de reflexão filosófica pelo mundo grego e mesopotâmico nos tempos iniciais da dominação de Judá pelos helenistas.</t>
+  </si>
+  <si>
+    <t>Todas as alternativas são verdadeiras.</t>
+  </si>
+  <si>
+    <t>O conceito de nulidade reúne o discurso judaico do discurso filosófico pós-metafísico na medida em que propõe o fim do fundamentalismo, tanto religioso quanto filosófico.</t>
+  </si>
+  <si>
+    <t>Há uma lógica, filosófica ou teológica, que atravessa a lógica poética, a desloca, se sustenta nela, mas não corresponde ao seu projeto. Uma lógica eivada de contrapontos, tensões e contradições, que obrigam leitores de Eclesiastes a exercícios intelectuais desafiadores.</t>
+  </si>
+  <si>
+    <t>Como Rorty vê a tarefa da Filosofia da religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Discute a relação da filosofia com a religião sob a ótica da tradução. Para ele, nesse esforço dialogal, a prioridade deveria ser o delineamento dos espaços próprios das diferentes linguagens da religião e da ciência.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Filosofia da Religião deve, com o auxílio das ciências, investigar em que medida as religiões se alinham com a verdade, afinal, uma de suas tarefas consiste em se buscar essa verdade.
+</t>
+  </si>
+  <si>
+    <t>A Filosofia da Religião pressupõe que o valor das ideias resida em sua utilidade ou conveniência, e não em sua fidelidade a um ideal transcendente.</t>
+  </si>
+  <si>
+    <t>Nenhuma das alternativas disponíveis.</t>
+  </si>
+  <si>
+    <t>A abordagem filosófica sistemática da religião é um produto do pensamento moderno. Quanto a isso, qual das afirmativas abaixo não é verdadeira?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A antiguidade clássica não considerou o tema como um aspecto particular de investigação, numa perspectiva sistematizada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A antiguidade clássica, bem como o pensamento cristão medieval, também elaboraram reflexões concernentes ao tema da religião.
+</t>
+  </si>
+  <si>
+    <t>A antiguidade clássica, bem como o pensamento cristão medieval, não elaboraram reflexões concernentes ao tema da religião.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abordagem sistemática, torna-se importante e necessária em virtude do conflito instaurado entre o mundo moderno, cada vez mais interessado no processo de libertação do homem a partir da ótica iluminista, e as doutrinas e instituições religiosas derivadas da tradição judaico-cristãs.
+</t>
+  </si>
+  <si>
+    <t>Qual das seguintes alternativas corresponde a uma tarefa da teologia em tom pós-metafísico?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A partir do diálogo público, defender a sociedade — especialmente as vítimas do capitalismo voraz — da dominação sistêmica.</t>
+  </si>
+  <si>
+    <t>A partir do diálogo religioso intramuros, defender os interesses do cristianismo da dominação antirreligiosa.</t>
+  </si>
+  <si>
+    <t>Defender a sociedade dos interesses de grupos defensores do ateísmo ou de religiões não-cristãs que interferem nas decisões do Estado a favor do cristianismo.</t>
+  </si>
+  <si>
+    <t>Defender a fé dos ataques à fé cristã, normalmente realizados a partir de conceitos derivados da ciência ou  da filosofia.</t>
+  </si>
+  <si>
+    <t>Qual das afirmativas Não demonstra uma tarefa da filosofia na contemporaneidade?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Mediar hermeneuticamente entre diferentes linguagens e não recair na posição de substituta da religião.</t>
+  </si>
+  <si>
+    <t>Desenvolver a dimensão epistemológica do saber.</t>
+  </si>
+  <si>
+    <t>Apoiar o aperfeiçoamento da democracia.</t>
+  </si>
+  <si>
+    <t>Desenvolver a dimensão terapêutica da racionalidade.</t>
+  </si>
+  <si>
+    <t>Qual o papel da teologia em tom pós-metafísico, em sua vertente libertadora?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Defender os direitos das pessoas mais empobrecidas e vitimadas pela globalização geográfica e simbólica da ideologia do livre-mercado e sua profetiza, a tecnologia.</t>
+  </si>
+  <si>
+    <t>Lutar por uma compreensão teológica mais fundamentada da realidade da libertação espiritual proposta pelo cristianismo ao longo de sua história.</t>
+  </si>
+  <si>
+    <t>Auxiliar a prática pastoral, na medida em que esta se baseia no fato de que as pessoas estão cada vez mais como “ovelhas sem pastor” e, portanto, necessitam de libertação.</t>
+  </si>
+  <si>
+    <t>Qual o período da história em que a filosofia assumiu o papel normativo, outrora pertencente à teologia e às vertentes clássicas da filosofia?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Primeira parte da Modernidade.</t>
+  </si>
+  <si>
+    <t>Durante toda a Modernidade.</t>
+  </si>
+  <si>
+    <t>Na Pós-Modernidade.</t>
+  </si>
+  <si>
+    <t>Durante a Idade Média</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas NÃO expressa um dos três grandes momentos de conflitividade entre filosofia e religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Quando filósofos tiveram de disputar com sacerdotes e líderes religiosos o direito de dizer a verdadee o prestígio social proveniente desse direito.</t>
+  </si>
+  <si>
+    <t>Quando o Cristianismo se tornou a religião oficial do Império Romano e a Igreja assumiu o controle da produção do saber legítimo, resultando numa predominância da teologia sobre a filosofia.</t>
+  </si>
+  <si>
+    <t>A partir da Modernidade, em que os interesses teológicos na busca pela verdade predominaram sobre os interesses filosóficos.</t>
+  </si>
+  <si>
+    <t>A partir da Modernidade até nossos dias, com os movimentos de secularização da sociedade, e a paulatina ascensão da ciência sobre a filosofia e a teologia.</t>
+  </si>
+  <si>
+    <t>Como Habermas vê a tarefa da filosofia da religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Para ele, o valor das ideias reside em sua utilidade, ou conveniência, e não na sua fidelidade a um ideal transcendente.</t>
+  </si>
+  <si>
+    <t>A filosofia, em tom pós-metafísico, não pode mais desempenhar o papel de discurso fundacional, mas deve assumir o lugar de mediadora, intérprete entre diferentes formas do saber humano. A filosofia da religião deveria se esforçar, primeiro, para, em diálogo com as pessoas e comunidades de fé, traduzir conceitos religiosos em linguagem não-religiosa, aberta.</t>
+  </si>
+  <si>
+    <t>A filosofia da religião deve, com o auxílio das ciências, investigar em que medida as religiões se alinham com a verdade, afinal, uma de suas tarefas consiste em se buscar essa verdade.</t>
+  </si>
+  <si>
+    <t>Resgatar a boa tradição.</t>
+  </si>
+  <si>
+    <t>Qual dos seguintes paradoxos aproxima o livro de Eclesiastes da reflexão filosófica contemporânea?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Se queremos compreender o “céu”, precisamos compreender a “terra”.</t>
+  </si>
+  <si>
+    <t>Se queremos compreender a vida, precisamos nos encantar com a morte.</t>
+  </si>
+  <si>
+    <t>Se queremos compreender a alma, precisamos aceitar o corpo.</t>
+  </si>
+  <si>
+    <t>Se queremos compreender a libertação, precisamos compreender a dominação.</t>
+  </si>
+  <si>
+    <t>A antiguidade clássica, bem como o pensamento cristão medieval, também elaboraram reflexões concernentes ao tema da religião.</t>
+  </si>
+  <si>
+    <t>A antiguidade clássica também considerou o tema como um aspecto particular de investigação, numa perspectiva sistematizada.</t>
+  </si>
+  <si>
+    <t>Abordagem sistemática, torna-se importante e necessária em virtude do conflito instaurado entre o mundo moderno, cada vez mais interessado no processo de libertação do homem a partir da ótica iluminista, e as doutrinas e instituições religiosas derivadas da tradição judaico-cristãs.</t>
+  </si>
+  <si>
+    <t>Qual a diferença entre a abordagem filosófica da religião e a abordagem da Psicologia da Religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), o enfoque da Psicologia da Religião é mais descritivo, afinal, parte do pressuposto de que interpretar um fato religioso implica em se conhecê-lo.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Psicologia da Religião a religião é uma forma fundamental de coesão social, ou seja, o fenômeno religioso mostra a realidade social e é essencialmente comunitário.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Psicologia da Religião os fatos religiosos espelham a psique humana, o que significa dizer que sem o ser humano, não há experiência religiosa, afinal, o sentimento religioso é uma elaboração do eros básico do ser humano.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), a Psicologia da Religião estuda a intencionalidade dos fatos religiosos, os testemunhos do ser humano religioso e o que para ele significam tais fatos, o que significa que o interesse está no modo como esse fenômeno se manifesta e como é recebido por aqueles que são adeptos dessas instituições.</t>
+  </si>
+  <si>
+    <t>Qual a diferença entre a abordagem filosófica da religião e a abordagem da Sociologia da Religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), o enfoque da Sociologia da Religião é mais descritivo, afinal, parte do pressuposto de que interpretar um fato religioso implica em se conhecê-lo.
+</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Sociologia da Religião a religião é uma forma fundamental de coesão social, ou seja, o fenômeno religioso mostra a realidade social e é essencialmente comunitário.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Sociologia da Religião os fatos religiosos espelham a psique humana, o que significa dizer que sem o ser humano, não há experiência religiosa, afinal, o sentimento religioso é uma elaboração do eros básico do ser humano.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), a Sociologia da Religião estuda a intencionalidade dos fatos religiosos, os testemunhos do ser humano religioso e o que para ele significam tais fatos, o que significa que o interesse está no modo como esse fenômeno se manifesta e como é recebido por aqueles que são adeptos dessas instituições.</t>
+  </si>
+  <si>
+    <t>“Quando qualquer coisa da criação de Deus é usada de maneira que não possa ser oferecida a Deus como um culto e não possa ser um ato de justiça, o universo foi profanado, por que o universo foi instrumentalizado para qualquer outra coisa que não seja o culto devido ao seu Criador. Então, isso quer dizer que qualquer movimento que descaracterize o propósito da criação de todas as coisas é um movimento profano. E qualquer movimento que leve a criação ao seu propósito, que é prestar ao Criador o culto que lhe é devido, é um movimento sagrado” (Cf. http://bit.ly/2jYSYyQ).
+Considere o trecho de uma fala de Ariovaldo Ramos, acima descrita, e responda: qual das seguintes alternativas não reflete o que está sendo dito?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Todas as coisas devem ser sacralizadas a fim de que prestem testemunho de que Deus é o Criador de tudo.</t>
+  </si>
+  <si>
+    <t>Sagrado e profano são operações do olhar, o que significa que as mesmas coisas podem ser sagradas e profanas, dependendo de como sejam vistas por cada pessoa.</t>
+  </si>
+  <si>
+    <t>O profano é compreendido de maneira negativa, como aquilo que supostamente não é dedicado a Deus ou que sobrevive de forma a descaracterizar o propósito da criação, que é prestar culto ao seu Criador.</t>
+  </si>
+  <si>
+    <t>Nenhuma das alternativas anteriores.</t>
+  </si>
+  <si>
+    <t>Qual das seguintes alternativas NÃO consiste numa sociedade pós-secular?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Uma sociedade na qual o discurso religioso, tanto quanto o discurso secular, tenham legitimidade na “arena pública”.</t>
+  </si>
+  <si>
+    <t>Uma sociedade na qual a consciência pública espelha muito mais um juízo normativo que tem consequências para o contato político entre cidadãos não-crentes e crentes.</t>
+  </si>
+  <si>
+    <t>Uma sociedade na qual não se tenta convencer a sociedade a destruir as crenças e instituições religiosas, nem mesmo impedir pessoas e instituições religiosas de participarem nos debates políticos nacionais.</t>
+  </si>
+  <si>
+    <t>Uma sociedade que legitima o secularismo e rejeita o fundamentalismo, enquanto perspectiva fundacional e antidemocrática.</t>
+  </si>
+  <si>
+    <t>Qual a diferença entre a abordagem filosófica da religião e a abordagem da Fenomenologia da Religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), o enfoque da Fenomenologia  da Religião é mais descritivo, afinal, parte do pressuposto de que interpretar um fato religioso implica em se conhecê-lo.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Fenomenologia  da Religião a religião é uma forma fundamental de coesão social, ou seja, o fenômeno religioso mostra a realidade social e é essencialmente comunitário.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), para a Fenomenologia  da Religião os fatos religiosos espelham a psique humana, o que significa dizer que sem o ser humano, não há experiência religiosa, afinal, o sentimento religioso é uma elaboração do eros básico do ser humano.</t>
+  </si>
+  <si>
+    <t>Enquanto a Filosofia se preocupa com o absoluto na condição de ser e de fundamento de toda a realidade (perspectiva de cunho mais metafísico) ou se preocupa com o ser numa uma perspectiva hermenêutico-antropológica (perspectiva de cunho mais pós-metafísico), a Fenomenologia  da Religião estuda a intencionalidade dos fatos religiosos, os testemunhos do ser humano religioso e o que para ele significam tais fatos, o que significa que o interesse está no modo como esse fenômeno se manifesta e como é recebido por aqueles que são adeptos dessas instituições.</t>
+  </si>
+  <si>
+    <t>Contribuir para a integração dos saberes em face dos perigos da fragmentação do conhecimento e da cisão entre as diferentes dimensões da razão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defender a fé dos ataques à fé cristã, normalmente realizados a partir de conceitos derivados da ciência ou  da filosofia.
+</t>
+  </si>
+  <si>
+    <t>Qual das seguintes afirmativas expressa um dos três grandes momentos de conflitividade entre filosofia e religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Quando cientistas tiveram de disputar com filósofos e líderes religiosos o direito de dizer a verdade e o prestígio social proveniente desse direito.</t>
+  </si>
+  <si>
+    <t>A Idade Média, caracterizada pelos movimentos de secularização da sociedade, e a paulatina ascensão da ciência sobre a filosofia e a teologia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defender a sociedade dos interesses, por vezes míopes, de instituições religiosas que interferem inadequadamente na discussão dos limites da ciência.
+</t>
+  </si>
+  <si>
+    <t>Interpretar os novos movimentos à luz dos clássicos e afirmar seu caráter de mestra e rainha do saber.</t>
+  </si>
+  <si>
+    <t>Em que termos Gianni Vattimo concebe a verdade revelada nas Escrituras?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Como a verdade do dogma, fruto da tradição.</t>
+  </si>
+  <si>
+    <t>Como a verdade da teologia, fruto da reflexão crítica.</t>
+  </si>
+  <si>
+    <t>Como a verdade da ciência, fruto da observação.</t>
+  </si>
+  <si>
+    <t>Como a verdade do amor, da caridade, fruto de um chamado à prática.</t>
+  </si>
+  <si>
+    <t>Por que se pode dizer que o sagrado é ambíguo?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrado é ambíguo, porquanto ao mesmo tempo em que dele mantemos certa distância pelo temor que nos provoca, por ele também nos sentimos atraídos e somos seduzidos a certa intimidade.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrado é ambíguo, porquanto se trata de objetos ou coisas que sempre trazem ambiguidade para aqueles que procuram entendê-lo.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrado é ambíguo porque pode estar no altar tanto do cristão, do budista, do muçulmano ou de qualquer outra religião.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sagrando, na realidade, não é ambíguo.
+</t>
+  </si>
+  <si>
+    <t>Psicologia Geral</t>
+  </si>
+  <si>
+    <t>A importância de Emil Kraepelin para o estudo das psicopatologias deve-se a que?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>As doenças mentais podem ser definidas a partir de desordens psíquicas em relação ao comportamento convencionado como padrão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Que a esquizofrenia não é uma coisa só, mas sim uma síndrome que supõe uma fragmentação e desorganização do funcionamento psicológico.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foi ele o responsável pela descrição e classificação dos transtornos mentais.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todas as respostas estão corretas.
+</t>
+  </si>
+  <si>
+    <t>Kurt Schneider os indivíduos do tipo “psicopatas fanáticos” são os que mais apresentam conteúdos e elementos religiosos em seu comportamento. Ele os divide em dois grupos que são:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fanáticos revolucionários e individualistas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fanático expansivos e discretos.
+</t>
+  </si>
+  <si>
+    <t>Fanáticos liberais e conservadores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fanáticos cultos e incultos.
+</t>
+  </si>
+  <si>
+    <t>São os precursores da psicologia moderna:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platão e Aristóteles.
+</t>
+  </si>
+  <si>
+    <t>Sócrates e Platão.</t>
+  </si>
+  <si>
+    <t>Aristóteles e Sócrates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma das respostas.
+</t>
+  </si>
+  <si>
+    <t>Psicopatologia pode ser entendida como:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A classificação dos transtornos mentais.
+</t>
+  </si>
+  <si>
+    <t>O estudo aplicado dos sintomas anormais demonstrados na vida do indivíduo.</t>
+  </si>
+  <si>
+    <t>Uma síndrome que aborda só um aspecto da saúde mental.</t>
+  </si>
+  <si>
+    <t>Todas as respostas estão incorretas.</t>
+  </si>
+  <si>
+    <t>Foi desenvolvida por Gerald Kleman e Myrna Weissmann nos anos 70:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Terapia Comportamental.</t>
+  </si>
+  <si>
+    <t>Terapia Cognitiva.</t>
+  </si>
+  <si>
+    <t>Terapia Familiar e de Casal.</t>
+  </si>
+  <si>
+    <t>Terapia interpessoal (TIP).</t>
+  </si>
+  <si>
+    <t>Foi quem criou os testes de inteligência estática, abrindo portas para os testes de QI do mundo moderno:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivan Pavlov.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Watson.
+</t>
+  </si>
+  <si>
+    <t>Alfred Binet.</t>
+  </si>
+  <si>
+    <t>Stanley Hall.</t>
+  </si>
+  <si>
+    <t>A quantos anos aproximadamente a psicologia é entendida como ciência?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130 anos.
+</t>
+  </si>
+  <si>
+    <t>90 anos.</t>
+  </si>
+  <si>
+    <t>100 anos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma das respostas.
+</t>
+  </si>
+  <si>
+    <t>É o conceito mais antigo da Psicologia:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanicista.
+</t>
+  </si>
+  <si>
+    <t>Organicista.</t>
+  </si>
+  <si>
+    <t>Estruturalista</t>
+  </si>
+  <si>
+    <t>Vitalista</t>
+  </si>
+  <si>
+    <t>Considerando o pensamento de Jung sobre o objetivo da religião é certo afirmar quer:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O objetivo maior da religião é  identificar-se com a psique universal.
+</t>
+  </si>
+  <si>
+    <t>O objetivo maior da religião é não submergindo a consciência num mar de esquecimento inconsciente.</t>
+  </si>
+  <si>
+    <t>O objetivo maior da religião é integrar a consciência pessoal, através de recursos supremos.</t>
+  </si>
+  <si>
+    <t>Todas as respostas estão corretas.</t>
+  </si>
+  <si>
+    <t>“Matéria e vida são da mesma essência e a análise dos elementos de um objeto animado ou inanimado nos leva à total explicação das manifestações do objeto.” Está frase deve ser associada a qual conceito:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conceito Mecanicista.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conceito Vitalista.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conceito Organicista.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhum dos Conceitos  Apontados.
+</t>
+  </si>
+  <si>
+    <t>Qual a importância da fala no método Psicanalítico adotado por Freud?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O que Freud observou é que no exercício da fala, os pacientes por vezes demonstravam inibição quanto a imagens e ideias que surgiam.</t>
+  </si>
+  <si>
+    <t>Facilita a indução a sonhos eróticos e de prazer.</t>
+  </si>
+  <si>
+    <t>É importante porque somente por meio da fala o paciente pode ser analisado.</t>
+  </si>
+  <si>
+    <t>Nenhuma das alternativas está correta.</t>
+  </si>
+  <si>
+    <t>Foi quem ampliou o conceito científico que envolvia questões de psiquiatria criminal, neuropatologia, hipnose, psicolopatologia do trabalho e psicose infantil como dementia precosíssima. Está se falando de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Freud.</t>
+  </si>
+  <si>
+    <t>Pinel.</t>
+  </si>
+  <si>
+    <t>De Sanctis.</t>
+  </si>
+  <si>
+    <t>Jung.</t>
+  </si>
+  <si>
+    <t>Os primeiros passos na direção do pensamento sobre o que poderia ser o mundo psicológico é atribuído a:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Sócrates</t>
+  </si>
+  <si>
+    <t>Platão.</t>
+  </si>
+  <si>
+    <t>Aristóteles.</t>
+  </si>
+  <si>
+    <t>Agostinho.</t>
+  </si>
+  <si>
+    <t>Tem seu fundamento nas teorias psicanalíticas da personalidade a seguinte terapia dinâmica:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Psicoterapia de Apoio.</t>
+  </si>
+  <si>
+    <t>Psicoterapia de Grupo.</t>
+  </si>
+  <si>
+    <t>Terapia Interpessoal.</t>
+  </si>
+  <si>
+    <t>Terapia comportamental.</t>
+  </si>
+  <si>
+    <t>Os fundadores da chamada psicologia experimental foram:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Wilhem Wundt , Ernst H.Weber, Gustav T. Fechner.</t>
+  </si>
+  <si>
+    <t>Pinel, Skinner e Ana Freud.</t>
+  </si>
+  <si>
+    <t>Platão, Sócrates e Aristóteles.</t>
+  </si>
+  <si>
+    <t>Nenhuma das respostas.</t>
+  </si>
+  <si>
+    <t>São Tomas de Aquino é influenciado em seu pensamento sobre essência e existência  por:  
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Sócrates.</t>
+  </si>
+  <si>
+    <t>Arquimedes</t>
+  </si>
+  <si>
+    <t>É o local em que se encontram as pulsões de vida e de morte:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>ID.</t>
+  </si>
+  <si>
+    <t>Ego.</t>
+  </si>
+  <si>
+    <t>Pré-consciente.</t>
+  </si>
+  <si>
+    <t>Consciente</t>
+  </si>
+  <si>
+    <t>Psicoterapias de apoio é apenas a que:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Está voltada primordialmente para o tratamento da depressão.</t>
+  </si>
+  <si>
+    <t>Tem como base o aprendizado como forma de entendimento da gênese dos sintomas, a manutenção e eliminação dos mesmos.</t>
+  </si>
+  <si>
+    <t>A intervenção do terapeuta é direta, funcionando como suporte, um ego auxiliar, e seu trabalho é focado na realidade atual do paciente.</t>
+  </si>
+  <si>
+    <t>São os três conceitos primordiais da psicologia:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Mecanicista, Filosofia e Estruturalista.</t>
+  </si>
+  <si>
+    <t>Organicista, Mecanicista e Vitalista.</t>
+  </si>
+  <si>
+    <t>Sensacionalista, Estruturalista, Fundamentalista.</t>
+  </si>
+  <si>
+    <t>“Essa teoria ocupa-se do ser humano como um todo e admite que qualquer evento psicológico é resultante de vários fatores e influenciam na conduta do indivíduo”. Esta frase faz parte do conceito:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Teoria Mecanicista.</t>
+  </si>
+  <si>
+    <t>Teoria Vitalista.</t>
+  </si>
+  <si>
+    <t>Teoria Organicista.</t>
+  </si>
+  <si>
+    <t>Teoria Analítica.</t>
+  </si>
+  <si>
+    <t>História e Cultura Helenística</t>
+  </si>
+  <si>
+    <t>Os gregos consideram a mensagem da cruz como loucura (1 Cor 1,22). De fato, quem poderia culpá-los, pois ninguém antes deles conhecera tão grande desenvolvimento cultural. Eles buscavam a sabedoria que traria sucesso na política, nos tribunais, na filosofia, no comércio, numa vida autárquica e, especialmente, a aprovação ou admiração de seus respectivos pares. A perspectiva de vida baseada nesses valores considera a “mensagem da cruz” uma afronta, pois a sabedoria humana considera loucura tudo o que é contrário a este modelo de vida. A “palavra da cruz” é também desprezada, pois a pessoa que Paulo proclamava havia aceitado um tipo de sofrimento e morte que eram considerados desonra e vergonha. A proclamação da “palavra da cruz” aos que buscavam honra e estima significava, portanto, uma grande afronta. Além disso, a renúncia à autarquia e a confiança posta inteiramente na ação de um “outro” significava a negação de tudo o que os gregos consideravam como caminho para o sucesso.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) Os gregos buscavam a sabedoria que traria sucesso na política, nos tribunais, na filosofia, no comércio, numa vida autárquica e, especialmente, a aprovação ou admiração de seus respectivos pares.
+( II ) A perspectiva de vida baseada nesses valores não considera a “mensagem da cruz” uma afronta, pois a sabedoria humana vê esta mensagem como adequada a este modelo de vida.
+( III ) A “palavra da cruz” é desprezada, pois a pessoa que Paulo proclamava havia aceitado um tipo de sofrimento e morte que eram considerados desonra e vergonha.
+( IV ) A renúncia à autarquia e a confiança posta na ação de um “outro” não significava a negação de tudo o que os gregos consideravam como caminho para o sucesso.
+Está correto o que se afirma em:
+Escolha uma opção</t>
+  </si>
+  <si>
+    <t>I e III apenas.</t>
+  </si>
+  <si>
+    <t>I e II apenas.</t>
+  </si>
+  <si>
+    <t>I, II e IV apenas.</t>
+  </si>
+  <si>
+    <t>II e IV apenas.</t>
+  </si>
+  <si>
+    <t>Através do processo de helenização, a língua e a cultura gregas se difundiram por todo o mundo mediterrâneo, especialmente graças às cidades fundadas por Alexandre e seus sucessores. Nestas cidades a civilização grega era implantada e se difundia pelo território ao seu derredor. O Judaísmo e o cristianismo nascente não podem ser entendidos de forma isolada do padrão cultural e religioso helenístico, mas o helenismo não pode ser visto como uma rua de mão única. A língua e a cultura gregas foram também influenciadas pelas culturas afro-asiáticas dos povos conquistados (desenvolveu-se o grego coinê, a forma da língua grega usada pela maioria da população, bem como no Novo Testamento), expandiram-se as religiões salvíficas de mistério (sincretismo de cultos afro-asiáticos com cultos greco-romanos), o Judaísmo ficou conhecido e era praticado em toda a região graças à dispersão de judeus (o que facilitou a expansão do Cristianismo).
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) O processo de helenização possibilitou a difusão da língua e a cultura gregas se difundiram por todo o mundo mediterrâneo, especialmente graças às cidades fundadas por Alexandre e seus sucessores.
+( II ) O helenismo é uma rua de mão única.
+( III ) Com o helenismo desenvolveu-se o grego coinê, a forma da língua grega usada pela maioria da população, bem como no Novo Testamento.
+( IV ) A dispersão dos judeus não facilitou o conhecimento do Judaísmo e não ajudou na expansão do Cristianismo.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>I, II e III apenas.</t>
+  </si>
+  <si>
+    <t>Um dos nomes mais conhecidos do Judaísmo fora de Israel é o de Filo, da cidade de Alexandria, um judeu que escreveu várias obras em que apresentou o Judaísmo ao mundo helênico. Filo lê a Escritura alegoricamente, associando-lhe significados que previamente não lhe diziam respeito. Ele compara a relação entre o sentido literal e o alegórico com a que existe entre o corpo e a alma, e o fato de que a alegoria quer alcançar algo invisível e mais elevado implica que este sentido não pode ser imediatamente acessível aos leitores. O intérprete experiente pode penetrar até este sentido mais elevado que Deus queria preservar do leitor comum, que fica preso no conteúdo literal. Para Filo, aqueles que “com base em pequenos indícios, conseguem entender o invisível através do visível” estão em condições de captar o sentido mais profundo das Escrituras.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) Filo, da cidade de Alexandria, escreveu várias obras em que apresentou o Judaísmo ao mundo helênico.
+( II ) A leitura alegórica da Escritura permite a Filo associar-lhe significados que previamente não lhe diziam respeito.
+( III ) Filo compara a relação entre o sentido literal e o alegórico com a que existe entre o corpo e a alma.
+( IV ) A leitura alegórica de Filo não procura apresentar o invisível através do visível.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+I, II e III apenas.
+</t>
+  </si>
+  <si>
+    <t>O exercício do senhorio de Cristo é totalmente distinto. É um senhorio que não conquista, mas reconcilia; não gera uniformidade, mas unidade. É um senhorio sem estratégias, mas com relacionamentos. Um senhorio cujo poder é exercido pelo Deus que faz a paz mediante a morte do seu próprio Filho, e não a dos seus inimigos. Na tradição judaico-cristã, a paz (shalom) é a plena harmonia que Deus estabelece na sua criação, com destaque para a justiça social, econômica e política que é a harmonia aplicada à convivência humana. Para restaurar a harmonia rompida da criação, Deus entrega Seu Filho à morte reconciliadora em benefício da criação alienada do Pai. Ou, nas palavras do próprio crucificado: “o Filho do Homem não veio para ser servido, mas para servir, e dar a sua vida em resgate de muitos” (Mc 10,45).
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) O senhorio de Cristo não significa conquista, mas reconciliação; não gera uniformidade, mas unidade.
+( II ) No senhorio de Cristo o poder é exercido pelo Deus que faz a paz mediante a morte do seu próprio Filho, e não a dos seus inimigos.
+( III ) Na tradição judaico-cristã, a paz (shalom), a plena harmonia que Deus estabelece na sua criação, não envolve a justiça social, econômica e política.
+( IV ) Para restaurar a harmonia rompida da criação, Deus entrega Seu Filho à morte reconciliadora em benefício da criação alienada do Pai.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A tecnologia de produção era precária, fortemente dependente da mão-de-obra, mas em comparação com períodos anteriores era mais adequada, na medida em que se usavam ferramentas de ferro (especialmente arados) que permitiam maior produtividade, de modo que se produzia suficientemente para a subsistência da população geral do Império. O problema maior era a distribuição desses produtos, de tal forma que os governantes romanos tinham um papel importante na distribuição do trigo como um dos meios de manter a tranquilidade nos seus domínios. Avanços mais significativos se deram na construção de estradas e aquedutos, bem como no desenvolvimento de formas mais seguras de navegação ao longo das diversas costas do Mediterrâneo. Tais avanços foram necessários em função de dois fatores principais: o comércio e a manutenção do controle militar (exércitos dependem de boas estradas para alcançar com rapidez regiões de guerra). Em parte isto nos ajuda a entender a importância do controle dos exércitos na tomada e manutenção do poder imperial. Também nos ajuda a entender a importância da pax romana (“paz romana”) como mecanismo ideológico de apoio para a manutenção da tranquilidade nos domínios imperiais.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) Embora a tecnologia de produção fosse precária, na medida em que se usavam ferramentas de ferro que permitiam maior produtividade, se produzia suficientemente para a subsistência da população geral do Império.
+( II ) A distribuição desses produtos era tranquila, não necessitando dos governantes romanos para a sua realização.
+( III ) Aconteceram avanços na construção de estradas e aquedutos e no desenvolvimento de formas mais seguras de navegação ao longo das diversas costas do Mediterrâneo.
+( IV ) A pax romana (“paz romana”) era um mecanismo ideológico de apoio para a manutenção da tranquilidade nos domínios imperiais.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>I, III e IV apenas.</t>
+  </si>
+  <si>
+    <t>O Cristianismo nasceu durante um período em que todo o mundo helenístico estava sob o domínio do Império Romano. O mundo helenístico se localizava no entorno do mar Mediterrâneo. A palavra “mediterrâneo” significa “entre terras”, e o Mar Mediterrâneo era chamado mare internum (latim). Do ponto de vista geográfico, o mundo mediterrâneo engloba três continentes: Europa, Ásia e África – o que acarreta uma grande diversidade cultural, étnica, política, econômica e religiosa. Não só o domínio imperial romano, mas, já antes dele, a conquista de partes significativas da Ásia e África por Alexandre, o Grande (séc. IV a.C.), produziu uma espécie de homogeneização cultural-religiosa através da difusão do helenismo.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) O Cristianismo nasceu durante um período em que todo o mundo helenístico estava sob o domínio do Império Romano.
+( II ) A palavra “mediterrâneo” significa “entre terras”, e o Mar Mediterrâneo era chamado mare internum.
+( III ) Do ponto de vista geográfico, o mundo mediterrâneo engloba os continentes: Europa, Ásia, África e América.
+( IV ) A conquista de partes significativas da Ásia e África por Alexandre, o Grande (séc. IV a.C.), não produziu uma espécie de homogeneização cultural-religiosa através da difusão do helenismo.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Para os saduceus, a pureza consistia na ausência, ou baixa presença, de defeitos ou máculas de tipo ritual (a presença dessas máculas definia a impureza). Havia máculas provisórias, que podiam ser eliminadas mediante sacrifícios e lavagens cerimoniais, e máculas permanentes que não podiam ser eliminadas. O critério de definição da pureza vinha da Torá sacerdotal, e aplicava ao mundo humano regras similares aplicadas ao mundo não-humano. Pessoas cuja mácula não podia ser eliminada estavam definitivamente afastadas de Deus e não poderiam participar da salvação do povo de Deus. Pessoas cuja mácula poderia ser removida deveriam se submeter às instruções sacerdotais para alcançar a purificação. Pessoas sem mácula eram aquelas que cumpriam rigorosamente as exigências da Torá sacerdotal e desfrutariam plenamente da salvação na era messiânica. Para os fariseus, que não negavam as noções de pureza sacerdotal, os sintomas mais importantes da pureza ou impureza tinham a ver com o cumprimento da Torá moral – especialmente a guarda do sábado, a ausência de contato com animais e/ou pessoas impuras, e a prática da piedade pessoal – especialmente a esmola, a oração e o jejum. Além das marcas da pureza vinculadas à ação humana, os fariseus também classificavam as pessoas em escalas de pureza conforme a sua condição física e de saúde (de modo similar à classificação dos saduceus). Assim, pessoas portadoras de deficiências físicas permanentes eram consideradas impuras (cegas, surdas, mudas, paralíticas, etc.); enquanto certas doenças mantinham as pessoas em situação de impureza até a sua cura (doenças da pele, especialmente aquelas cuja cura era desconhecida, eram as mais evidentes doenças relativas à impureza). Tanto para fariseus quanto para saduceus, as mulheres, pelo simples fato de serem mulheres, já estavam em condição pior do que os homens no quesito da pureza.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) Para os saduceus, a pureza não envolvia defeitos ou máculas de tipo ritual (a presença dessas máculas definia a impureza).
+( II ) O critério de definição da pureza dos saduceus vinha da Torá sacerdotal, e aplicava ao mundo humano regras similares aplicadas ao mundo não-humano.
+( III ) Para os fariseus, os sintomas mais importantes da pureza ou impureza tinham a ver com o cumprimento da Torá moral: a guarda do sábado, a ausência de contato com animais e/ou pessoas impuras, a prática da piedade pessoal.
+( IV ) Para fariseus e saduceus as mulheres tinham o mesmo valor que os homens no quesito da pureza.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>II e III apenas.</t>
+  </si>
+  <si>
+    <t>O dito de Jesus sobre odres novos e remendos novos é fundamental para entender o discurso do seu movimento. Não é possível criar um novo mundo sem rompermos com as amarras do velho mundo. O discurso do movimento de Jesus era um discurso de tipo profético-apocalíptico. Da profecia vem a intensa crítica contra toda forma de injustiça e dominação. Da apocalíptica vem a intensa expectativa de uma transformação radical da realidade social. De ambas vem a confiante certeza em Deus como o Senhor da história, que encaminhará essa transformação em conformidade com Sua vontade libertadora. É por isso que o tema central da mensagem de Jesus é o Reino de Deus. Jesus não prega a si mesmo como rei, fala de si mesmo como servo, como filho, como aquele que foi enviado pelo Pai para anunciar e concretizar a iminente chegada do Reino. Se Deus reina, não pode imperar a injustiça, a violência, a opressão. Se Deus reina, rompidos estão os grilhões da Lei e ativa a salvação pela graça.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) O dito de Jesus sobre odres novos e remendos novos é fundamental para entender o discurso do seu movimento, mas é possível criar um mundo novo sem rompermos com as amarras do velho mundo.
+( II ) A profecia crítica apenas pecados individuais e hipocrisia religiosa.
+( III ) A apocalíptica contém uma intensa expectativa de uma transformação radical da realidade social.
+( IV ) Jesus fala de si mesmo como servo, como filho, como aquele que foi enviado pelo Pai para anunciar e concretizar a iminente chegada do Reino.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>III e IV apenas.</t>
+  </si>
+  <si>
+    <t>Os essênios têm um papel peculiar no universo discursivo judaico, pois se constituía como uma cunha de oposição radical dentro do campo discursivo do Judaísmo Oficial. Eles não podem ser classificados exclusivamente como um grupo de resistência na medida em que não se opõem às características dominantes do discurso oficial. São, sim, um grupo de oposição, uma vez que disputa a legitimidade da liderança sacerdotal, bem como a legitimidade da interpretação da Torá – deste modo, ameaçam tanto a estabilidade política dos saduceus quanto a liderança teológica dos fariseus. Sua interpretação da Torá era peculiar, com três grandes ênfases: (a) um dualismo angelológico e moral, com características de determinismo; (b) um messianismo apocalíptico e guerreiro radical, que alimentava sonhos de libertação total da dominação imperial; (c) uma espiritualidade radical de seguimento das normas comunitárias e de afastamento da vida cotidiana, com vistas à plena consagração à vontade soberana do Senhor.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) Os essênios não podem ser classificados como um grupo de resistência na medida em que não se opõem às características dominantes do discurso oficial judaico.
+( II ) Uma das características da sua interpretação da Torá era um dualismo angelológico e moral, com características de determinismo.
+( III ) Um messianismo apocalíptico e guerreiro radical, que alimentava sonhos de libertação total da dominação imperial, não fazia parte da interpretação da Torá pelos essênios.
+( IV ) Os essênios estavam perfeitamente integrados na social e cultural judaica.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>“É sintomático e carregado de sentido que desde o início, das primeiras vezes em que a pax romana é mencionada, se fala do imperador como chefe militar. O altar da paz ao Imperador Augusto, construído no simbólico lugar do Campo de Marte, deus da guerra, na verdade dava sentido à história da violência calcada no sucesso do vencedor. Sobre ele, o holocausto que queimava a vítima totalmente e por inteiro, sublinhava o fato do preço da paz proclamada e celebrada: o sangue derramado. A pax romana, portanto, é paz querida politicamente pelo imperador e seus mais altos funcionários, e estabelecida e garantida militarmente pela intervenção das legiões. A guerra que leva à vitória forma o pressuposto do tempo feliz da paz, no qual o Imperador triunfa. E este tempo feliz continua a ser assegurado pelas legiões e suas armas. Esta paz que Roma traz é paz-de-vitória para os romanos; para os vencidos, paz de submissão. Em teoria uma relação de direito entre dois parceiros, a pax romana é na realidade uma ordem de dominação. Roma é o parceiro que, a partir de si mesmo, ordena a relação e propõe as condições que o não romano deve aceitar, confirmando sua submissão ao poderoso Império que o protegia contra os ataques de outros povos estrangeiros. Esta paz estabelecida e mantida, portanto, com meios militares, é acompanhada de rios de sangue e lágrimas de enormes dimensões. Na verdade, nesta época da história, o mundo conhecido tem paz porque “todo o orbe terrestre” é dominado por Roma.
+De acordo com essa declaração, avalie as seguintes afirmações:
+( I  ) O altar da paz ao Imperador Augusto era muito mais a história da violência calcada no sucesso do vencedor.
+( II ) A pax romana (“paz romana”) era desejada politicamente pelo imperador e seus mais altos funcionários, mas estabelecida e garantida militarmente pela intervenção das legiões.
+( III ) A pax romana (“paz romana”) era a realidade da ordem de dominação do mundo da época por Roma.
+( IV ) Os povos conquistados aceitavam amigavelmente as propostas da paz por Roma.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Grego Instrumental</t>
+  </si>
+  <si>
+    <t>Na língua portuguesa há ditongos e tritongos. Porém, quando aparecem duas ou três vogais juntas, mas estas não formam ditongo ou tritongo, utilizamos um sinal sobre uma das vogais indicando que a mesma será considerada em separado, e que as vogais não serão lidas juntas. No grego Coinê há um sinal que tem função semelhante chamado de... Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Acento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apóstrofo.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspiração.
+</t>
+  </si>
+  <si>
+    <t>Trema.</t>
+  </si>
+  <si>
+    <t>Marque a alternativa que não corresponde à verdade acerca das palavras Proclíticas e Enclíticas: Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Tanto as enclíticas quanto as proclíticas são, por regra, monossilábicas.</t>
+  </si>
+  <si>
+    <t>As proclíticas são pronunciadas junto com a palavra que sucedem.</t>
+  </si>
+  <si>
+    <t>As enclíticas podem ter uma ou duas sílabas.</t>
+  </si>
+  <si>
+    <t>As proclíticas e enclíticas nunca são pronunciadas junto com as palavras que antecedem ou sucedem.</t>
+  </si>
+  <si>
+    <t>Os modos verbais, segundo Soares, são as diferentes formas que o verbo assume para indicar a atitude de certeza, de dúvida, de suposição, de mando de quem fala em relação ao fato que anuncia. Em outras palavras, os modos verbais esclarecem como podemos usar os verbos, dependendo da significação que pretendemos dar a eles. Marque a alternativa que contem os quatro principais modos verbais no grego Coinê. Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicativo, subjuntivo, imperativo e optativo.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subjuntivo, presente, aoristo e optativo.
+</t>
+  </si>
+  <si>
+    <t>Indicativo, substantivo, imperativo e futuro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicativo, subjuntivo, perfeito e mais-que-perfeito.
+</t>
+  </si>
+  <si>
+    <t>Os acentos no Português, além da função de indicar a sílaba tônica, mudam o som das sílabas, abrindo ou fechando-os.  Na língua grega Coinê há três acentos. São eles: Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Trema, apóstrofo e grave.</t>
+  </si>
+  <si>
+    <t>Agudo, espírito e grave.</t>
+  </si>
+  <si>
+    <t>Agudo, grave e circunflexo.</t>
+  </si>
+  <si>
+    <t>Nenhuma das respostas acima está correta.</t>
+  </si>
+  <si>
+    <t>A Bíblia Sagrada é considerada uma coletânea composta de vários livros, sendo estes escritos por diversos autores, em épocas diferentes, e em línguas diferentes. Sendo assim, marque a afirmação correta a respeito da língua utilizada para a escrita do Novo Testamento:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nem todo o Novo Testamento foi escrito em grego; partes foram escritas em Aramaico, especialmente o livro de Hebreus.
+</t>
+  </si>
+  <si>
+    <t>Todo o Novo Testamento foi escrito em Grego Coinê.</t>
+  </si>
+  <si>
+    <t>Todo o Novo Testamento foi escrito em Hebraico.</t>
+  </si>
+  <si>
+    <t>É ____________ que contém o sentido primário, anterior, do verbo. Essa parte permanece 'quase' inalterada, havendo mudanças apenas quando há contrações. No geral, ele permanece igual em todas as flexões.
+Marque a alternativa que corresponde à palavra que preenche o espaço na afirmativa acima. Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A vogal temática.</t>
+  </si>
+  <si>
+    <t>O radical.</t>
+  </si>
+  <si>
+    <t>A desinência.</t>
+  </si>
+  <si>
+    <t>Assim como na Língua Portuguesa, os modos verbais gregos indicam as maneiras diferentes de um fato realizar-se. Dessa forma, por exemplo, quando damos uma ordem, estamos utilizando o modo verbal no imperativo.
+Acerca do Modo Subjuntivo, avalie as seguintes afirmações:
+1) O modo subjuntivo expressa apenas a ideia de tempo, não se preocupando se o fato é verdadeiro ou não.
+2) O modo subjuntivo é utilizado quando queremos expressar expectativa ou desejo.
+3) O modo subjuntivo é utilizado quando se fala com hesitação, dúvida ou, em alguns casos, probabilidade.
+4) No modo subjuntivo não há referência a tempo, pois a qualidade da ação é mais importante que a questão temporal.
+Marque a alternativa correta acerca do modo subjuntivo: Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>II, III e IV apenas.</t>
+  </si>
+  <si>
+    <t>I apenas.</t>
+  </si>
+  <si>
+    <t>Analise as frases: “...a pedra, ...havia sido removida” / “Jesus fez com que os discípulos entrassem no barco” / “E se ela se divorciar do marido”. Indique a alternativa que corresponde às três vozes do grego Coinê, na ordem das frases, respectivamente. Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Passiva, Média e Ativa.</t>
+  </si>
+  <si>
+    <t>Ativa, Média e Passiva.</t>
+  </si>
+  <si>
+    <t>Ativa, Passiva e Média.</t>
+  </si>
+  <si>
+    <t>Passiva, Ativa e Média.</t>
+  </si>
+  <si>
+    <t>As ________ são fonemas que se formam pela vibração das _______ vocais estimuladas pela corrente de ar que se desloca dos ________ e passa pela boca ou pelo nariz.Marque a alternativa que preenche corretamente as lacunas.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>vogais – têmporas – pulmões.</t>
+  </si>
+  <si>
+    <t>letras – pregas – ouvidos.</t>
+  </si>
+  <si>
+    <t>vogais – pregas – pulmões.</t>
+  </si>
+  <si>
+    <t>vogais – matrizes – pulmões.</t>
+  </si>
+  <si>
+    <t>No grego Coinê há duas formas verbais que tem semelhanças com os modos, mas não são classificadas como tal. Indique a alternativa que indica quais são essas duas formas verbais. Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Indicativo e subjuntivo.</t>
+  </si>
+  <si>
+    <t>Particípio e Infinitivo.</t>
+  </si>
+  <si>
+    <t>Indicativo e perfeito.</t>
+  </si>
+  <si>
+    <t>Subjuntivo e mais-que-perfeito.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -636,8 +2155,18 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF001A1E"/>
+      <name val="Poppins"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF8E662E"/>
+      <name val="Poppins"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -656,6 +2185,12 @@
         <bgColor rgb="FFE7F3F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFDC"/>
+        <bgColor rgb="FFFCEFDC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -663,7 +2198,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -689,7 +2224,13 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -746,6 +2287,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -990,7 +2535,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="18.0"/>
     <col customWidth="1" min="2" max="2" width="53.63"/>
-    <col customWidth="1" min="3" max="3" width="51.38"/>
+    <col customWidth="1" min="3" max="3" width="22.88"/>
     <col customWidth="1" min="4" max="4" width="46.0"/>
     <col customWidth="1" min="5" max="5" width="49.5"/>
     <col customWidth="1" min="6" max="6" width="29.88"/>
@@ -2341,13 +3886,27 @@
       <c r="Z32" s="5"/>
     </row>
     <row r="33">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="A33" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -2369,13 +3928,27 @@
       <c r="Z33" s="5"/>
     </row>
     <row r="34">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
+      <c r="A34" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
@@ -2397,13 +3970,27 @@
       <c r="Z34" s="5"/>
     </row>
     <row r="35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="A35" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
@@ -2425,13 +4012,27 @@
       <c r="Z35" s="5"/>
     </row>
     <row r="36">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
+      <c r="A36" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
@@ -2453,13 +4054,27 @@
       <c r="Z36" s="5"/>
     </row>
     <row r="37">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+      <c r="A37" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
@@ -2481,13 +4096,27 @@
       <c r="Z37" s="5"/>
     </row>
     <row r="38">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
+      <c r="A38" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
@@ -2509,13 +4138,27 @@
       <c r="Z38" s="5"/>
     </row>
     <row r="39">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
+      <c r="A39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
@@ -2537,13 +4180,27 @@
       <c r="Z39" s="5"/>
     </row>
     <row r="40">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
+      <c r="A40" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
@@ -2565,13 +4222,27 @@
       <c r="Z40" s="5"/>
     </row>
     <row r="41">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
+      <c r="A41" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -2593,13 +4264,27 @@
       <c r="Z41" s="5"/>
     </row>
     <row r="42">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
+      <c r="A42" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
@@ -2621,13 +4306,27 @@
       <c r="Z42" s="5"/>
     </row>
     <row r="43">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
+      <c r="A43" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
@@ -2649,13 +4348,27 @@
       <c r="Z43" s="5"/>
     </row>
     <row r="44">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
+      <c r="A44" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
@@ -2677,13 +4390,27 @@
       <c r="Z44" s="5"/>
     </row>
     <row r="45">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
+      <c r="A45" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
@@ -2705,13 +4432,27 @@
       <c r="Z45" s="5"/>
     </row>
     <row r="46">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
+      <c r="A46" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
@@ -2733,13 +4474,27 @@
       <c r="Z46" s="5"/>
     </row>
     <row r="47">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
+      <c r="A47" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
@@ -2761,13 +4516,27 @@
       <c r="Z47" s="5"/>
     </row>
     <row r="48">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
+      <c r="A48" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
@@ -2789,13 +4558,27 @@
       <c r="Z48" s="5"/>
     </row>
     <row r="49">
-      <c r="A49" s="5"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+      <c r="A49" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
@@ -2817,13 +4600,27 @@
       <c r="Z49" s="5"/>
     </row>
     <row r="50">
-      <c r="A50" s="5"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
+      <c r="A50" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
@@ -2845,13 +4642,27 @@
       <c r="Z50" s="5"/>
     </row>
     <row r="51">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
+      <c r="A51" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C51" s="6">
+        <v>80.0</v>
+      </c>
+      <c r="D51" s="6">
+        <v>90.0</v>
+      </c>
+      <c r="E51" s="6">
+        <v>50.0</v>
+      </c>
+      <c r="F51" s="6">
+        <v>70.0</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
@@ -2873,13 +4684,27 @@
       <c r="Z51" s="5"/>
     </row>
     <row r="52">
-      <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
+      <c r="A52" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
@@ -2901,13 +4726,27 @@
       <c r="Z52" s="5"/>
     </row>
     <row r="53">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
+      <c r="A53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
@@ -2929,13 +4768,27 @@
       <c r="Z53" s="5"/>
     </row>
     <row r="54">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
+      <c r="A54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
@@ -2957,13 +4810,27 @@
       <c r="Z54" s="5"/>
     </row>
     <row r="55">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
+      <c r="A55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
@@ -2985,13 +4852,27 @@
       <c r="Z55" s="5"/>
     </row>
     <row r="56">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
+      <c r="A56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
@@ -3013,13 +4894,27 @@
       <c r="Z56" s="5"/>
     </row>
     <row r="57">
-      <c r="A57" s="5"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
+      <c r="A57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
@@ -3041,13 +4936,27 @@
       <c r="Z57" s="5"/>
     </row>
     <row r="58">
-      <c r="A58" s="5"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
+      <c r="A58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
@@ -3069,13 +4978,27 @@
       <c r="Z58" s="5"/>
     </row>
     <row r="59">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
+      <c r="A59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
@@ -3097,13 +5020,27 @@
       <c r="Z59" s="5"/>
     </row>
     <row r="60">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
+      <c r="A60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
@@ -3125,13 +5062,27 @@
       <c r="Z60" s="5"/>
     </row>
     <row r="61">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
+      <c r="A61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
@@ -3153,13 +5104,27 @@
       <c r="Z61" s="5"/>
     </row>
     <row r="62">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
+      <c r="A62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
@@ -3181,13 +5146,27 @@
       <c r="Z62" s="5"/>
     </row>
     <row r="63">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
+      <c r="A63" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
@@ -3209,13 +5188,27 @@
       <c r="Z63" s="5"/>
     </row>
     <row r="64">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
+      <c r="A64" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
@@ -3237,13 +5230,27 @@
       <c r="Z64" s="5"/>
     </row>
     <row r="65">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
+      <c r="A65" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
@@ -3265,13 +5272,27 @@
       <c r="Z65" s="5"/>
     </row>
     <row r="66">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
+      <c r="A66" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
@@ -3293,13 +5314,27 @@
       <c r="Z66" s="5"/>
     </row>
     <row r="67">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
+      <c r="A67" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
@@ -3321,13 +5356,27 @@
       <c r="Z67" s="5"/>
     </row>
     <row r="68">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
+      <c r="A68" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
@@ -3349,13 +5398,27 @@
       <c r="Z68" s="5"/>
     </row>
     <row r="69">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
+      <c r="A69" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
@@ -3377,13 +5440,27 @@
       <c r="Z69" s="5"/>
     </row>
     <row r="70">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
+      <c r="A70" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
@@ -3405,13 +5482,27 @@
       <c r="Z70" s="5"/>
     </row>
     <row r="71">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
+      <c r="A71" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
@@ -3433,13 +5524,27 @@
       <c r="Z71" s="5"/>
     </row>
     <row r="72">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
+      <c r="A72" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
@@ -3461,13 +5566,27 @@
       <c r="Z72" s="5"/>
     </row>
     <row r="73">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
+      <c r="A73" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
@@ -3489,13 +5608,27 @@
       <c r="Z73" s="5"/>
     </row>
     <row r="74">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
+      <c r="A74" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
@@ -3517,13 +5650,27 @@
       <c r="Z74" s="5"/>
     </row>
     <row r="75">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
+      <c r="A75" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3545,13 +5692,27 @@
       <c r="Z75" s="5"/>
     </row>
     <row r="76">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
+      <c r="A76" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
@@ -3573,13 +5734,27 @@
       <c r="Z76" s="5"/>
     </row>
     <row r="77">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
+      <c r="A77" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
@@ -3601,13 +5776,27 @@
       <c r="Z77" s="5"/>
     </row>
     <row r="78">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
+      <c r="A78" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -3629,13 +5818,27 @@
       <c r="Z78" s="5"/>
     </row>
     <row r="79">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
+      <c r="A79" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
@@ -3657,13 +5860,27 @@
       <c r="Z79" s="5"/>
     </row>
     <row r="80">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
+      <c r="A80" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
@@ -3685,13 +5902,27 @@
       <c r="Z80" s="5"/>
     </row>
     <row r="81">
-      <c r="A81" s="5"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
+      <c r="A81" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
@@ -3713,13 +5944,27 @@
       <c r="Z81" s="5"/>
     </row>
     <row r="82">
-      <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
+      <c r="A82" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -3741,13 +5986,27 @@
       <c r="Z82" s="5"/>
     </row>
     <row r="83">
-      <c r="A83" s="5"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
+      <c r="A83" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
@@ -3769,13 +6028,27 @@
       <c r="Z83" s="5"/>
     </row>
     <row r="84">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
+      <c r="A84" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
@@ -3797,13 +6070,27 @@
       <c r="Z84" s="5"/>
     </row>
     <row r="85">
-      <c r="A85" s="5"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
+      <c r="A85" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
@@ -3825,13 +6112,27 @@
       <c r="Z85" s="5"/>
     </row>
     <row r="86">
-      <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5"/>
+      <c r="A86" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
@@ -3853,13 +6154,27 @@
       <c r="Z86" s="5"/>
     </row>
     <row r="87">
-      <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
+      <c r="A87" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
@@ -3881,13 +6196,27 @@
       <c r="Z87" s="5"/>
     </row>
     <row r="88">
-      <c r="A88" s="5"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
+      <c r="A88" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
@@ -3909,13 +6238,27 @@
       <c r="Z88" s="5"/>
     </row>
     <row r="89">
-      <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
+      <c r="A89" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
@@ -3937,13 +6280,27 @@
       <c r="Z89" s="5"/>
     </row>
     <row r="90">
-      <c r="A90" s="5"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
+      <c r="A90" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
@@ -3965,13 +6322,27 @@
       <c r="Z90" s="5"/>
     </row>
     <row r="91">
-      <c r="A91" s="5"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
+      <c r="A91" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
@@ -3993,13 +6364,27 @@
       <c r="Z91" s="5"/>
     </row>
     <row r="92">
-      <c r="A92" s="5"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
+      <c r="A92" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
@@ -4021,13 +6406,27 @@
       <c r="Z92" s="5"/>
     </row>
     <row r="93">
-      <c r="A93" s="5"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
+      <c r="A93" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
@@ -4049,13 +6448,27 @@
       <c r="Z93" s="5"/>
     </row>
     <row r="94">
-      <c r="A94" s="5"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="5"/>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
+      <c r="A94" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
@@ -4077,13 +6490,27 @@
       <c r="Z94" s="5"/>
     </row>
     <row r="95">
-      <c r="A95" s="5"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
+      <c r="A95" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
@@ -4105,13 +6532,27 @@
       <c r="Z95" s="5"/>
     </row>
     <row r="96">
-      <c r="A96" s="5"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
+      <c r="A96" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
@@ -4133,13 +6574,27 @@
       <c r="Z96" s="5"/>
     </row>
     <row r="97">
-      <c r="A97" s="5"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
+      <c r="A97" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
@@ -4161,13 +6616,27 @@
       <c r="Z97" s="5"/>
     </row>
     <row r="98">
-      <c r="A98" s="5"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
+      <c r="A98" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
@@ -4189,13 +6658,27 @@
       <c r="Z98" s="5"/>
     </row>
     <row r="99">
-      <c r="A99" s="5"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
+      <c r="A99" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
@@ -4217,13 +6700,27 @@
       <c r="Z99" s="5"/>
     </row>
     <row r="100">
-      <c r="A100" s="5"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
+      <c r="A100" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
@@ -4245,13 +6742,27 @@
       <c r="Z100" s="5"/>
     </row>
     <row r="101">
-      <c r="A101" s="5"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
+      <c r="A101" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
@@ -4273,13 +6784,27 @@
       <c r="Z101" s="5"/>
     </row>
     <row r="102">
-      <c r="A102" s="5"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="5"/>
-      <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
-      <c r="G102" s="5"/>
+      <c r="A102" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
@@ -4301,13 +6826,27 @@
       <c r="Z102" s="5"/>
     </row>
     <row r="103">
-      <c r="A103" s="5"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-      <c r="G103" s="5"/>
+      <c r="A103" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
@@ -4329,13 +6868,27 @@
       <c r="Z103" s="5"/>
     </row>
     <row r="104">
-      <c r="A104" s="5"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
+      <c r="A104" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
@@ -4357,13 +6910,27 @@
       <c r="Z104" s="5"/>
     </row>
     <row r="105">
-      <c r="A105" s="5"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="5"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
+      <c r="A105" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
@@ -4385,13 +6952,27 @@
       <c r="Z105" s="5"/>
     </row>
     <row r="106">
-      <c r="A106" s="5"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
+      <c r="A106" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
@@ -4413,13 +6994,27 @@
       <c r="Z106" s="5"/>
     </row>
     <row r="107">
-      <c r="A107" s="5"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
-      <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-      <c r="G107" s="5"/>
+      <c r="A107" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
@@ -4441,13 +7036,27 @@
       <c r="Z107" s="5"/>
     </row>
     <row r="108">
-      <c r="A108" s="5"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-      <c r="G108" s="5"/>
+      <c r="A108" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
@@ -4469,13 +7078,27 @@
       <c r="Z108" s="5"/>
     </row>
     <row r="109">
-      <c r="A109" s="5"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-      <c r="G109" s="5"/>
+      <c r="A109" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
@@ -4497,13 +7120,27 @@
       <c r="Z109" s="5"/>
     </row>
     <row r="110">
-      <c r="A110" s="5"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="5"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-      <c r="G110" s="5"/>
+      <c r="A110" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
@@ -4525,13 +7162,27 @@
       <c r="Z110" s="5"/>
     </row>
     <row r="111">
-      <c r="A111" s="5"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-      <c r="G111" s="5"/>
+      <c r="A111" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
@@ -4553,13 +7204,27 @@
       <c r="Z111" s="5"/>
     </row>
     <row r="112">
-      <c r="A112" s="5"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-      <c r="G112" s="5"/>
+      <c r="A112" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
@@ -4581,13 +7246,27 @@
       <c r="Z112" s="5"/>
     </row>
     <row r="113">
-      <c r="A113" s="5"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
-      <c r="G113" s="5"/>
+      <c r="A113" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
@@ -4609,13 +7288,27 @@
       <c r="Z113" s="5"/>
     </row>
     <row r="114">
-      <c r="A114" s="5"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
+      <c r="A114" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
@@ -4637,13 +7330,27 @@
       <c r="Z114" s="5"/>
     </row>
     <row r="115">
-      <c r="A115" s="5"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
-      <c r="G115" s="5"/>
+      <c r="A115" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
@@ -4665,13 +7372,27 @@
       <c r="Z115" s="5"/>
     </row>
     <row r="116">
-      <c r="A116" s="5"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-      <c r="G116" s="5"/>
+      <c r="A116" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
@@ -4693,13 +7414,27 @@
       <c r="Z116" s="5"/>
     </row>
     <row r="117">
-      <c r="A117" s="5"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
-      <c r="G117" s="5"/>
+      <c r="A117" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
@@ -4721,13 +7456,27 @@
       <c r="Z117" s="5"/>
     </row>
     <row r="118">
-      <c r="A118" s="5"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="5"/>
-      <c r="D118" s="5"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="5"/>
-      <c r="G118" s="5"/>
+      <c r="A118" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
@@ -4749,13 +7498,27 @@
       <c r="Z118" s="5"/>
     </row>
     <row r="119">
-      <c r="A119" s="5"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
-      <c r="G119" s="5"/>
+      <c r="A119" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
@@ -4777,13 +7540,27 @@
       <c r="Z119" s="5"/>
     </row>
     <row r="120">
-      <c r="A120" s="5"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="5"/>
-      <c r="G120" s="5"/>
+      <c r="A120" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
@@ -4805,13 +7582,27 @@
       <c r="Z120" s="5"/>
     </row>
     <row r="121">
-      <c r="A121" s="5"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="5"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
+      <c r="A121" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
@@ -4833,13 +7624,27 @@
       <c r="Z121" s="5"/>
     </row>
     <row r="122">
-      <c r="A122" s="5"/>
-      <c r="B122" s="5"/>
-      <c r="C122" s="5"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
-      <c r="G122" s="5"/>
+      <c r="A122" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
@@ -4861,13 +7666,27 @@
       <c r="Z122" s="5"/>
     </row>
     <row r="123">
-      <c r="A123" s="5"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
-      <c r="D123" s="5"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="5"/>
-      <c r="G123" s="5"/>
+      <c r="A123" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
@@ -4889,13 +7708,27 @@
       <c r="Z123" s="5"/>
     </row>
     <row r="124">
-      <c r="A124" s="5"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="5"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="5"/>
-      <c r="G124" s="5"/>
+      <c r="A124" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
@@ -4917,13 +7750,27 @@
       <c r="Z124" s="5"/>
     </row>
     <row r="125">
-      <c r="A125" s="5"/>
-      <c r="B125" s="5"/>
-      <c r="C125" s="5"/>
-      <c r="D125" s="5"/>
-      <c r="E125" s="5"/>
-      <c r="F125" s="5"/>
-      <c r="G125" s="5"/>
+      <c r="A125" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
@@ -4945,13 +7792,27 @@
       <c r="Z125" s="5"/>
     </row>
     <row r="126">
-      <c r="A126" s="5"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="5"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="5"/>
-      <c r="G126" s="5"/>
+      <c r="A126" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
@@ -4973,13 +7834,27 @@
       <c r="Z126" s="5"/>
     </row>
     <row r="127">
-      <c r="A127" s="5"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="5"/>
-      <c r="G127" s="5"/>
+      <c r="A127" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="G127" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
@@ -5001,13 +7876,27 @@
       <c r="Z127" s="5"/>
     </row>
     <row r="128">
-      <c r="A128" s="5"/>
-      <c r="B128" s="5"/>
-      <c r="C128" s="5"/>
-      <c r="D128" s="5"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="5"/>
-      <c r="G128" s="5"/>
+      <c r="A128" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="G128" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
@@ -5029,13 +7918,27 @@
       <c r="Z128" s="5"/>
     </row>
     <row r="129">
-      <c r="A129" s="5"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="5"/>
-      <c r="D129" s="5"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="5"/>
-      <c r="G129" s="5"/>
+      <c r="A129" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
@@ -5057,13 +7960,27 @@
       <c r="Z129" s="5"/>
     </row>
     <row r="130">
-      <c r="A130" s="5"/>
-      <c r="B130" s="5"/>
-      <c r="C130" s="5"/>
-      <c r="D130" s="5"/>
-      <c r="E130" s="5"/>
-      <c r="F130" s="5"/>
-      <c r="G130" s="5"/>
+      <c r="A130" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="G130" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
@@ -5085,13 +8002,27 @@
       <c r="Z130" s="5"/>
     </row>
     <row r="131">
-      <c r="A131" s="5"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="5"/>
-      <c r="D131" s="5"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="5"/>
-      <c r="G131" s="5"/>
+      <c r="A131" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
@@ -5113,13 +8044,27 @@
       <c r="Z131" s="5"/>
     </row>
     <row r="132">
-      <c r="A132" s="5"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="5"/>
-      <c r="D132" s="5"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="5"/>
-      <c r="G132" s="5"/>
+      <c r="A132" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>

--- a/Simulados Faculdade.xlsx
+++ b/Simulados Faculdade.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="1102">
   <si>
     <t>Matéria</t>
   </si>
@@ -2125,6 +2125,1917 @@
   </si>
   <si>
     <t>Subjuntivo e mais-que-perfeito.</t>
+  </si>
+  <si>
+    <t>Um dos cinco casos do substantivo grego indica o sujeito ou, de outra maneira, o seu atributo. O referido caso é: Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nominativo.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genitivo.
+</t>
+  </si>
+  <si>
+    <t>Vocativo</t>
+  </si>
+  <si>
+    <t>Dativo</t>
+  </si>
+  <si>
+    <t>Os artigos gregos são ὁ, ἡ e τό, respectivamente masculino, feminino e neutro. Pelo número de vezes que são utilizados no Novo Testamento, 19.904 vezes, é bem provável que não haja nenhuma linha do texto bíblico sem que apareça um artigo. Por essa razão, entre outras, a ação dos artigos na oração é tida como muito importante pois...
+De acordo com a declaração acima, avalie as seguintes afirmações acerca do artigo:
+I) Empresta seu significado ao objeto a quem qualifica.
+II) Mesmo que o artigo seja omitido, as preposições, pronomes possessivos e demonstrativos, e o caso genitivo fazem também com que uma palavra seja definida.
+III) A função do artigo é assinalar um objeto ou chamar a atenção para ele.
+IV) Sempre que o artigo aparece, o objeto é definido.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+I, III, IV apenas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I e II apenas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I, II e III apenas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II, III e IV apenas.
+</t>
+  </si>
+  <si>
+    <t>O período denominado Formativo da língua Grega utilizada no Novo Testamento compreendeu...
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entre 1500 até 900 a.C.
+</t>
+  </si>
+  <si>
+    <t>Entre 3200 até 1500 a.C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entre 330 até 1453 d.C.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma das respostas acima está correta.
+</t>
+  </si>
+  <si>
+    <t>O tempo verbal utilizado na língua grega para descrever as ações de Jesus e seus discípulos é o mais utilizado para narrativas, pois descreve a ação no passado, mas ainda não finalizada. A esse tempo verbal chamamos: Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presente.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futuro.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imperfeito.
+</t>
+  </si>
+  <si>
+    <t>A sílaba é a menor unidade sonora de uma palavra, é um som. Para a formação da sílaba escrita utilizamos letras, as quais chamamos consoantes e vogais. Marque a alternativa correta nas afirmações a seguir:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O núcleo de uma sílaba é a vogal.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De uma sílaba ou da junção de duas ou mais obtemos uma palavra.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">É possível produzir uma sílaba através da emissão de um único som.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todas as respostas anteriores estão corretas.
+</t>
+  </si>
+  <si>
+    <t>Os sinais de pontuação de uma língua se prestam para pausar e reproduzir entonações de fala. Na língua grega Coinê há quatro sinais gráficos de pontuação. São eles: Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponto final, vírgula, ponto alto e ponto e vírgula.
+</t>
+  </si>
+  <si>
+    <t>Ponto final, vírgula, ponto alto e ponto e vírgula.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponto final, vírgula, exclamação e interrogação.
+</t>
+  </si>
+  <si>
+    <t>Todas as alternativas anteriores estão corretas.</t>
+  </si>
+  <si>
+    <t>Avalie as afirmativas abaixo acerca do modo subjuntivo e marque a alternativa que lhe parecer correta:
+1)  O modo Subjuntivo tem maneiras especiais de expressar ideias no Novo Testamento como propósito e fim, exortações, proibições, negações enfáticas e perguntas deliberativas.
+2) A flexão presente do Subjuntivo é formado pelas terminações do presente do Indicativo, voz ativa, com vogais temáticas alongadas, acrescidas de aspiração branda e acento circunflexo.
+3) A principal característica na formação do subjuntivo é a utilização de uma vogal temática alongada entre o radical e a terminação.
+4) Quando falamos com hesitação ou dúvida, utilizamos o modo verbal denominado subjuntivo.
+Marque a alternativa correta acerca do modo subjuntivo: Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>I e IV apenas.</t>
+  </si>
+  <si>
+    <t>Todas as afirmativas acima estão corretas.</t>
+  </si>
+  <si>
+    <t>O período denominado Clássico da língua Grega Coinê compreendeu...
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entre 330 a.C. até 330 d.C.
+</t>
+  </si>
+  <si>
+    <t>Entre 900 até 330 a.C.</t>
+  </si>
+  <si>
+    <t>Entre 900 a.C. até 330 d.C.</t>
+  </si>
+  <si>
+    <t>Nenhuma das respostas acima.</t>
+  </si>
+  <si>
+    <t>Os substantivos gregos, em se tratando do número, podem ser flexionados em: Apenas uma das respostas está correta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Singular, plural e dual.</t>
+  </si>
+  <si>
+    <t>Singular e plural, apenas.</t>
+  </si>
+  <si>
+    <t>Singular, plural e neutro.</t>
+  </si>
+  <si>
+    <t>O período denominado Bizantino da língua Grega Coinê compreendeu...
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Entre 330 a.C. até 823 d.C.</t>
+  </si>
+  <si>
+    <t>Entre 330 a.C. até 330 d.C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma das respostas acima está correta.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">História e Cultura de Israel
+</t>
+  </si>
+  <si>
+    <t>Quais seriam as fortes razões para o desejo por um Rei?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Ameaças filisteias, proteção e esperança de serem julgados por bom juiz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O entendimento de que isso era uma exigência da lei e deveria ser cumprida por Samuel.
+</t>
+  </si>
+  <si>
+    <t>Equiparar-se às demais nações adotando seus sistemas de governo e religioso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estabelecer a dinastia de Samuel por meio do governo de seus filhos.
+</t>
+  </si>
+  <si>
+    <t>Os projetos monocêntricos de resistência no período babilônico foram incorporados em grupos específicos, os quais foram identificados como:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesus, Maria e José.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fariseus, escribas e essênios.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escribas, sacerdotes herdeiros do sacerdócio jerusalemita e zelotas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma opção está correta.
+</t>
+  </si>
+  <si>
+    <t>Nas concepções essencialistas, a identidade é compreendida como:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algo permanente, fixo, estável, às vezes marcada como identidade-em-si e para-si.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algo flexível e passível de reflexão e mudança.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como algo externo ao elemento identificado e relacionado à ele por meras características.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma das afirmativas é verdadeira.
+</t>
+  </si>
+  <si>
+    <t>A fragmentação da identidade estatal monocêntrica judaica se refere a qual processo histórico do reino de Judá?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Extinção do reino de Judá mediante a conquista babilônica e da pluralização dos discursos identitários que se deu em função dessa extinção</t>
+  </si>
+  <si>
+    <t>Extinção do reino de Israel por meio da conquista assíria e a consequente desidentificação dos seus membros com a herança abraâmica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extinção do reino de Judá por meio da conquista grega e da concentração dos discursos identitários como consequência.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extinção do reino de Judá por meio da conquista assíria e a pluralização dos discursos identitários como consequência.
+</t>
+  </si>
+  <si>
+    <t>No processo originário de constituição do povo israelita é possível afirmar:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não houve um centro político, social, territorial, nem religioso; assim como não havia claras fronteiras étnicas e nacionais.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foram desde cedo estabelecidas bases governamentais de um sistema monárquico.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não houve um centro religioso, nem político, mas havia uma homogeneidade cultural e étnica que identificava a nação.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houve um centro político, social, territorial, religioso.
+</t>
+  </si>
+  <si>
+    <t>É correto afirmar sobre a dimensão histórica da Identidade:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procura dar conta das permanências, transformações e desaparecimentos de identidades ou etnicidades.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se ocupa muito mais das análises conceituais e filosóficas do termo.
+</t>
+  </si>
+  <si>
+    <t>Analisa as questões relacionadas à linguagem da memória cultural.</t>
+  </si>
+  <si>
+    <t>Nenhuma das afirmativas se aplica ao enunciado.</t>
+  </si>
+  <si>
+    <t>A nova sociedade proposta pelo movimento deuteronomista consistia de normas relativas aos seguintes elementos da sociedade judaica, menos uma:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O calendário litúrgico.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As instruções cúlticas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O exercício das funções de governo (profeta e sacerdote), juntamente com a descrição do papel dos levitas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A expectativa de um profeta com características messiânicas.
+</t>
+  </si>
+  <si>
+    <t>A divisão de Israel entre Reino de Norte e Reino do sul se dá no reinado de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Salomão</t>
+  </si>
+  <si>
+    <t>Davi.</t>
+  </si>
+  <si>
+    <t>Josias.</t>
+  </si>
+  <si>
+    <t>Roboão.</t>
+  </si>
+  <si>
+    <t>Qual o maior risco de uma conceituação de “Identidade”:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torná-lo tão intenso e plural que seja impossível de operacionalização.
+</t>
+  </si>
+  <si>
+    <t>Torná-lo restrito aos estudos filosóficos.</t>
+  </si>
+  <si>
+    <t>Não torná-lo possível de uso no estudo da Histórica Cultural.</t>
+  </si>
+  <si>
+    <t>Podemos mencionar como os principais componentes teológicos do processo de construção da identidade estatal monocêntrica, que encontra seu clímax na segunda metade do século VIII a. C. e início do VII:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O saulismo e a unificação do reino de Israel.</t>
+  </si>
+  <si>
+    <t>O davidismo; a inviolabilidade de Sião; o reinado de YHWH mediado pelo rei davídico.</t>
+  </si>
+  <si>
+    <t>O retorno à lei e o estabelecimento da monarquia como comprovação disso.</t>
+  </si>
+  <si>
+    <t>A permanência do sistema dos juízes e rejeição da monarquia.</t>
+  </si>
+  <si>
+    <t>Não houve um centro político, social, territorial, nem religioso; assim como não havia claras fronteiras étnicas e nacionais.</t>
+  </si>
+  <si>
+    <t>Foram desde cedo estabelecidas bases governamentais de um sistema monárquico.</t>
+  </si>
+  <si>
+    <t>Não houve um centro religioso, nem político, mas havia uma homogeneidade cultural e étnica que identificava a nação.</t>
+  </si>
+  <si>
+    <t>Nenhuma correta.</t>
+  </si>
+  <si>
+    <t>Em relação à transição para um sistema monárquico em Israel, podemos mencionar como uma de suas principais dificuldades de consolidação:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A falta de reis para ocupar os novos papéis de governança.</t>
+  </si>
+  <si>
+    <t>A aplicação da ordenança da lei de estabelecimento da monarquia.</t>
+  </si>
+  <si>
+    <t>A aceitação da legitimidade dos reis pela população.</t>
+  </si>
+  <si>
+    <t>A ausência de um sistema tributário que desse sustentabilidade para a máquina do Estado.</t>
+  </si>
+  <si>
+    <t>É correto afirmar que como mecanismo básico de construção da identidade a diferenciação é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O processo mediante o qual um grupo social constrói discursivamente os seus outros, define o “eles” em contraposição ao “nós”, se dissocia de um conjunto de representações, de um discurso a respeito do outro.</t>
+  </si>
+  <si>
+    <t>O mecanismo mediante o qual um grupo social constrói a sua auto-imagem, pelo que se associa a um conjunto de representações, a um discurso a respeito de si mesmo.</t>
+  </si>
+  <si>
+    <t>Essencialista e rejeita sistemas classificatórios como modos pelo qual também se faz.</t>
+  </si>
+  <si>
+    <t>Nenhuma das afirmativas é verdadeira.</t>
+  </si>
+  <si>
+    <t>Os temas que constituem o projeto da nova sociedade conforme o movimento deuteronomista são os alistados abaixo, exceto:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>As ofertas de dízimos e primogênitos.</t>
+  </si>
+  <si>
+    <t>O perdão de dívidas.</t>
+  </si>
+  <si>
+    <t>A libertação de escravos hebreus.</t>
+  </si>
+  <si>
+    <t>A retomada dos empréstimos ao necessitado no sexto ano do ciclo sabático.</t>
+  </si>
+  <si>
+    <t>A fase judaica de consolidação e rompimento da identidade étnico-religiosa monocêntrica é localizada:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>No Período persa.</t>
+  </si>
+  <si>
+    <t>No período helenístico.</t>
+  </si>
+  <si>
+    <t>No período Babilônico.</t>
+  </si>
+  <si>
+    <t>No período patriarcal.</t>
+  </si>
+  <si>
+    <t>Esta nova identidade apontada no texto (“Por identidade étnico-religiosa monocêntrica, viso descrever a nova articulação da identidade israelita, durante o processo de reorganização de Judá como uma província do Império Persa, Yehud”), refere-se ao período de Israel:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>De estabelecimento da monarquia com Davi e Salomão.</t>
+  </si>
+  <si>
+    <t>De exílio babilônico.</t>
+  </si>
+  <si>
+    <t>De pós-exílio, retorno e reconstrução de Jerusalém.</t>
+  </si>
+  <si>
+    <t>Dos patriarcas.</t>
+  </si>
+  <si>
+    <t>Fazia parte do projeto do movimento deuteronomista:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Construir uma nova sociedade sob um novo tipo de rei.
+</t>
+  </si>
+  <si>
+    <t>Refazer a Lei de Moisés e construir uma nova sociedade.</t>
+  </si>
+  <si>
+    <t>Eleger um novo tipo de rei fora da linhagem davídica.</t>
+  </si>
+  <si>
+    <t>Nenhuma está correta.</t>
+  </si>
+  <si>
+    <t>“A exclusão das múltiplas divindades então adoradas e a concentração da fé em YHWH aparecia como um quase suicídio religioso”. Essa afirmação descreve que tipo de grupo de resistência na sociedade israelita?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Grupo estatal monárquico.</t>
+  </si>
+  <si>
+    <t>Grupo rural popular.</t>
+  </si>
+  <si>
+    <t>Grupo sacerdotal litúrgico.</t>
+  </si>
+  <si>
+    <t>Grupo comercial urbano.</t>
+  </si>
+  <si>
+    <t>A Monarquia era outra possibilidade de pensar as relações sociais. Isso geraria reformulações. Quais?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Novas dinâmicas de poder entre rei-povo; cidade-campo.</t>
+  </si>
+  <si>
+    <t>A manutenção do sistema vigente de relações sob a novidade de uma monarquia.</t>
+  </si>
+  <si>
+    <t>A mudança nas relações internacionais de Israel e a manutenção da forma das relações internas da nação.</t>
+  </si>
+  <si>
+    <t>A principal norma do chamado Código Deuteronômico é a relativa ao culto sacrificial, que só pode ser realizado no lugar escolhido por YHWH. O movimento deuteronomista ressignifica o culto do seguinte modo, exceto:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Um lugar central para o culto sacrificial.</t>
+  </si>
+  <si>
+    <t>Cabe ao movimento deuteronômico a indicação do lugar de culto a YHWH.</t>
+  </si>
+  <si>
+    <t>Combate a baalização do culto a YHWH.</t>
+  </si>
+  <si>
+    <t>Faz com que Israel aceite as outra divindades.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma das afirmativas é verdadeira.
+</t>
+  </si>
+  <si>
+    <t>Dentre os elementos que descrevem a fidelidade inegociável a YHWH, assinale o único que está correto.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Qualquer responsável pelo desvio da adoração exclusiva a YHWH deveria ser expulso.</t>
+  </si>
+  <si>
+    <t>Foi um mecanismo de defesa e resistência contra a ameaça conjunta da identidade estatal monocêntrica e do imperialismo assírio.</t>
+  </si>
+  <si>
+    <t>Descreve o conflito judaico-israelita.</t>
+  </si>
+  <si>
+    <t>Estratégia inclusivista na construção da identidade por este grupo em Judá, a fim de inserir todos no culto de YHWH.</t>
+  </si>
+  <si>
+    <t>Na literatura profética o tema dominante para avaliar a vida do povo e do reinado é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O cumprimento da aliança entre YHWH e seu povo, mediante a justiça social.</t>
+  </si>
+  <si>
+    <t>O cumprimento da aliança entre YHWH e seu povo, mediante a obediência à Torá.</t>
+  </si>
+  <si>
+    <t>O cumprimento da aliança entre YHWH e seu povo, mediante a oração.</t>
+  </si>
+  <si>
+    <t>O cumprimento da aliança entre YHWH e seu povo, mediante a santificação.</t>
+  </si>
+  <si>
+    <t>Em termos concretos, a mudança para a monarquia concretizava:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Uma ampla reformulação das relações de poder entre governo e povo, entre cidades e campo.</t>
+  </si>
+  <si>
+    <t>A adoção de novas políticas para a manutenção das relações vigentes entre cidades e campo.</t>
+  </si>
+  <si>
+    <t>Assmann relaciona seis características principais da formação da memória cultural, entre elas estão:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O lugar social da identidade, a capacidade de reconstrução, a organização desse conhecimento e a reflexividade.</t>
+  </si>
+  <si>
+    <t>O lugar social da identidade, o abandono do passado e a individualização do conhecimento.</t>
+  </si>
+  <si>
+    <t>A capacidade de reconstrução, a individualização do conhecimento e ausência de reflexividade.</t>
+  </si>
+  <si>
+    <t>A capacidade de reconstrução, o abandono do passado conhecimento e ausência de reflexividade.</t>
+  </si>
+  <si>
+    <t>O Reino do Norte, chamado de Israel e tendo como capital Samaria, foi destruído pelo seguinte império:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Babilônios.</t>
+  </si>
+  <si>
+    <t>Assírios.</t>
+  </si>
+  <si>
+    <t>Gregos.</t>
+  </si>
+  <si>
+    <t>Romanos.</t>
+  </si>
+  <si>
+    <t>O livro do Deuteronômio é caracterizado como:
+I. Síntese da reflexão identitária deuteronomista em Judá no período da dominação persa.
+II. Fruto de um amplo processo de escrita e editoração, iniciado sob a dominação assíria.
+III. Assumido, ressignificado e ampliado por escribas e demais intelectuais judaítas.
+IV. Finalizado no período do Judaísmo do Segundo Templo, no século I da Era Cristã.
+Acerca das afirmações acima, assinale a sequência correta:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>I-III-IV.</t>
+  </si>
+  <si>
+    <t>I-II-III.</t>
+  </si>
+  <si>
+    <t>II-III-IV.</t>
+  </si>
+  <si>
+    <t>I-II-IV.</t>
+  </si>
+  <si>
+    <t>O pedido de um rei feito pelos anciãos de Israel, aprovado por Deus e realizado em Saul e posteriormente em Davi, tinha como possíveis razões:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Cansados das ameaças filistéias queriam um rei que os protegesse e governasse sobre eles, uma espécie de líder e protetor militar, bem como um bom juiz.</t>
+  </si>
+  <si>
+    <t>O entendimento de que isso era uma exigência da lei e deveria ser cumprida por Samuel.</t>
+  </si>
+  <si>
+    <t>Estabelecer a dinastia de Samuel por meio do governo de seus filhos.</t>
+  </si>
+  <si>
+    <t>Os principais fatores denunciados pelos profetas que levaram à destruição do Reino do Norte foram:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Idolatria, injustiça e falta de estabilidade no Estado.</t>
+  </si>
+  <si>
+    <t>Fidelidade à YHWH e cumprimento da aliança.</t>
+  </si>
+  <si>
+    <t>Estabelecimento da dinastia davídica, mas com prática da idolatria e da injustiça.</t>
+  </si>
+  <si>
+    <t>Estabelecimento da dinastia de Jeroboão, mas com políticas injustas.</t>
+  </si>
+  <si>
+    <t>A Obra Histórica Deuteronomista (OHD = Josué, Juízes, Samuel &amp; Reis) descreve vários reinados de Judá e Israel sob um critério fundamental de avaliação. Este seria:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A adoração a outros deuses, ou, a falha dos profetas em fazer valer a exclusividade da adoração de YHWH.</t>
+  </si>
+  <si>
+    <t>A adoração a outros deuses, ou, a falha dos sacerdotes em fazer valer a exclusividade da adoração de YHWH.</t>
+  </si>
+  <si>
+    <t>Fazer valer a exclusividade da adoração de YHWH.</t>
+  </si>
+  <si>
+    <t>A adoração a Baal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Literatura Joanina
+</t>
+  </si>
+  <si>
+    <t>Outra característica joanina é sua linguagem irônica, especialmente em cenas com seus adversários, os quais são por vezes expostos ao ridículo ou revelam sua incapacidade de entender as palavras de Jesus. Cite um exemplo onde isso acontece.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>No capítulo 1, porque mostra a luz recebendo rejeição.</t>
+  </si>
+  <si>
+    <t>No discurso sobre o Espírito Santo, porque não deixa ninguém aceitá-lo facilmente</t>
+  </si>
+  <si>
+    <t>No cap. 9, porque o legalismo e a religião nos modelos do lideres religiosos são ridicularizados.</t>
+  </si>
+  <si>
+    <t>No capítulo 2, onde água se transforma em vinho. Ou seja, não dá para ficar numa festa judaica só com água.</t>
+  </si>
+  <si>
+    <t>O Montanismo, movimento sectário do séc. II, foi combatido por um presbítero romano chamado Gaio. Para Gaio, quem seria o autor do Evangelho de João e do Apocalipse?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>João, filho de Zebedeu.</t>
+  </si>
+  <si>
+    <t>Cerinto o gnóstico.</t>
+  </si>
+  <si>
+    <t>Paulo, o apóstolo.</t>
+  </si>
+  <si>
+    <t>Nenhuma das opções.</t>
+  </si>
+  <si>
+    <t>Muitas foram as pesquisas sobre o Quarto Evangelho. Entre elas, encontramos as produzidas por Bultmann. Qual das opções abaixo apresenta alguma de suas perspectivas sobre Jo?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Segundo a perspectiva de Bultmanniana o quarto evangelho era a junção de fontes pré-joaninas. Assim, para redigir seu texto o evangelista dispunha de um relato da paixão, de um conjunto de fontes dos sinais, e de ditos (logia) reelaborados pelo autor nos discursos. Ainda, depois, a obra foi, segundo sua hipótese, retomada e aprofundada pela escola joanina.</t>
+  </si>
+  <si>
+    <t>Jo seria uma unidade literária sem qualquer fonte ou junção de tradições.</t>
+  </si>
+  <si>
+    <t>O autor seria o discípulo amado e juntamente com ele a comunidade joanina escreveu, inclusive, o Apocalipse.</t>
+  </si>
+  <si>
+    <t>Todas as afirmações acima estão corretas.</t>
+  </si>
+  <si>
+    <t>Seguindo algumas pesquisas, como os gregos entraram na comunidade joanina?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Através das viúvas pobres ajudadas pelos diáconos.</t>
+  </si>
+  <si>
+    <t>Com a abertura da comunidade a peripatéticos gregos.</t>
+  </si>
+  <si>
+    <t>Depois da decepção de João com os judeus, ele vai a Roma e ganha alguns gregos para a comunidade.</t>
+  </si>
+  <si>
+    <t>O distanciamento com o judaísmo abre a porta para a entrada de gregos, cuja conversão era vista como cumprimento dos planos de Deus (Jo 12.20-23).</t>
+  </si>
+  <si>
+    <t>1Jo 2.19-20 fala a respeito de um episódio na história da comunidade joanina pós-evangelho. O que seria?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A alegria de receberem juntos à comunidade dos Batistas entre os irmãos.</t>
+  </si>
+  <si>
+    <t>A separação de um grupo que possuía ideias diferentes a respeito de temas cristológicos. Eles são conhecidos como separatistas.</t>
+  </si>
+  <si>
+    <t>A discórdia entre os gnósticos que desejavam novas perspectivas encarnacionistas, as quais não aceitavam o Verbo.</t>
+  </si>
+  <si>
+    <t>Uma disputa sobre o fim dos tempos.</t>
+  </si>
+  <si>
+    <t>Em relação a estrutura e forma literária, 3Jo tem quais características?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">É uma exortação parenêtica com características apocalípticas.
+</t>
+  </si>
+  <si>
+    <t>Um evangelho com traços parecidos com as Vidas dos Césares.</t>
+  </si>
+  <si>
+    <t>Uma carta universal caótica e sem qualquer forma.</t>
+  </si>
+  <si>
+    <t>Assim como 2Jo, a terceira epístola é uma típica carta, com características estruturais parecidas às cartas greco-romanas. Ela possui uma forma introdutória (1-2), com desejo de saúde; uma expressão transicional de alegria.</t>
+  </si>
+  <si>
+    <t>Leia com atenção. “Esses são aquele judeus cristãos que permaneceram na sinagoga, recusando-se a admitir publicamente a fé joanina. Esse podem ser representados pelos pais do cego de Jo 9. Acreditavam que poderiam manter a fé em Jesus sem romper como a sinagoga. Para os joaninos, eles eram mais discípulos de Moisés do que de Jesus e tentava persuadi-los”. Como podemos chamar esse grupo?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Os proto-cristãos.</t>
+  </si>
+  <si>
+    <t>Os seguidores do Batista.</t>
+  </si>
+  <si>
+    <t>Os criptocristãos.</t>
+  </si>
+  <si>
+    <t>Os judeus.</t>
+  </si>
+  <si>
+    <t>Em 85 d.C aproximadamente, há uma reformulação das Dezoito Bençãos (Shemoneh Esreh) que eram recitadas na sinagoga. O que isso pode nos ajudar na compreensão da expulsão dos joaninos da sinagoga?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Com essa reformulação a relação entre eles melhora.</t>
+  </si>
+  <si>
+    <t>Na décima terceira benção encontramos o amor ao próximo.</t>
+  </si>
+  <si>
+    <t>Na décima segunda, a Birkat ha-mînîm, há uma maldição aos hereges, acabou atingindo os judeus cristãos, os mînîm.</t>
+  </si>
+  <si>
+    <t>As vozes discordantes são respeitadas.</t>
+  </si>
+  <si>
+    <t>Quais são os livros bíblicos considerados parte da tradição joanina?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Lucas, João e Mateus.</t>
+  </si>
+  <si>
+    <t>Mateus, Lucas e Marcos.</t>
+  </si>
+  <si>
+    <t>As Epístolas joaninas e Marcos.</t>
+  </si>
+  <si>
+    <t>Jo, 1Jo, 2Jo, 3Jo.</t>
+  </si>
+  <si>
+    <t>Nas pesquisas Joaninas há uma discussão antiga a respeito das fases da comunidade portadora a tradição. Como podemos descrever a primeira fase da história da comunidade?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A comunidade considerada "os judeus" como cegos e descrentes (Jo 12. 37-40). Esses judeus não seriam todos do Judaísmo, mas os que estavam na sinagoga e decidiram que qualquer um fiel às perspectivas de Jesus como messias ou preexistente deveria ser perseguido ou expulso.</t>
+  </si>
+  <si>
+    <t>Esta precede o evangelho. Esse momento vai de 50 até final dos anos 80 d.C. Nesse momento da história da comunidade há Judeus com perspectivas messiânicas comuns, inclusive seguidores de João Batista, os quais encontravam em Jesus aquele em quem se realizavam as profecias e viam nele o messias davídico, confirmado com os milagres.</t>
+  </si>
+  <si>
+    <t>Foi a fase da escrita do Evangelho e inserção do cap. 21.</t>
+  </si>
+  <si>
+    <t>Não é possível fazer qualquer afirmação sobre essa fase, porque fois a mais misteriosa da história joanina.</t>
+  </si>
+  <si>
+    <t>Literatura Joanina</t>
+  </si>
+  <si>
+    <t>Jo tem traços muito característicos em sua linguagem. Um deles é a poesia e dualismo. O que podemos afirmar sobre esse ponto.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Essa estratégia serviria para explicar coisas relacionadas a sua vinda, as categorias celestiais ou qualquer ideia difícil.</t>
+  </si>
+  <si>
+    <t>Qualquer leitura do texto já identifica pares opostos que dividem a realidade em forças contrastantes: luz/trevas, bem/mal, verdade/mentira, do alto/de baixo, céu/terra, vida/perdição. Esse dualismo não é gnóstico.</t>
+  </si>
+  <si>
+    <t>É nítido o dualismo Deus e Diabo, onde a qualquer momento um poderá vencer o outro.</t>
+  </si>
+  <si>
+    <t>Nenhuma poderia ser certa, porque não há dualismo em Jo.</t>
+  </si>
+  <si>
+    <t>É muito comum no Evangelho de João o uso da linguagem figurada para explicar coisas relacionadas à sua vinda, as categorias celestiais ou qualquer ideia difícil. Esse uso ora e outra gera um típico mal entendido, o que permite Jesus explicar seu ensinamento de forma mais extensa e desenvolver sua doutrina. Como esse esquema, de fala paradoxal e explicação, é articulado em Jo?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Há uma parábola bem complexa, uma resposta viável e outra parábola.</t>
+  </si>
+  <si>
+    <t>Não há um esquema, mas junção aleatória de palavras e respostas.</t>
+  </si>
+  <si>
+    <t>Dois dialogam, o que gera a dúvida e, depois, muitos são confundidos e esclarecidos.</t>
+  </si>
+  <si>
+    <t>Uma palavra de Jesus, de caráter paradoxal; isso suscita a incompreensão dos interlocutores; e, por fim, oferece, assim, a Jesus ou ao evangelista a ocasião de desenvolver ou de explicar o sentido desta palavra.</t>
+  </si>
+  <si>
+    <t>Qual afirmação abaixo NÃO é verdadeira em relação à carta escrita pelo Ancião para Gaio (3Jo)?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Terceira Epístola de João (3Jo) é o mais breve livro do NT que indica o mesmo "Ancião" como seu autor (v.1).</t>
+  </si>
+  <si>
+    <t>João na epístola mostra ser o líder oficial da igreja e pode destituir Diótrefres do pastoreio da igreja na Ásia.</t>
+  </si>
+  <si>
+    <t>Além da mesma autoria, o estilo e expansão são muito próximos à 2Jo. Como defendemos nas lições anteriores, o mesmo autor desse pequeno texto é o responsável pelas outras epístolas joaninas.</t>
+  </si>
+  <si>
+    <t>Em 3Jo não há crítica à indiferença moral ou a erros cristológicos, mas exortação em relação a recebimento e colhimento de missionários itinerantes que representavam o Ancião que por sua vez representavam um "nós" (1Jo 1.1-4): "não nos recebe" (v.9)</t>
+  </si>
+  <si>
+    <t>Em 3Jo é acusado de condutas reprováveis: é ambicioso, deseja o primeiro lugar; não recebe os enviados pelo Ancião e escola joanina ("nos recebe", v.9); espalha calúnias sobre o Ancião e a tradição que representa; impede os membros de sua comunidade receberem esses pregadores Ele não é acusado de erros teológicos ou morais, como é feito aos separatistas de 1Jo e 2Jo. Contudo, a crítica a ele se dá diante da sua postura de desrespeito ao Ancião e seus representantes. A respeito de quem se refere essa descrição?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Diótrefres.</t>
+  </si>
+  <si>
+    <t>Gaio</t>
+  </si>
+  <si>
+    <t>Em 3 João aparece alguns personagens importantes para a pesquisa na comunidade Joanina ou, pelo menos, para a essa carta e seus desafios. Entre eles há Gaio. Assinale uma opção correta a respeito como 3Jo apresenta.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>No texto ele é acusado de condutas reprováveis: é ambicioso, deseja o primeiro lugar; não recebe os enviados pelo Ancião e escola joanina.</t>
+  </si>
+  <si>
+    <t>É um importante líder missionário e está, inclusive com Paulo em suas viagens.</t>
+  </si>
+  <si>
+    <t>As respostas a e b estão corretas.</t>
+  </si>
+  <si>
+    <t>Oferece hospitalidade aos pregadores itinerantes próximos da escola joanina e enviados pelo Ancião da Igreja-Mãe. É conhecido por sua amabilidade e vivência na verdade, que seria fidelidade à tradição joanina representada pelo Ancião, motivo de disputa com os separatistas.</t>
+  </si>
+  <si>
+    <t>Seguindo algumas pesquisas, para dar coesão à estrutura do livro, indicam que João usa estratégias e técnicas. Quais seriam?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Inclusão de expressões que fazem ligação entre as partes ou dão continuidade ao texto.</t>
+  </si>
+  <si>
+    <t>Repetição de palavras.</t>
+  </si>
+  <si>
+    <t>Releitura de tradições.</t>
+  </si>
+  <si>
+    <t>Inserção de novas expressões desconhecidas.</t>
+  </si>
+  <si>
+    <t>Qual era a principal discórdia, testemunhadas nas epístolas, dos separatistas com a comunidade joanina?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A principal discórdia dos separatistas tinha relação com a cristologia, ou seja, discurso teológico a respeito de Jesus Cristo. Como percebemos em 2.22 e 4.2 – 3.15 as divergências se davam em torna da questão sobre a encarnação de Jesus, sua condição humana em relação e à filiação divina e, ainda, a dificuldade em conciliarem as ideias a respeito da expiação e sacrifício de Jesus.</t>
+  </si>
+  <si>
+    <t>O principal problema era a maneira como os joaninos pensavam a ceia.</t>
+  </si>
+  <si>
+    <t>Não é correto afirmar que a principal discórdia dos separatistas tinha relação com a cristologia, ou seja, discurso teológico a respeito de Jesus Cristo. Pelo contrário, não havia discórdia.</t>
+  </si>
+  <si>
+    <t>Muitas são as razões, mas a principal era o medo do autoritarismo.</t>
+  </si>
+  <si>
+    <t>Em Jo encontramos vários grupos em disputa com a comunidade joanina. Quem eram, entre esses, os adeptos de João Batista?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Os amigos de André, os quais não aceitaram seguir João e se tornaram fariseus.</t>
+  </si>
+  <si>
+    <t>Esses tinham o Batista como figura principal, o que levou o Quarto Evangelho a negar diretamente atributos como messias, Elias, o Profeta ou Luz ao Batista.</t>
+  </si>
+  <si>
+    <t>Alguns homens e curados por João Batista e por ele discipulado.</t>
+  </si>
+  <si>
+    <t>Seguidores de Jesus e, ao mesmo tempo, amigos de João Batista. Esses formam os que convenceram Jesus a ser batizado.</t>
+  </si>
+  <si>
+    <t>Alguns pesquisadores liam Jo em diálogo com o Gnosticismo. O que foi o Gnosticismo?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Não há um sistema monolítico gnósticos, mas várias perspectivas internas diferentes. As teses relativamente comuns diziam que a alma humana ou os princípios espirituais não pertenceriam a este mundo material (muitas vezes descrito como mau e ignorante), e poderiam ser salvas somente se recebessem a revelação de que pertenceriam a um reino celeste de luz (o plêroma ou plenitude), onde existiria uma hierarquia de emanações do verdadeiro Deus.</t>
+  </si>
+  <si>
+    <t>Ele é um sistema único de pensamento e dizia que a alma humana ou os princípios espirituais pertenceriam a este mundo, que seria o melhor possível e criado perfeito.</t>
+  </si>
+  <si>
+    <t>O Gnosticismo seria um filosofia nórdica na qual Thor daria a vida pelos seus súditos em nome de Odim.</t>
+  </si>
+  <si>
+    <t>Uma narrativa cristã apologética na qual Deus é bom e o Diabo é Mal.</t>
+  </si>
+  <si>
+    <t>Os joaninos foram expulsos pelos judeus das sinagogas por conta da alta cristologia. Como são descritos em Jo esses inimigos da comunidade?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Amigos do imperador e inimigos dos fariseus. Gente de boa fé, mas enganados.</t>
+  </si>
+  <si>
+    <t>Lideres com grande capacidade de manipulação de massa.</t>
+  </si>
+  <si>
+    <t>Filhos de Deus e amados do Pai.</t>
+  </si>
+  <si>
+    <t>Para Jo eles estavam nas trevas. Eles negavam ser Jesus a presença de Deus. Por isso, eram chamados de filhos do Diabo.</t>
+  </si>
+  <si>
+    <t>A estruturação de Jo é muito importante para sua compreensão. Como podemos estruturar esse evangelho?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Há um prólogo no final do texto e uma esquema de divisão em cinco partes.</t>
+  </si>
+  <si>
+    <t>Há um prólogo de abertura do texto (1.1-18) que pode ser observado como um texto separado, da mesma forma um epílogo (cap. 21), posto após a conclusão do evangelho (20. 30-31). Essas duas partes formam uma moldura no texto, como num quadro esquemático. O corpo do evangelho é composto pelo bloco 1.19–20.31, cuja forma final pode ser dividida em duas partes: 1.19–12.50 e 13.1–20.30.</t>
+  </si>
+  <si>
+    <t>1.19–12.50; 13.1–20.30 e 20-22,12.</t>
+  </si>
+  <si>
+    <t>Não há estrutura em Jo.</t>
+  </si>
+  <si>
+    <t>Na terceira fase da comunidade é o tempo quando as epístolas de 1Jo e 2Jo foram escritas, em torno de 100 d.C. Quais são as características dessa fase?  
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A comunidade se dividiu em dois grupos:  os que permaneceram com a teologia joanina e os que seguiram os separatistas.</t>
+  </si>
+  <si>
+    <t>Um tempo de expansão e unidade.</t>
+  </si>
+  <si>
+    <t>É o período de muita riqueza da comunidade, quando eles se alinham ao imperador.</t>
+  </si>
+  <si>
+    <t>Foi o tempo da grande ascensão do Discípulo amado na liderança da igreja no Oriente.</t>
+  </si>
+  <si>
+    <t>Marque a opção que caracteriza a ultima fase da comunidade joanina.
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>É o tempo em que a comunidade se dividiu em dois grupos.  a) alguns aderiram à visão representada pelo autor de 1 e 2 João, que foi escrito por um autor diferente do evangelho.</t>
+  </si>
+  <si>
+    <t>Essa é fase quando 3Jo foi escrita e o redator final inseriu o capítulo 21 no quarto Evangelho. A comunidade joanina começa um processo de desintegração. Os representados pelos que permaneceram na comunidade e nas epístolas foram absorvidos pela Igreja mãe ou "igreja católica".</t>
+  </si>
+  <si>
+    <t>Nenhuma resposta está correta.</t>
+  </si>
+  <si>
+    <t>Segundo o Gnosticismo do séc. II como seria possível acender a realidade perfeita do Reino da Luz?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Por meio da ascese corporal e ritos de lutas contra os seres malignos.</t>
+  </si>
+  <si>
+    <t>Por meio do batismo, de complexos rituais cúlticos (frenquentemente envolvendo unção) ou, ainda, por meio da reflexão filosófica.</t>
+  </si>
+  <si>
+    <t>Através das forças da natureza boa do mundo.</t>
+  </si>
+  <si>
+    <t>Nenhuma das afirmações acima.</t>
+  </si>
+  <si>
+    <t>Qual a melhor explicação para a expulsão dos cristãos joaninos da sinagoga?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O evangelho mostra que a alto cristologia escandalizava os judeus mais tradicionais da sinagoga por interpretarem isso como afronta ao monoteísmo, porque reconhecia Jesus como um tipo de "segundo Deus" (5.18). Isso gerou a expulsão dos joaninos das sinagogas (Jo 9.22; 16.2).</t>
+  </si>
+  <si>
+    <t>Porque fizerem algumas acusações contra os judeus, tais quais hipócritas, raça de víboras ou filhos da guerra.</t>
+  </si>
+  <si>
+    <t>Porque comiam carne no interior da sinagoga com churrasqueira imprópria e vinho de marca romana, o que seria uma blasfêmia.</t>
+  </si>
+  <si>
+    <t>Nada há no texto sobre isso.</t>
+  </si>
+  <si>
+    <t>Tradicionalmente, a quem é atribuída a autoria da tradição joanina?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Marcos o discípulo de Pedro.</t>
+  </si>
+  <si>
+    <t>Lucas o médico.</t>
+  </si>
+  <si>
+    <t>João filho de Sóstenes.</t>
+  </si>
+  <si>
+    <t>Em 3Jo também aparece um personagem chamado Demétrio. Seguindo os indícios do texto, quem ele era?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Um forasteiro da Ásia convertido durante a pregação do Discípulo Amado.</t>
+  </si>
+  <si>
+    <t>Um apóstolo entre os doze.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Era um dos missionários que gozava do respeito de todos e iria visitar a Gaio, talvez com 3Jo em mãos como recomendação.
+</t>
+  </si>
+  <si>
+    <t>Um missionário companheiro de Justino, o Mártir.</t>
+  </si>
+  <si>
+    <t>Em Jo aparece um personagem muito emblemático, o discípulo amado. Alguns o confundiam com João, filho de Zebedeu. Contudo, as pesquisas avançaram. Quem seria, hoje nas pesquisas esse personagem?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O Discípulo Amado, antes identificado como o Apóstolo João, filho de Zebedeu, é o herói da comunidade, iniciador das tradições que geraram o evangelho e fonte para a escola joanina, provavelmente formada por seus discípulos.</t>
+  </si>
+  <si>
+    <t>Um personagem presente nos quatro evangelhos. Talvez, a inspiração para todos eles.</t>
+  </si>
+  <si>
+    <t>O autor do Evangelho de João, aquele que corrigiu o texto e deu sua forma final.</t>
+  </si>
+  <si>
+    <t>Um personagem sem muita importância para a comunidade joanina.</t>
+  </si>
+  <si>
+    <t>Seguindo a hipótese de Brown, qual foi o futuro dos separatistas?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Tornaram-se amigos da igreja mãe.</t>
+  </si>
+  <si>
+    <t>Forma expulsos de uma seita posterior chamada gnosticismo.</t>
+  </si>
+  <si>
+    <t>Tornaram-se monges beneditinos.</t>
+  </si>
+  <si>
+    <t>Tenderam para o docetismo ( que era uma seita reconhecida no século II por não considerar a humanidade de Jesus) incrementando sua interpretação, também para gnosticismo, especialmente o de linha valentiniana.</t>
+  </si>
+  <si>
+    <t>“Durante muito tempo, o Quarto Evangelho foi considerado como um texto helenístico; ou seja, obra influenciada e com traços das ideias gregas”. Seguindo essa afirmação, o que podemos ainda acrescentar a essa discussão?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Entendia-se que o uso de ideias como luz e verdade, seu dualismo luz e trevas (verdade e mentira) e, especialmente, o conceito de Verbo (lógos) era consequência da relação de Jo com o pensamento filosófico grego e suas ramificações.</t>
+  </si>
+  <si>
+    <t>Por isso, muitos acabavam dizendo que Jo era um evangelho muito judaico e pouco grego.</t>
+  </si>
+  <si>
+    <t>O logos era como uma afirmação da Hokamah de Provérbios.</t>
+  </si>
+  <si>
+    <t>Não há qualquer razão para pensar em Grécia e Judéia. Bastaria do Mundo Antigo o Império Babilônico.</t>
+  </si>
+  <si>
+    <t>Literatura Paulina</t>
+  </si>
+  <si>
+    <t>De acordo com as cartas de Paulo e o livro dos Atos dos Apóstolos, antes do encontro com Cristo no caminho de Damasco, Paulo foi um grande perseguidor da igreja. Ele atacou a igreja nascente com violência, procurando destruí-la (Gl 1,13). Era esse o aspecto negativo de seu zelo pelas tradições de Israel, que talvez tenha encontrado uma saída positiva no proselitismo dos gentios. Quando Paulo afirma que perseguiu “a Igreja de Deus” (1 Cor 15,9), é natural pensar na Igreja de Jerusalém. A “igreja de Deus” dificilmente seria uma entidade reconhecível fora de Jerusalém nos primeiros dois ou três anos após a ressurreição de Cristo. O livro de Atos dos Apóstolos afirma que Saulo “assolava a igreja, entrando pelas casas; e, arrastando homens e mulheres, encerrava-os no cárcere” (At 8,3). Além disso, quando a perseguição provocava dispersão, Paulo atormentava os refugiados até fora da província da Judeia.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Paulo foi um grande perseguidor da igreja. Ele atacou a igreja nascente com violência, procurando destruí-la.
+II - Era esse o aspecto negativo de seu zelo pelas tradições de Israel, que talvez tenha encontrado uma saída positiva no proselitismo dos gentios.
+III - Quando Paulo afirma que perseguiu “a Igreja de Deus”, a referência envolve todas as igrejas, não apenas a Igreja de Jerusalém.
+IV - Quando a perseguição provocava dispersão, Paulo atormentava os refugiados até fora da província da Judeia.
+Está correto o que se afirma em:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+I, II e III apenas.
+</t>
+  </si>
+  <si>
+    <t>1 Depois disso, Paulo afastou-se de Atenas e foi para Corinto. 2 Lá encontrou um judeu chamado Áquila, natural do Ponto, recém-chegado da Itália com Priscila, sua mulher, em vista de Cláudio ter decretado que todos os judeus afastassem de Roma. Foi, pois, ter com eles. 3 Como exercesse a mesma atividade artesanal, ficou ali hospedado e trabalhando; eram, de profissão, fabricantes de tendas. 4 Cada sábado, ele discorria na sinagoga, esforçando-se por persuadir judeus e gregos. 5 Quando, porém, Silas e Timóteo chegaram da Macedônia, Paulo começou a dedicar-se inteiramente à Palavra, atestando aos judeus que Jesus é o Cristo. 6 Contudo, diante da oposição e das blasfêmias deles, Paulo sacudiu suas vestes e disse-lhes: “Vosso sangue recaia sobre a vossa cabeça! Quanto a mim, estou puro, e de agora em diante dirijo-me aos gentios”. 7 Então, retirando-se dali, dirigiu-se à casa de certo Justo, adorador de Deus, cuja casa era contígua à sinagoga. 8 Mas Crispo, o chefe da sinagoga, creu no Senhor com toda a sua casa. Também muitos dos coríntios, ouvindo a Paulo, abraçavam a fé e eram batizados. 9 Uma noite, disse o Senhor a Paulo, em visão: “Não temas. Continua a fala e não te cales. 10 Eu estou contigo, e ninguém porá a mão em ti para fazer-te mal, pois tenho um povo numerosos nesta cidade”. 11 Assim, residiu ali um ano e seis meses, ensinando entre eles a palavra de Deus. 12 Sendo Galião procônsul da Acaia, os judeus levantaram-se unanimemente contra Paulo e conduziram-no ao tribunal, 13 dizendo: “Este indivíduo procura persuadir os outros a adorar a Deus de maneira contrária à Lei”. 14 Paulo ia abria a boca, quando Galião retrucou aos judeus: “Se se tratasse de delito ou ato perverso, ó judeus, com razão eu vos atenderia. 15 Mas se são questões de palavras, de nomes, e de vossa própria Lei, tratai vós mesmos disso! Juiz destas coisas eu não quero ser”. 16 E despediu-os do tribunal. 17 Todos então se apoderaram de Sóstenes, o chefe da sinagoga, e os espancaram diante do tribunal, sem que Galião absolutamente interviesse. 18 Paulo, porém, permaneceu ali ainda muitos dias. Depois, despediu-se dos irmãos e embarcou para a Síria (At 18,1-18).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - At 18,1-18 apresenta as atividades de Paulo em Corinto e demonstra que a comunicação da “palavra da cruz” entre os judeus provocou diversas reações: um grupo o expulsou da sinagoga e ainda queria que as autoridades romanas o condenassem, mas outro grupo ajuntou-se a Paulo.
+II - Em Corinto Paulo encontrou Priscila e Áquila, recém-chegados da Itália, pois o imperador Cláudio havia expulsado os judeus de Roma.
+III - Paulo permaneceu cerca de dois anos na cidade de Corinto.
+IV -  Paulo foi acusado pelos judeus de persuadir os outros a adorar a Deus de maneira contrária à Lei diante do procônsul Galião.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O “corpo” que alguns coríntios não percebem enquanto comem e bebem é a comunidade, isto é, a igreja como corpo de Cristo. A expressão “sem discernir o corpo” descreve a forma como os coríntios celebravam a Ceia: com total descuido pela união do grupo e o apoio a este corpo que deveria manifestar-se no cuidado com os pobres e fracos. Com a expressão “sem discernir o corpo” Paulo, portanto, sintetiza tudo o que disse sobre a maneira em que os coríntios comem e bebem na Ceia supostamente comunitária. Quando os irmãos mais ricos envergonham os pobres, menosprezam a igreja de Deus (11,22), ou seja, não discernem o corpo de Cristo que é constituído pelos “pequenos”, a comunidade torna-se “culpada do corpo e sangue de Jesus”(11,27). A conexão entre o irmão mais fraco e a pessoa de Cristo já tinha sido indicada em 8,11-12: pecam contra Cristo os que ferem os mais fracos. Paulo ousa dizer agora que os que desprezam “os que nada têm” são responsáveis pela crucificação. Ainda que afirmem ser cristãos, atuam como as autoridades que não puderam discernir em Jesus, companheiro dos humildes e desprezados, o Senhor da glória (1 Cor 2,8). As ações destas pessoas contradizem a vida de Jesus, que se identificou com os necessitados ao ponto de experimentar junto com eles a rejeição e a condenação das autoridades religiosas e civis.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - O “corpo” que alguns coríntios não percebem enquanto comem e bebem não é a comunidade, isto é, a igreja como corpo de Cristo, mas a si mesmos enquanto indivíduos.
+II - A expressão “sem discernir o corpo” descreve a forma como os coríntios celebravam a Ceia: com total descuido pela união do grupo e o apoio a este corpo que deveria manifestar-se no cuidado para com os pobres e fracos.
+III - Os irmãos mais ricos envergonham os pobres e menosprezam a igreja de Deus quando não discernem que o corpo de Cristo é constituído pelos “pequenos”.
+IV - As ações destas pessoas contradizem a vida de Jesus, pois Ele se identificou com os necessitados ao ponto de experimentar junto com eles a rejeição e a condenação das autoridades religiosas e civis.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Paulo depende da proclamação da cruz para anunciar a transformação dos seus ouvintes. A “palavra da cruz”, que indica o destino dos “estão a caminho da ruína” e dos que “estão sendo salvos”, é o poder que, de acordo com a citação da Escritura, destruirá “a sabedoria dos sábios e anulará a inteligência dos entendidos”. A destruição da “sabedoria dos sábios” e anulação da “inteligência dos entendidos” é indicada pelas perguntas: “Onde está o sábio? Onde o escriba? Onde o inquiridor deste século?” (1,20a). Por meio destas perguntas Paulo quer que os coríntios vejam qual é o destino da “sabedoria deste mundo” à luz da ação salvadora de Deus na cruz de Jesus. “Sábio”, “escriba” e “inquiridor” envolvem, pleonasticamente, todo o âmbito da sabedoria humana, como afirma a referência à “sabedoria do mundo” da questão seguinte: “Porventura não tornou Deus louca a sabedoria do mundo” (1,20b)? Deus substitui a sabedoria humana da presente ordem pela “palavra cruz”. Deus promete destruir e anular a sabedoria das pessoas que estavam comprometidas com a “sabedoria de palavra” e eram responsáveis pelas divisões na igreja (1,10-17), além de indicar que elas não possuem o status que afirmam possuir (1,20).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Paulo de forma alguma depende da proclamação da cruz para anunciar a transformação dos seus ouvintes.
+II - A “palavra da cruz” é o poder que, de acordo com a citação da Escritura, destruirá “a sabedoria dos sábios e anulará a inteligência dos entendidos”.
+III - Por meio de perguntas retóricas Paulo quer que os coríntios vejam qual é o destino da “sabedoria deste mundo” à luz da ação salvadora de Deus na cruz de Jesus.
+IV - Deus promete destruir e anular a sabedoria das pessoas que estavam comprometidas com a “sabedoria de palavra” e eram responsáveis pelas divisões na igreja.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Paulo introduz a verdadeira forma pela qual os coríntios devem considerar a sua vocação ao afirmar que a fonte da identidade é Cristo, “poder e sabedoria de Deus” (1,24). “Vós, porém, sois dele, em Cristo Jesus” (1,30) indica que os coríntios se encontram “entre os que creem” e demonstra quão diferente significa ser “os que estão sendo salvos” (1,18-25). Os coríntios foram chamados e têm o status de nova criação (2 Cor 5,17). Eles pertencem a Cristo como pessoas e como corpo, isto é, a comunidade dos que creem. A vocação não muda necessariamente o status social daqueles que creem (cf. 1 Cor 7,17-24), mas os que creem e são desprezados de acordo com os padrões de pensamento “deste mundo” ganham um novo status diante de Deus. Paulo quer que os coríntios reflitam sobre quem eles eram no tempo da sua vocação e refletir sobre o seu significado. Os coríntios deveriam ver a si mesmos da perspectiva de Deus para compreender que agora em Cristo são uma comunidade que deve ser caracterizada pela unidade, não preocupada com status social e pela fidelidade a esta ou aquela pessoa.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - A fonte da identidade cristã é Cristo, “poder e sabedoria de Deus”.
+II - Os coríntios foram chamados e têm o status de nova criação. Eles pertencem a Cristo como pessoas e como corpo, isto é, a comunidade dos que creem.
+III - A vocação muda necessariamente o status social daqueles que creem.
+IV - Os coríntios deveriam ver a si mesmos da perspectiva de Deus para compreender que agora em Cristo são uma comunidade que deve ser caracterizada pela unidade.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Paulo indica com a expressão “Não posso louvar-vos” (11,17a) que abordará um problema que lhe ser bem negativo e que desaprovava o que ocorria na igreja por ocasião do culto (11,17.18.20.22). Estas reuniões, em vez de edificar a igreja, causavam-lhe danos. O que ocorria era: “as pessoas que nada têm”, isto é pobres”, eram marginalizadas por ocasião da refeição comunitária, que supostamente era comum. A rivalidade que havia entre os grupos existentes na igreja envolvia uma distinção entre ricos e pobres: “... cada um se apressa a comer a sua própria ceia; e, enquanto um passa fome, o outro fica embriagado. Não tendes casas onde comer e beber? Ou desprezais a igreja de Deus e quereis envergonhar aqueles que nada têm?” (11,21b-22a). Paulo critica duramente uma Ceia na qual as necessidades dos irmãos e irmãs mais necessitados são omitidas. O juízo de que Paulo fala tem antecedentes na história de Israel: com linguagem similar, os profetas condenaram o culto que não era acompanhado da prática da justiça (Is 1,14-17; 58,1-14; Jr 7,1-7; Am 4,10-5,24; Mq 6,5-8). A ação de Paulo reflete também a prática de Jesus, que denunciou veementemente os comerciantes que tinham desvirtuado o culto do templo ao monopolizar para os seus negócios o único espaço destinado à participação dos grupos marginalizados (Mc 11,15-19).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Com a expressão “Não posso louvar-vos” (11,17a), Paulo concorda com a forma como os coríntios celebravam a Ceia do Senhor.
+II - Na igreja de Corinto algumas pessoas eram marginalizadas por ocasião da refeição comunitária.
+III - A rivalidade que havia entre os grupos existentes na igreja estava relacionada com uma distinção entre ricos e pobres.
+IV - Paulo critica duramente uma Ceia na qual as necessidades dos irmãos e irmãs mais necessitados são omitidas.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Paulo nasceu na cidade de Tarso, localizada na província da Cilícia, hoje parte da Turquia. Tarso era uma cidade importante ligada aos Romanos, onde havia também uma escola filosófica estoica. Paulo afirma que era hebreu e pertencia à tribo de Benjamin (2 Cor 11,22; Rm 11,1; Fl 3,4-5). Sua insistência em afirmar que é israelita denuncia que, embora criado na diáspora, era um judeu convicto. Paulo recebeu o nome Saulo, o nome do primeiro rei de Israel. Paulo, como é comumente chamado, é parte do seu triplo nome como cidadão romano: “Bem que eu poderia confiar também na carne. Se qualquer outro pensa que pode confiar na carne, eu ainda mais: circuncidado ao oitavo dia, da tribo de Benjamin, hebreu de hebreus, quanto à lei, fariseu” (Fp 3,4-5).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Paulo nasceu na cidade de Tarso, localizada na província da Cilícia, cidade importante ligada aos Romanos.
+II - Embora criado na diáspora, Paulo era um judeu convicto de suas tradições religiosas.
+III - Paulo recebeu o nome Saulo, o nome do primeiro rei de Israel. Paulo, como é comumente chamado, é parte do seu triplo nome como cidadão romano.
+IV - Embora fosse um judeu convicto, não é possível associar Paulo à tradição farisaica.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I, II e III apenas.                  
+</t>
+  </si>
+  <si>
+    <t>Desde a época de Alexandre Magno (século IV a. C.), os povos independentes da antiga Grécia mesclaram-se nos exércitos e nas novas cidades povoadas por colonos gregos através das regiões conquistadas por Alexandre. Com sua posterior incorporação ao Império Romano, o caráter multiétnico da sociedade grega consolidou-se ainda mais. Neste processo, o caráter da religião também mudou. Os deuses antigos perderam sua credibilidade como protetores do bem-estar do povo e garantidores da vitória sobre os seus inimigos. A maioria dos habitantes de um império que não era seu, que produzia miséria e grande insegurança diante do futuro, buscava na religião uma resposta para suas necessidades pessoais ou, pelo menos, delas escapar. Estas inquietações impulsionaram as pessoas a procurar novas divindades e novas formas de culto, como as que eram trazidas do Egito pelos imigrantes, soldados e comerciantes. Os cultos de “mistérios” ofereciam aos iniciados uma salvação dos poderes malignos do mundo e do universo, além de uma experiência imediata de êxtase espiritual. Toleradas pelas autoridades civis, às vezes estas religiões provocavam oposição por causa do caráter escandaloso de algumas de suas celebrações.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Desde a época de Alexandre Magno (século IV a. C.), os povos independentes da antiga Grécia mesclaram-se nos exércitos e nas novas cidades povoadas por colonos gregos através das regiões conquistadas por Alexandre.
+II - A maioria dos habitantes de um império que não era seu buscava na religião uma resposta para suas necessidades pessoais ou, pelo menos, delas escapar.
+III - Os cultos de “mistérios” não ofereciam aos iniciados uma salvação dos poderes malignos do mundo e do universo, além de uma experiência imediata de êxtase espiritual.
+IV - Toleradas pelas autoridades civis, as religiões de mistério não provocavam oposição e eram, em geral, aceitas pela população.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I, II e IV apenas.
+</t>
+  </si>
+  <si>
+    <t>Paulo deixa claro que os dons foram dados para a edificação da igreja no “agora” da sua existência. Para algumas pessoas da igreja de Corinto o dom de línguas era a evidência de sua espiritualidade. Eles também pensavam que tinham o conhecimento de todas as coisas no tempo presente. Elas não conseguiam perceber que o conhecimento e, mesmo a profecia, são parciais, que o conhecimento total só será possível quando estivermos “face a face com Cristo”. Os dons sustentam e orientam a comunidade de fé neste momento anterior ao “tempo final”, mas quando estivermos “face a face” com Cristo os carismas perderão sua vigência. Para esclarecer esse assunto, Paulo propõe a si mesmo como exemplo de criança que se tornou pessoa adulta (13,11): a pessoa adulta abandona as características próprias da infância. Há uma ruptura entre a vida presente e a vida futura, que é comparada com a percepção difícil das coisas que se vêm num espelho e sua observação direta em toda sua claridade (13,12).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I -  Para algumas pessoas da igreja de Corinto o dom de línguas era a evidência de sua espiritualidade.
+II - Estas pessoas também pensavam que tinham o conhecimento de todas as coisas no tempo presente, no agora da existência cristã.
+III - Os dons sustentam e orientam a comunidade de fé no momento anterior ao “tempo final”, mas quando estivermos “face a face” com Cristo os dons não terão mais valor.
+IV - Não há uma ruptura entre a vida presente e a vida futura, que é comparada com a percepção difícil das coisas que se vêm num espelho.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I, II e IV apenas.
+</t>
+  </si>
+  <si>
+    <t>Paulo tinha cidadania romana, uma honra raramente concedida a pessoas que viviam nas províncias. Ele herdou a cidadania romana ao nascer, talvez concedida a seu pai ou avô por serviços proeminentes prestados a um procônsul militar. A cidadania romana trazia consigo diversos privilégios, dos quais Paulo valeu-se durante o seu ministério, entre os quais destacam-se: o direito a um julgamento justo, por exemplo, a isenção de punições degradantes como ser chicoteado e, principalmente, o direito de apelar da jurisdição de um tribunal inferior para o tribunal do imperador de Roma (At 16,37; 22,25; 25,11).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Paulo tinha cidadania romana, uma honra comumente concedida a pessoas que viviam nas províncias.
+II - Paulo herdou a cidadania romana ao nascer, talvez concedida a seu pai ou avô por serviços proeminentes prestados aum procônsul militar.
+III - Entre os privilégios da cidadania romana destacam-se: o direito a um julgamento justo, por exemplo, a isenção de punições degradantes e, principalmente, o direito de apelar da jurisdição de um tribunal inferior para o tribunal do imperador de Roma.
+IV - A cidadania romana trazia consigo diversos privilégios, mas Paulo não se valeu de nenhum deles durante o seu ministério.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I e III apenas.
+</t>
+  </si>
+  <si>
+    <t>Paulo não procura ocultar a afronta causada pela proclamação da realidade ofensiva de um Messias crucificado. A narrativa da cruz envolve a vida de uma pessoa considerada do mais baixo status social, que, paradoxalmente, “para os que são chamados”, “judeus e gregos”, significa “poder” e a “sabedoria de Deus”. Para “os que são chamados”, o Cristo crucificado não significa escândalo ou loucura. A sabedoria de Deus está fundamentada na loucura pregação, no anúncio do Cristo crucificado, em quem Deus inaugurou uma nova forma de salvação. A proclamação do “Cristo crucificado”, “sabedoria e poder de Deus”, faz com que a diferença entre judeus e gentios seja superada. Os limites existentes até este momento entre judeus e gentios são derrubados. Novos limites são colocados, mas eles são definidos em relação em relação à “palavra da cruz”, o paradigma fundacional do novo mundo criado para a humanidade (1Cor 1,23-24).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Paulo procura ocultar a afronta causada pela proclamação da realidade ofensiva de um Messias crucificado.
+II - A narrativa da cruz envolve a vida de uma pessoa considerada do mais baixo status social, mas que, para os que são chamados” significa “poder” e a “sabedoria de Deus”.
+III - A proclamação do “Cristo crucificado”, “sabedoria e poder de Deus”, de forma alguma provoca a superação da diferença entre judeus e gentios.
+IV - A “palavra da cruz” é o paradigma fundacional do novo mundo criado para a humanidade.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O orador greco-romano explorava suas habilidades retóricas para atingir as metas propostas, mas Paulo recusa seguir este modelo. Recorrer à sabedoria humana, especialmente a eloquência e dinâmica humanas através da retórica era, para ele, indigno de um pregador fiel à mensagem da cruz. A proclamação da cruz de Paulo indica uma forma de ação que procurava evitar usurpar o seu poder. A retórica greco-romana confiava nos recursos humanos, mas Paulo depende do poder do Espírito para produzir os resultados desejados, a fé. Ele estava convencido que tinha sido comissionado não para “apresentar” um discurso eloquente, mas proclamar o “mistério” de Deus. Era este “mistério” que determinava a forma da sua pregação, distinguindo-o também dos oradores greco-romanos, para quem a forma de apresentação era tão ou talvez mais importante do que o próprio conteúdo do discurso. O fato de que Paulo decidiu “nada saber” não significa que ele tenha rejeitado qualquer outro tipo de conhecimento, mas que seu foco central era o “Cristo crucificado”.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Para Paulo, recorrer à sabedoria humana, especialmente a eloquência e dinâmica humanas através da retórica, era indigno de um pregador fiel à mensagem da cruz.
+II - A “proclamação da cruz” de Paulo assinala uma forma de ação que procura evitar usurpar o seu poder.
+III - O conteúdo da mensagem não determinava a forma da pregação de Paulo.
+IV - Paulo não se distinguia dos oradores greco-romanos, para quem a forma de apresentação era tão ou talvez mais importante do que o próprio conteúdo do discurso.
+Está correto o que se afirma em:</t>
+  </si>
+  <si>
+    <t>Durante o período de expansão do domínio romano, muitos escravos foram incorporados à economia do império por meio das guerras. O sequestro de aldeias inteiras e a pirataria em alto mar produziam também grande número de escravos. O endividamento produzia também a escravidão. Muitos nasciam escravos, já que os filhos de uma escrava herdavam sua condição. A maior parte dos escravos de como Corinto em meados do primeiro século era de origem grega e havia nascido na casa do seu senhor. A multidão de escravos das minas de todo o Império e os escravos que realizavam tarefas agrícolas nos latifúndios da Itália, onde a escravidão era mais brutal e opressora, suportavam condições sub-humanas. Os escravos urbanos incorporados na produção das empresas domésticas tinham outras condições: nesta categoria, nas casas ricas, encontram-se cozinheiros, mordomos, pedagogos, administradores, etc. Filósofos e pensadores populares da época enfatizavam a condição plenamente humana dos escravos, a liberdade de espírito que possui todo ser humano.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - A base da economia do mundo greco-romano era o trabalho escravo.
+II - Durante o período de expansão do domínio romano, muitos escravos foram incorporados à economia do império por meio das guerras.
+III - A maior parte dos escravos de Corinto em meados do primeiro século era de origem grega e tornara-se escrava por causa da guerra.
+IV - Filósofos e pensadores populares da época enfatizavam a condição plenamente humana dos escravos, a liberdade de espírito que possui todo ser humano.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Quando Paulo e Barnabé retornaram a Antioquia, logo surgiu uma controvérsia. Parece que Paulo logo começou a sentir que os líderes de Jerusalém não estavam observando o espírito do acordo. Houve um choque entre ele e Pedro em Antioquia, enquanto Pedro passava algum tempo com eles ali. No início, Pedro comia livremente com os cristãos gentios, mas alguns mensageiros de Tiago vindos de Jerusalém persuadiram-no a mudar seus modos e se afastar do convívio à mesa com os gentios. Como esta discordância afetava a unidade da igreja, os seus líderes organizaram uma reunião em Jerusalém, comumente chamada Assembleia de Jerusalém, para examinar o problema, com a participação de pessoas da igreja de Antioquia (At 15,1-35). Os membros da igreja de Jerusalém que afirmavam que os convertidos gentios tinham de ser circuncidados e submeter-se à lei mosaica tiveram a oportunidade de expressar sua opinião, mas os apóstolos e anciãos decidiram que aos cristãos gentios seria apenas exigido que se abstivessem “das carnes imoladas aos ídolos, do sangue, das carnes sufocadas, e das uniões ilegítimas” (15,29). Se os cristãos gentios concordavam com esses termos, a barreira do convívio à mesa seria removida.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - O choque entre Paulo e Pedro em Antioquia deve-se a que, enquanto Pedro passava algum tempo com ali, comia livremente com os cristãos gentios, mas alguns mensageiros de Tiago vindos de Jerusalém persuadiram-no a mudar seus modos e se afastar do convívio à mesa com os gentios.
+II - Esta discordância, sentar ou não à mesa com os gentios, afetava a unidade da igreja.
+III - A reunião em Jerusalém, comumente chamada Assembleia de Jerusalém, foi convocada para examinar este problema que envolvia a missão aos gentios.
+IV - Os membros da igreja de Jerusalém que afirmavam que os convertidos gentios tinham de ser circuncidados e submeter-se à lei mosaica não tiveram a oportunidade de expressar sua opinião.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A “palavra da cruz” era o centro da proclamação de Paulo e o seu objetivo era estabelecê-la como base da vida comunitária (1,10-17). A “palavra da cruz”, uma expressão que Paulo utiliza para a narrativa do evangelho na sua totalidade e que inclui a morte e ressurreição de Cristo, estabelece “uma nova forma de ser no mundo”. Esta mensagem é a base da identidade da comunidade cristã e o seu poder transformador dá forma à sua existência no presente e no futuro. Nesse sentido, o discurso de Paulo contra as divisões na igreja de Corinto inicia-se com uma explicação do “por que” e “como” o Evangelho entra em conflito com a “sabedoria do mundo”. A discussão apresentada apresenta uma oposição entre Deus e o “mundo”, que se manifesta nos valores apresentados na antítese poder-fraqueza, embora Paulo atribua um significado positivo a estes termos ao apresentar a revelação do poder de Deus na fraqueza da cruz.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - “Palavra da cruz” designa a narrativa do evangelho na sua totalidade, que inclui a morte e ressurreição de Cristo e estabelece “uma nova forma de ser no mundo.
+II - A “palavra da cruz” é a base da identidade da comunidade cristã e o seu poder transformador dá forma à sua existência no presente e no futuro.
+III - Não há conflito algum entre a proclamação da “palavra da cruz” e a “sabedoria deste mundo”.
+IV - Paulo atribua um significado positivo aos termos “poder” e fraqueza” ao apresentar a revelação do poder de Deus na fraqueza da cruz.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>“Na Antiguidade (...) as convenções da carta eram conservadoras, mas nem sempre observadas. Os manuais da Antiguidade tardia oferecem formatos de cartas com espaços em branco para os detalhes apropriados serem inseridos para uma variedade de propósitos. Estes vão desde uma simples carta amigável, que é toda saudações sem mensagem alguma, a cartas de crítica e recomendação, cujo propósito é estabelecer ou confirmar um tipo específico de relacionamento. Mas esses tratamentos são muito esquemáticos; as cartas antigas de fato dizem qualquer coisa que seus autores queriam dizer, e as convenções são adaptadas de acordo. Por exemplo, cartas começam quase sempre com uma saudação, “A para B”, saudações”, para estabelecer um relacionamento entre escritor e destinatário. Mas quando o imperador manda uma carta para uma cidade em sua capacidade oficial, a saudação inclui todos os seus títulos para mostrar sua autoridade, por exemplo, para legislar para a cidade, ou outorgar benefícios. De modo semelhante, Paulo adorna o próprio nome a fim de dar autoridade ao ensinamento em suas cartas. Os desejos de saúde pro forma e o reconhecimento de uma carta anterior, que geralmente se seguem às saudações iniciais, podem de modo semelhante ser adaptados. Em cartas sobre filosofia moral, Sêneca faz de seus votos de saúde e bem-estar filosófico a Lucílio uma parte substancial de cada uma, e ao comentar os relatos de Lucílio sobre seu progresso, “documenta” o efeito de seu próprio ensino” (KERMODE, Frank &amp; ALTER, Robert (Orgs). Guia Literário da Bíblia. São Paulo: Editora UNESP, 1997, p. 612).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Na Antiguidade, as convenções da carta eram conservadoras, mas nem sempre observadas.
+II - Os manuais da Antiguidade tardia oferecem formatos de cartas com espaços em branco para os detalhes apropriados serem inseridos para uma variedade de propósitos.
+III - Quando o imperador mandava uma carta para uma cidade em sua capacidade oficial, a saudação não incluía todos os seus títulos, pois ele era autoridade final.
+IV - Paulo insere o próprio nome em suas cartas com objetivo de dar autoridade ao ensinamento nelas contido.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Como um homem afronta a Cristo, sua “cabeça” (11,3), se tem a cabeça coberta? Em que sentido a mulher afronta o homem, sua “cabeça” (fonte da criação - v. 3), se não se cobre com o cabelo de forma bem arrumada? A definição da apresentação pessoal que constitui uma afronta para outras pessoas ou que possa ser considerada vergonhosa é determinada de forma particular em cada cultura (11,6). O que interessa a Paulo é que os cristãos evitem certas práticas que atentem contra a sensibilidade das pessoas em seu contexto social. A cultura greco-romana valorizava a dignidade, a honra pessoal e o papel das mulheres era a chave para a estima social atribuída ao seu esposo e família ou o grupo social a que pertenciam. Numa sociedade que não concedia muito espaço público à mulher, as poucas mulheres que atuavam diante dos homens eram julgadas como honradas ou não segundo a forma como acatavam o código cultural referente à arrumação pessoal, um juízo que era extensivo a sua família ou grupo social. As mulheres que não cumpriam estas normas eram qualificadas de indecentes e desonestas, algo que também se estendia à reputação do grupo que tolerava a infração das normas sociais. Se as mulheres profetas rejeitavam a norma social referente à arrumação do cabelo, envergonham a si mesmas e afrontam os homens do seu grupo e a igreja em geral.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Paulo não está, de forma alguma, preocupado com práticas que atentem contra a sensibilidade das pessoas em seu contexto social.
+II - A honra pessoal e o papel das mulheres era a chave para a estima social atribuída ao seu esposo e família ou o grupo social a que pertenciam.
+III - As poucas mulheres que atuavam diante dos homens não eram julgadas como honradas ou não segundo a forma como acatavam o código cultural referente à arrumação pessoal, um juízo que era extensivo a sua família ou grupo social.
+IV - As mulheres que não cumpriam o código cultural referente à arrumação pessoal eram qualificadas de indecentes e desonestas, algo que também se estendia à reputação do grupo que tolerava a infração das normas sociais.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Segundo 1 Cor 11, 28, é preciso “discernir o corpo”, isto é, “examinarmos a nós mesmos”.  Com o uso duplo do verbo “examinar”, destaca-se a obrigação que os cristãos têm de analisar se estão ou não contribuindo para que a igreja seja verdadeiramente o corpo de Cristo, uma comunidade solidária e de serviço. Paulo inclui-se neste “nós” e se une aos coríntios no autoexame que os coríntios devem fazer e no sofrimento que estão experimentando como consequência do juízo (11,30). Nas duas partes da exortação (11,27-29 e 11,31-32) o vocabulário forense evoca o ambiente de juízo, mas há também uma nota de esperança (11,32): o juízo e a correção de Deus têm o propósito de livrar-nos de sermos condenados com o mundo. A correção “pelo Senhor” é administrada por um Juiz que ao mesmo tempo torna possível a restauração do culpado. Ao referir-se ao juízo escatológico (11,32), evento que revelará e instaurará o amor e a justiça em toda a convivência humana, Paulo sublinha a obrigatoriedade de novas relações sociais.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - O verbo “examinar” destaca a obrigação que os cristãos têm de analisar se estão ou não contribuindo para que a igreja seja verdadeiramente o corpo de Cristo.
+II - Paulo não inclui-se neste “nós”, unindo-se aos coríntios no autoexame que deviam fazer e no sofrimento que experimentavam como consequência do juízo.
+III - O juízo e a correção de Deus têm o propósito de livrar-nos de sermos condenados com o mundo.
+IV - Ao referir-se ao juízo escatológico, evento que revelará e instaurará o amor e a justiça em toda a convivência humana, Paulo sublinha a “obrigatoriedade de novas relações sociais”.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A região que envolve a Síria e a Palestina é uma faixa relativamente estreita de terra entre o mar e o deserto, dividida em zonas por cordilheiras que vão do Norte ao Sul, que separam as planícies férteis, e em locais que apresentam obstáculos para viajar do interior para o litoral. Paulo passava por esta região em suas visitas a Jerusalém, cidade importante por ter sido a capital de Judá e cujo Templo a transformou num importante centro de culto. No início de sua carreira, Paulo viajou numa das rotas do interior, do norte de Jerusalém a Damasco e, daí, à Arábia. Mais tarde, em suas viagens missionárias utilizou a rota que passava pelo litoral. Era possível atravessar o deserto leste da região e o comércio de algumas cidades costeiras dependia das rotas das caravanas que iam até o Leste. A parte mais ao norte da região era habitável, mas os exércitos não a atravessavam. Campanhas militares do Egito ou contra este país tinham como rota a Síria e Palestina, tornando o controle desta área estrategicamente importante. (...) A região tornou-se um campo de batalha entre as duas dinastias que herdaram o império de Alexandre - os Ptolomeus, no Sul, e os selêucidas, no Norte - no período anterior ao domínio romano na região.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - A região que envolve a Síria e a Palestina é uma faixa relativamente estreita de terra entre o mar e o deserto.
+II - Paulo passava por esta região em suas visitas a Jerusalém, cidade importante por ter sido a capital de Judá e cujo Templo a transformou num importante centro de culto.
+III - Nas suas viagens missionárias utilizou apenas a rota que passava pelo interior da região.
+IV - Campanhas militares do Egito ou contra este país tinham como rota a Síria e Palestina, tornando o controle desta área estrategicamente importante.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>1 Cor 1,26-31 indica que Deus em Cristo realiza uma inversão das avaliações humanas referentes a status, realizações e sucesso ao descrever como, em sua sabedoria, Ele agiu na constituição da igreja de Corinto. O texto indica três dimensões através das quais o status social era medido: sabedoria, poder e nobreza. “Sabedoria”, “poder” e “nobreza” eram valorizados na sociedade greco-romana, mas, segundo Paulo, Deus vê as coisas de forma inversa, pois escolheu “as coisas loucas do mundo”, “as coisas fracas do mundo”, “as coisas desprezíveis” e “as coisas que nada são” para compor a comunidade cristã. A apresentação dos grupos sociais que compõem a comunidade destaca a ação de Deus e sujeita a estrutura social da igreja a uma interpretação da perspectiva da cruz. No texto de paulino, o uso das expressões “as coisas loucas”, “as coisas fracas”, “as “coisas desprezadas” e “as coisas que nada são” indica que a escolha das pessoas que compõem a comunidade está relacionada com a sabedoria e poder de Deus que se manifestam no Messias crucificado. A antítese “as coisas que nada são”/“as coisas que são” é o clímax da apresentação de Paulo, que destaca “as coisas desprezadas” e “as coisas que nada são” como objeto da eleição divina. Os “sábios” e “poderosos” são apresentados como objeto do verbo “envergonhar” e “as coisas que são” como objeto do verbo “destruir” (1,27-28).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Deus, em Cristo, realiza uma inversão das avaliações humanas referentes a status, realizações e sucesso ao descrever como, em sua sabedoria, Ele agiu na constituição da igreja de Corinto.
+II - “Sabedoria”, “poder” e “nobreza” tinham pouco valor na sociedade greco-romana.
+III - Deus escolheu não “as coisas loucas do mundo”, “as coisas fracas do mundo”, “as coisas desprezíveis” e “as coisas que nada são” para compor a comunidade cristã.
+IV - A apresentação dos grupos sociais que compõem a comunidade destaca a ação de Deus e sujeita a estrutura social da igreja a uma interpretação da perspectiva da cruz.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Em meados do primeiro século e. C., Corinto era um mercado religioso livre, igual a muitas cidades da parte oriental do Império Romano. O desejo de conhecer uma divindade universal motivava grande parte da busca religiosa do primeiro século. Entre os cultos de maior êxito estava o culto de Isis, deusa egípcia que foi convertida em uma divindade universal na sua passagem para a Grécia e Roma. Ainda que Isis tenha sido introduzida no mundo greco-romano em companhia de sua consorte Serápis, ela foi acolhida por um grande setor da população como divindade suprema do céu, mãe do tudo o que existe. A astrologia ofereceu também outra maneira de ampliar os alcances do antigo panteão grego: os deuses gregos foram identificados com certos planetas e estrelas, com o sol e a lua. O movimento pré-fixado dos corpos celestes foi interpretado como algo inflexível, que também caracterizava os deuses, cuja vontade era imposta aos seres humanos sem que estes pudessem alterá-la. Restavam somente acomodar-se a um destino pessoal e social predeterminado e evitar os perigos e danos já estabelecidos. Esta situação provocava também em grande parte da população a busca pela redenção. Não faltava novas religiões que ofereciam a redenção, entre elas o cristianismo.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - A cidade de Corinto da época de Paulo era um mercado religioso livre, igual a muitas cidades da parte oriental do Império Romano.
+II - O desejo de conhecer uma divindade universal motivava grande parte da busca religiosa do primeiro século.
+III - A deusa Isis e seu culto foram acolhidos por um grande setor da população como divindade suprema do céu, mãe do tudo o que existe.
+IV - A vontade dos deuses imposta aos seres humanos não era vista como o movimento pré-fixado dos corpos celestes, como algo inflexível que não era possível alterar.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Nas práticas religiosas tradicionais da Grécia clássica, as pitonisas ou profetisas dos oráculos indicavam o seu abandono total ao influxo do deus ou espírito mântico soltando o cabelo. Com a chegada de novas religiões orientais ao mundo grego durante o primeiro século, os cultos de tipo extático proliferaram, com muita participação feminina. Durante seus arrebatamentos frenéticos, as mulheres costumavam soltar os cabelos, possuídas pelo espírito do deus ou deusa. No caso do culto de Isis, deusa muito estimada em todo o Oriente do Império e com um centro importante em Corinto, as mulheres soltavam os cabelos nos cultos de louvor. O judaísmo contrastava de forma marcante com com estas práticas. Nas sinagogas, a tendência era as mulheres ficarem num lugar a elas reservado e seu recato devia manifestar-se por meio do uso do véu e do cabelo bem arrumado.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Nas práticas religiosas tradicionais da Grécia clássica, era comum as pitonisas ou profetisas dos oráculos soltarem os cabelos quando entravam em êxtase.
+II - Com a chegada de novas religiões orientais ao mundo grego durante o primeiro século, os cultos de tipo extático proliferaram, com muita participação feminina.
+III - O culto de Isis eram comum apenas em Corinto.
+IV - Na sinagoga, era também comum as mulheres judias soltarem os cabelos.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Paulo descreve sua experiência de conversão/vocação para proclamar Cristo aos gentios como parte da experiência de revelação (Gl 1,11-17). Fil 3 Paulo fala do “chamado que, do alto, Deus dirige em Jesus Cristo”. Na verdade, estas passagens não nos informam do real acontecimento da conversão/vocação, mas refletem a mudança radical nos valores e compromissos de Paulo quando recebeu a revelação de Cristo. Os relatos de Atos dos Apóstolos que se concentram nos acontecimentos que envolvem a conversão/vocação de Paulo são três: At 9,1-19; 22,1-21; 26,2-23. O primeiro relato, 9,1-19, é uma narrativa histórica. Os outros dois relatos, At 22,1-21; 26,2-23, fazem parte dos discursos de Paulo perante os judeus e o rei Agripa. Os eventos de At 9,1-19 marcam um ponto decisivo na narrativa de Atos. Lucas toma um fragmento de narrativa histórica e descreve um acontecimento de importância fundamental para a missão cristã. A narrativa dramática da conversão/vocação paulina é colocada imediatamente antes da narrativa de Cornélio e introduz o início da missão aos gentios. No início de At 9, Paulo é apresentado como um perseguidor da Igreja que se opõe completamente aos discípulos do Senhor.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Paulo não descreve sua experiência de conversão/vocação para proclamar Cristo aos gentios como parte da experiência reveladora.
+II - Gl 1,11-17 e Fil 3 não refletem uma mudança radical nos valores e compromissos de Paulo quando recebeu a revelação de Cristo.
+III - Os relatos de Atos dos Apóstolos concentram-se nos acontecimentos que envolvem a conversão/vocação de Paulo (At 9,1-19; 22,1-21; 26,2-23).
+IV - Ao apresentar a conversão/vocação de Paulo (At 9,1-19), Lucas descreve um acontecimento de importância fundamental para a missão cristã, pois a narrativa da conversão/vocação paulina é colocada imediatamente antes da narrativa de Cornélio e introduz o início da missão aos gentios.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Da Macedônia, Paulo foi para Atenas e Corinto, no Sul da Grécia. Paulo permaneceu dezoito meses em Corinto. Ali encontrou Áquila e Priscila, casal que havia saído de Roma quando Cláudio expulsara os judeus da cidade. Paulo foi também acusado por certo líder judaico da cidade perante Galião, que acabara de chegar à cidade, de propagar uma religião não autorizada pela lei romana. Galião não considerou que Paulo estava errado e ele continuou seu trabalho sem impedimento. Ao deixar Corinto, havia ali uma grande comunidade, embora nos anos seguintes tivesse de lidar com seus problemas de divisão.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - A presença de Priscila e Áquila em Corinto está relacionada com o decreto de expulsão dos judeus de Roma pelo imperador Cláudio.
+II - Paulo foi acusado por um líder judeu da cidade perante Galião de propagar uma religião não autorizada pela lei romana.
+III - Galião entendeu que Paulo estava errado, colocando impedimentos ao seu trabalho missionário.
+IV - Não há nenhuma ligação posterior de Paulo com igreja de Corinto.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A economia da cidade de Corinto tinha como base o assentamento de libertos e veteranos e baseava-se no comércio, uma situação que contrasta com a base econômica comum do mundo antigo, a posse da terra. Muitas pessoas fizeram fortuna, mas a vasta maioria da população beneficiava-se apenas indiretamente da riqueza da cidade, no sentido de que tinham mercado para sua produção artesanal ou seus serviços. Grande número de comerciantes e homens e mulheres de negócio viajavam frequentemente entre Corinto e as outras cidades do Império Romano. Vários membros da igreja de Corinto participavam nesta atividade comercial, seja como dirigentes de uma “casa” (Estéfanas, 16,15-18), seja como representantes mais humildes (os da casa de Cloe, 1,11). Ligado ao comércio havia bancos e em Corinto não faltava uma importante atividade financeira. Além da atividade comercial e financeira, Corinto tinha também uma importante produção artesanal. O “bronze de Corinto” deu fama à cidade e os artefatos que exportava eram estimados como ouro e pedras preciosas.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - A economia da cidade de Corinto baseava-se no assentamento de libertos e veteranos e no comércio, sendo igual à base econômica comum do mundo antigo.
+II - A vasta maioria da população de Corinto beneficiava-se diretamente da riqueza da cidade.
+III - Grande número de comerciantes e homens e mulheres de negócio viajavam frequentemente entre Corinto e as outras cidades do Império Romano.
+IV - O “bronze de Corinto” deu fama à cidade e os artefatos que exportava eram estimados como ouro e pedras preciosas.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>“Por essa ocasião, houve um tumulto bastante grave a respeito do caminho. Certo Demétrio, que era ourives, era fabricante de nichos de Ártemis, em prata, proporcionando aos artesãos não pouco lucro. Tendo-os reunido, bem como a outros que trabalhavam em no mesmo ramo, disse: ‘Amigos, sabeis que é deste ganho que provém o nosso bem-esta. Entretanto, vedes e ouvis que não somente em Éfeso, mas em quase toda a Ásia, este Paulo desencaminhou, com suas persuasões, uma multidão considerável [...] isto não só traz perigo de a nossa profissão cair em descrédito, mas também o próprio templo da grande deusa Ártemis perderá o seu prestígio, sendo logo despojada de sua majestade aquela que toda a Ásia adora’. Ouvindo isso, ficaram cheios de furor e puseram-se a gritar: “Grande é a Ártemis dos efésios” (At 19,23-28).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - O ministério de Paulo em Éfeso foi relativamente tranquilo.
+II - Demétrio, que era ourives, reuniu os demais artesãos, levando-os a colocarem-se contra Paulo.
+III - Eles tinham medo de que tanto o templo quanto a deusa Ártemis perdesse prestígio frente ao que acontecia na cidade como resultado da pregação de Paulo.
+IV - A pregação de Paulo foi também considerada como uma ameaça econômica aos comerciantes que, para viver, dependiam do culto a Ártemis.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A igreja de Antioquia, de maioria gentia, foi logo instituída. Seus membros mostraram seu grande caráter ao enviar uma soma de dinheiro para a Igreja-mãe de Jerusalém a fim de ajudá-la quando houve escassez de alimento na Judeia, designando Barnabé e Paulo para entregar a dádiva (At 11,27-30). Pode ter sido esta a ocasião do encontro que Paulo descreve em Gálatas 2,10. Barnabé e Paulo foram recebidos pelos líderes da Igreja de Jerusalém, Tiago (irmão do Senhor), Pedro e João. Ficou acertado que Barnabé e Paulo dariam continuidade à missão aos gentios e que os líderes de Jerusalém se dedicariam a testemunhar o Evangelho entre os judeus. O acordo escondia diversas ambiguidades que poderiam provocar tensão se não fosse mantida a plena confiança entre os dois lados. Atendendo ao pedido dos líderes de Jerusalém, Barnabé e Paulo prometeram lembrar-se dos pobres da Igreja-mãe. Paulo assumiu esta promessa com muita seriedade.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Os membros da igreja de Antioquia, de maioria gentia, mostraram seu grande caráter ao enviar algum dinheiro para a Igreja de Jerusalém a fim de ajudá-la quando ali houve escassez de alimento.
+II - Ficou acertado que Barnabé e Paulo dariam continuidade à missão aos gentios e que os líderes de Jerusalém se dedicariam a testemunhar o Evangelho entre os judeus.
+III - Não havia ambiguidades no acordo e a missão continuou sem tensão que quebrasse a confiança entre os dois lados.
+ IV - Barnabé e Paulo prometeram lembrar-se dos pobres da Igreja-mãe. Paulo assumiu também esta promessa com muita seriedade
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>14 - Paulo procurou anunciar o Evangelho “não em sabedoria de palavra, mas em demonstração do Espírito e poder”. A atitude de Paulo está demonstrada nas declarações: “não em exaltação de linguagem ou sabedoria” (2,1) e “não em palavras persuasivas de sabedoria” (2,4). Estas declarações, além de “não em sabedoria de palavra” (1,17) e “não em palavras ensinadas pela sabedoria humana” (2,13), referem-se a uma forma eloquente e conteúdo sábio que apontam para formas dos discursos prescritas pela retórica greco-romana e praticada pelos oradores da época de Paulo. Paulo rejeita este tipo de ensino e as formas de discurso construído apenas para impressionar os ouvintes como inapropriados para a pregação do Evangelho, concentrando-se apenas na proclamação da cruz. Ele depende do poder do Espírito que opera através do Evangelho proclamado e evita o uso de qualquer dinâmica de persuasão para gerar a fé naqueles que ouvem a mensagem. Ele confia na dinâmica da cruz para criar a fé.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Paulo procurou anunciar o Evangelho apelando somente aos padrões prescritos pela retórica greco-romana.
+II - Paulo aceita o ensino e as formas de discurso construído apenas para impressionar os ouvintes como apropriados à pregação do Evangelho.
+III - Paulo concentra-se apenas na “proclamação da cruz”, o elemento central da sua pregação.
+IV - Paulo confia na dinâmica da “proclamação da cruz” para criar a fé nos seus ouvintes.
+Está correto o que se afirma em:</t>
+  </si>
+  <si>
+    <t>No desenvolvimento de 1 Cor 13 Paulo menciona em primeiro lugar o dom de línguas: “Ainda que eu fale as línguas dos homens e dos anjos, se não tiver amor, sou como um bronze que soa ou um címbalo que retine” (13:1). Em segundo lugar, ele amplia sua perspectiva e inclui na discussão três dos carismas de 12,8-10: “profecia”, “conhecimento” e fé. Uma pessoa pode ter estes dons, mas se não tem amor, nada disso vale. Paulo amplia ainda mais esta perspectiva e ultrapassa a esfera dos dons ao oferecer o exemplo do sacrifício pessoal: “Ainda que eu distribua todos os meus bens” e “entregue o meu corpo para ser queimado”. Estas ações supõem um impulso de amor, mas se este está ausente, o exercício do dom nada vale. O que desqualifica a pessoa e invalida seu dom é um estilo de vida carente do amor, que desemboca no menosprezo às outras pessoas. Estas afirmações procuram impactar os coríntios, que tinham orgulho do seu elevado conhecimento espiritual, mas não respeitavam os mais fracos da comunidade cristã. O mesmo sucede com os discursos em línguas, pronunciados sem preocupação com compreensão e a edificação da Igreja (14,4-17). São sons ocos, como os sons do “bronze que soa ou do címbalo que tine”.
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - Uma pessoa pode ter diversos dons, mas se não tiver amor, nada disso vale..
+II - O que desqualifica a pessoa e invalida seu dom é um estilo de vida carente do amor, que desemboca no menosprezo às outras pessoas.
+III - Os coríntios tinham orgulho do seu elevado conhecimento espiritual, mas não respeitavam os mais fracos da comunidade cristã.
+IV - Os discursos em línguas, pronunciados sem preocupação com compreensão e a edificação da igreja, são válidos, pois estão relacionados apenas com o indivíduo.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>No mundo greco-romano do primeiro século havia associações voluntárias de tipo social e religioso. Numa sociedade cosmopolita, as relações tradicionais e as crenças religiosas em que se haviam fundamentado perdiam sua força. O povo buscava suprir esta falta agrupando-se de várias maneiras e para diversos propósitos. Estas associações privadas ou confrarias tinham membresia voluntária, com certa heterogeneidade: escravos, libertos e pessoas livres de pouco nível social, muitos deles estrangeiros. Em algumas associações havia somente homens. Em outros casos, as pessoas se uniam a um grupo particular para cultuar sua divindade. Outras associações proviam serviços fúnebres para seus membros e perpetuava sua memória mediante ceias comemorativas. Um tipo de associação chamada collegium pelos romanos agrupava pessoas de uma mesma profissão e de uma devoção religiosa, com o fim principal de promover atividades sociais para seus integrantes. O grupo podia também mobilizar-se ocasionalmente para defender algum interesse econômico (cf. At 19,23-41).
+De acordo com essa declaração, avalie as seguintes afirmações:
+I - No mundo greco-romano do primeiro século eram comuns as associações voluntárias de tipo social e religioso.
+II - As relações tradicionais e as crenças religiosas começaram a perder a sua força numa sociedade cosmopolita, fazendo com que o povo procurasse suprir esta falta agrupando-se de várias maneiras e para diversos propósitos.
+III - As associações privadas ou confrarias tinham membresia voluntária, com certa heterogeneidade: escravos, libertos e pessoas livres de pouco nível social, muitos deles estrangeiros.
+IV - Um collegium não agrupava pessoas de uma mesma profissão e de uma devoção religiosa.
+Está correto o que se afirma em:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Psicologia da Religião</t>
+  </si>
+  <si>
+    <t>Para Poter existe a loucura boa e loucura má, o que caracteriza uma e outra é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A loucura má estaria diretamente ligada a satanás que buscava se apoderar dos pecadores fracos e a loucura boa  seria  seitas e religiões que utilizam de seus ritos e cultos religiosos para impactarem de forma positiva o indivíduo e a sociedade.</t>
+  </si>
+  <si>
+    <t>A loucura má seriam as neuroses transformadas em uma religião, mas mesmo assim a construção patológica e as psicoses não podem alimentar-se de seus  delírios. Loucura boa seria o inverso do processo, porém o indivíduo não teria nossa desse tipo de loucura.</t>
+  </si>
+  <si>
+    <t>A loucura má  não se aproxima dos distúrbios mentais, enquanto outros podem levar as pessoas a se afastarem dele. A loucura boa aproxima as pessoas dos distúrbios mentais e assim desejarem a cura.</t>
+  </si>
+  <si>
+    <t>Todas as respostas estão erradas.</t>
+  </si>
+  <si>
+    <t>A pesquisa de Nina Rodrigues se mostra particularmente importante porque aborda o(s) seguintes aspectos:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Foi o primeiro a estudar a religiosidade de negros e pardos. O seu trabalho discorreu detalhadamente as diversas práticas, cultos e ritos e entidades sagradas de africanos e seus descendentes, tendo um especial valor no campo etnográﬁco.</t>
+  </si>
+  <si>
+    <t>Os estudos de Rodrigues no que concerne às fraturas psíquicas demonstraram como as crenças não se tornam poderosas e diminuem as dimensões sobre um terreno fértil de populações invulneráveis.</t>
+  </si>
+  <si>
+    <t>Não é importante identificar alguns traços racistas, conforme  os estudos de Rodrigues, posto que na religiosidade brasileira faz-se necessário o entendimento de cada poucas terminologias para o estudo de práticas terapêuticas.</t>
+  </si>
+  <si>
+    <t>Na opinião de Bastide o risco da religião pode ser sintetizado na seguinte frase:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A religião pode ser transformada em uma patologia por meio das neuroses, enquanto as psicoses poderiam alimentar os delírios.</t>
+  </si>
+  <si>
+    <t>A psicose não é formada de questões religiosas, mas de questões biológicas que o indivíduo carrega desde  sua formação interior, aparecendo quando ele se converte a alguma religião.</t>
+  </si>
+  <si>
+    <t>Tanto a neurose como a psicose não têm relação com a questão religiosa, estão ligadas apenas a questões que foram amplamente abordadas por Pinel na sua teoria da personalidade.</t>
+  </si>
+  <si>
+    <t>Dos elementos comuns existentes nas diferentes psicoterapias é INCORRETO afirmar que:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Existe confiança emocional do paciente em relação ao terapeuta.</t>
+  </si>
+  <si>
+    <t>Existe uma explicação plausível para o que o paciente esteja sentindo.</t>
+  </si>
+  <si>
+    <t>Os objetivos a que se propõe modificar devem ser claramente especificados.</t>
+  </si>
+  <si>
+    <t>O paciente não acredita na capacidade do terapeuta.</t>
+  </si>
+  <si>
+    <t>É importante compreender o adjetivo “místico" porque ele permite a seguinte compreensão:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A compreensão do adjetivo “místico” permite desligar cérebro e alma.</t>
+  </si>
+  <si>
+    <t>A compreensão do adjetivo "místico" permite interligar neurofisiologia à física quântica.</t>
+  </si>
+  <si>
+    <t>A compreensão do adjetivo “místico” permite compreender corpo, alma e espírito.</t>
+  </si>
+  <si>
+    <t>A compreensão do adjetivo “místico” permite entender a filosofia grega.</t>
+  </si>
+  <si>
+    <t>O seguimento científico que já constatou diversos avanços no entendimento cerebral e que  há certezas que podem ajudar a entender o homem e o fenômeno religioso, é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A neurofisiologia.</t>
+  </si>
+  <si>
+    <t>A neuropsiquiatria.</t>
+  </si>
+  <si>
+    <t>A neuroteologia.</t>
+  </si>
+  <si>
+    <t>Para Esquirol a monomania apresenta duas causas principais que seriam de origem:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Endógena e exógena.</t>
+  </si>
+  <si>
+    <t>Familiar e social.</t>
+  </si>
+  <si>
+    <t>Individual e psíquica.</t>
+  </si>
+  <si>
+    <t>Físicas e mentais.</t>
+  </si>
+  <si>
+    <t>Para H.F. Dunbar fatores emocionais estão ligados a quase todas as doenças.  Dentre os quatro fatores estudados o que mais causa tensão emocional, afetando questões ligadas à religiosidade é aquele que promove:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Sentimentos.</t>
+  </si>
+  <si>
+    <t>Sinestesia.</t>
+  </si>
+  <si>
+    <t>Super-estimulação ou contração.</t>
+  </si>
+  <si>
+    <t>Nenhuma das alternativas.</t>
+  </si>
+  <si>
+    <t>Pode ser considerado um dos quatro pontos como se dava o relacionamento entre religião e ciência, do ponto de vista da neurociência a seguinte afirmativa: ( Marque a correta).   
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Religiosos e cientistas firmam uma dependência entre os dois tipos de conhecimento.</t>
+  </si>
+  <si>
+    <t>O grande antagonismo entre as visões religiosas e científicas.</t>
+  </si>
+  <si>
+    <t>A consciência passou a ser percebida como "capaz de dar sentido e de integrar tudo”, menos as ciências humanas.</t>
+  </si>
+  <si>
+    <t>As ciências da computação propiciaram avanços significativos para a neurologia e a neuropsiquiatria.</t>
+  </si>
+  <si>
+    <t>É possível encontrar diferentes quantidades de instintos quanto “situações às quais os organismos reagem”. Este pensamento está associado a:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>McDougall.</t>
+  </si>
+  <si>
+    <t>Perry.</t>
+  </si>
+  <si>
+    <t>Thorndike.</t>
+  </si>
+  <si>
+    <t>Qual a tarefa terapêutica da religião?
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Promover a saúde e a integridade mental dos fieis.</t>
+  </si>
+  <si>
+    <t>Aproximar o entendimento entre magia e religião.</t>
+  </si>
+  <si>
+    <t>A religião não deve pelo tentar legitimar a fé do indivíduo que a ela se achega, pois isso vem de cada um.</t>
+  </si>
+  <si>
+    <t>O fanatismo religioso é um grave problema que vem assolando a sociedade moderna. Do ponto de vista patológico pode-se afirmar que ele:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O ponto de vista patológico discute a interferência no comportamento “normal” do indivíduo, frente a sua dedicação excessiva a fé, poder, união, autossacrifício.</t>
+  </si>
+  <si>
+    <t>Do ponto de vista patológico o fanatismo religioso não interfere no estado psíquico do indivíduo que tem fé.</t>
+  </si>
+  <si>
+    <t>Do ponto de vista patológico a discussão não leva em consideração elementos externos ao ser humano.</t>
+  </si>
+  <si>
+    <t>Do ponto de vista patológico pessoas sadias não apresentarão qualquer nível de doença mental.</t>
+  </si>
+  <si>
+    <t>Quatro etapas podem ser entendidas na dinâmica de nos tornarmos consciente:
+Dessas quatro a integração de propósito é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Algo precisa ser executado quando se tem consciência que o novo dia demanda novas possibilidades, considerando o passado e projetando alvos futuros.</t>
+  </si>
+  <si>
+    <t>É o grau de seletividade de acordo com o estímulo recebido, dando relevância a estes ou não.</t>
+  </si>
+  <si>
+    <t>Busca-se informação para que o incomodo seja superado o mal estar vencido com ajuda de medicamentos prescritos pelo médico.</t>
+  </si>
+  <si>
+    <t>Aquela em que as percepções sejam padronizadas totalmente pelos significados adquiridos durante a sessão de análise.</t>
+  </si>
+  <si>
+    <t>A diferença entre o pensamento de Jung em relação ao pensamento de Freud, com respeito a religião é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Para Jung a religião é capaz de revelar o que existe de mais profundo no ser humano, aliado ao que este pode associar de significado ao mundo em que vive.</t>
+  </si>
+  <si>
+    <t>Para Freud a religião não revela nada, apenas permite que o ser humano se sinta melhor frente a sua religiosidade.</t>
+  </si>
+  <si>
+    <t>O ser humano necessita da dimensão religiosa para preencher o significado de sua existência.</t>
+  </si>
+  <si>
+    <t>Os antigos psicólogos cultivaram uma forma de sabedoria que pudesse analisar as vivências religiosas de sua época. Esta frase está associada a:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Perspectiva Hindu.</t>
+  </si>
+  <si>
+    <t>Perspectiva Egípcia.</t>
+  </si>
+  <si>
+    <t>Perspectiva Hebraica.</t>
+  </si>
+  <si>
+    <t>Perspectiva Judáica.</t>
+  </si>
+  <si>
+    <t>É possível estabelecer um diálogo entre Teologia e Psicologia devido a:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A Teologia consegue perceber que as ciências naturais também têm algo a dizer sobre o homem e suas relações sociais até mesmo com o que é transcendente. Daí então ser possível estabelecer um diálogo entre a Teologia e a Psicologia, pois está também procura entender as complexidades da natureza humana, seus conflitos e dinâmicas existenciais.</t>
+  </si>
+  <si>
+    <t>A abordagem científica não  tem como tarefa principal  juntar, classificar e dispor em ordem os fatos por ela analisados, de forma subjetiva, descritiva e narrativa, busca progredir em sua forma de pesquisa e abordagem somente com o empirismo moderno.</t>
+  </si>
+  <si>
+    <t>É de interesse da Psicologia da religião entender como a religião torna-se relevante para as pessoas os que creem, independente de  como esse saber se relaciona com outros estudos científicos.</t>
+  </si>
+  <si>
+    <t>Organização social, costumes e padrões culturais não contribuem para a significação psicológica da religião, posto que esta se preocupa apenas com o desenvolvimento espiritual do ser humano.</t>
+  </si>
+  <si>
+    <t>A teoria psicanalítica de Freud tenta explica a experiência religiosa a partir de elementos distintos. Um deles deve considerar que:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Observando os conflitos humanos no decorrer de seu desenvolvimento psicológico, e também das relações estabelecidas desde a infância com o mundo que a rodeia, a religião poderá ser explicada.</t>
+  </si>
+  <si>
+    <t>Ela não admite que no interior de cada personalidade exista uma luta entre energias conflitantes, pelo contrário, as energias são equilibradas pelo inconsciente.</t>
+  </si>
+  <si>
+    <t>É de seu interesse analisar aspectos do relacionamento do homem com o homem, sendo este apenas  um dos motivos secundários de pesquisa  do pai da psicanálise que não interfere na religião.</t>
+  </si>
+  <si>
+    <t>A libido não é, dentre tantos aspectos geradores de conflitos nos vários sistemas religiosos, o que mais causa desconforto até hoje, nas comunidades ditas cristãs.</t>
+  </si>
+  <si>
+    <t>O pensamento de Pinel e o de Freud podem ser considerados convergentes porque:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O tratamento da loucura religiosa só poderia se dar pela desconstrução de elementos religiosos, objetos, livros e quaisquer elementos que estejam ligados à religião.</t>
+  </si>
+  <si>
+    <t>O fator irrelevante na gênese da alienação mental era o fanatismo religioso, pois ele não interfere nas doenças psicológicas, especialmente nas subjetivas.</t>
+  </si>
+  <si>
+    <t>A forma utilizada pelo demônio seria fazer com que as pessoas crescem que as vozes que eles ouviam eram do próprio deus.</t>
+  </si>
+  <si>
+    <t>A existência de seitas e religiões que utilizam de seus ritos e cultos religiosos para impactarem de forma positiva o indivíduo e a sociedade.</t>
+  </si>
+  <si>
+    <t>O que mais fez com que Freud caísse no conceito de vários teólogos foi:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Afirmar que as pulsões sexuais surgem na mais tenra infância e acompanha o ser humano até sua morte.</t>
+  </si>
+  <si>
+    <t>Afirmar a morte de Deus.</t>
+  </si>
+  <si>
+    <t>Desconsiderar a fé de cada indivíduo.</t>
+  </si>
+  <si>
+    <t>Acreditar que a ciência eliminaria a religião.</t>
+  </si>
+  <si>
+    <t>Dos personagens importantes no estudo da psicologia aparece o nome de BUDA isto porque:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Ele cria uma teoria semelhante a de Freud, em que a causa do sofrimento é o desejo e que o esclarecimento ou a compreensão é essencial para a cura.</t>
+  </si>
+  <si>
+    <t>Porque era um sábio e não se deixou levar pelas aparências de seu tempo, nem pelo seu status social.</t>
+  </si>
+  <si>
+    <t>Buda desenvolveu uma nova técnica de abordagem do inconsciente, por isso sua teoria é relevante para o estudo da religião.</t>
+  </si>
+  <si>
+    <t>O budismo é uma religião mais antiga que outras e isso coloca Buda numa posição de destaque frente a outras divindades.</t>
+  </si>
+  <si>
+    <t>Após o estudo das quatro etapas  dinâmicas de conscientização ( 1 - Consciência ou atenção seletiva. 2- Processo de pesquisa  3 -  Julgamento ou reconhecimento 4 - Integração de propósito) é possível afirmar que:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Algumas tomadas de consciência estão associadas ao estímulo religioso e também procura pelo significado religioso.</t>
+  </si>
+  <si>
+    <t>Nem todos os estímulos religiosos fazem parte da consciência natural embora o conteúdo tenha as suas possíveis variações.</t>
+  </si>
+  <si>
+    <t>É natural que a sociedade construa a sua realidade a partir do pensamento sobre suas esperanças que os outros nela depositam.</t>
+  </si>
+  <si>
+    <t>A possessão é considerada um fenômeno religioso normal numa perspectiva, racial, culturalista e psicodinâmica. Este pensamento é de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Lewis</t>
+  </si>
+  <si>
+    <t>Higard.</t>
+  </si>
+  <si>
+    <t>Arthur Ramos.</t>
+  </si>
+  <si>
+    <t>Schumaker.</t>
+  </si>
+  <si>
+    <t>A palavra “religião”, por ser uma palavra de variadas interpretações, pode mesmo assim ser segmentada em alguns aspectos. Indique, nas alternativas apresentadas, quais delas NÃO podem fazer parte dessa interpretação:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Sistema, símbolo, percepção.</t>
+  </si>
+  <si>
+    <t>Expressão, controle, conhecimento.</t>
+  </si>
+  <si>
+    <t>Sentido, existência, humana.</t>
+  </si>
+  <si>
+    <t>Matemática, computação, finitude.</t>
+  </si>
+  <si>
+    <t>As percepções religiosas perpassam a condição sensorial do ser humano.
+Esta frase é associada ao pensamento de:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Emil Brunner.</t>
+  </si>
+  <si>
+    <t>Willian James.</t>
+  </si>
+  <si>
+    <t>J.S.Bruner.</t>
+  </si>
+  <si>
+    <t>Rudolf Otto.</t>
+  </si>
+  <si>
+    <t>Considerando a Filosofia e a Teologia é certo afirmar que:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Ambas procuram descobrir a verdade existente na realidade como um todo.</t>
+  </si>
+  <si>
+    <t>A Teologia consegue perceber que as ciências naturais também têm algo a dizer sobre o homem e suas relações sociais até mesmo com o que é transcendente.</t>
+  </si>
+  <si>
+    <t>Na questão filosófica o que está em evidência é a interpretação da realidade a que a religião se refere.</t>
+  </si>
+  <si>
+    <t>O pensamento de Otto Rank sobre a religião se aproxima mais do que pensa Jung do que pensa o próprio Freud, isto porque:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>O homem nasce além da psicologia e morre além dela, mas pode viver além dela somente através de usa própria experiência vital – em termos religiosos, através da revelação, conversão e novo nascimento.</t>
+  </si>
+  <si>
+    <t>Jung admite que a religião ou experiência religiosa  seja ilusão, criação de uma mente doentia, cheia uma neurose obsessiva compulsiva. E Freud pensa o mesmo que Jung.</t>
+  </si>
+  <si>
+    <t>Em se tratando de conduta religiosa as questão que envolve a crença na imortalidade da alma, que tem sua experiência vitalizante, estão mais próximas das teorias freudianas que junguianas.</t>
+  </si>
+  <si>
+    <t>Quando se pensa a psicologia da religião um dos elementos principais a ser observado é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A pessoa.</t>
+  </si>
+  <si>
+    <t>O local.</t>
+  </si>
+  <si>
+    <t>A história.</t>
+  </si>
+  <si>
+    <t>A motivação.</t>
+  </si>
+  <si>
+    <t>É a mais antiga literatura indo-européia,  sua origem segundo a tradição é datada de 3102 a. C. Esta afirmativa é aplicada aos escritos:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Do Antigo Testamento.</t>
+  </si>
+  <si>
+    <t>Aos Vedas.</t>
+  </si>
+  <si>
+    <t>Ao Escritos de Buda.</t>
+  </si>
+  <si>
+    <t>Aos escritos de Jeremias.</t>
+  </si>
+  <si>
+    <t>O que pode revelar um erotismo disfarçado em mística, nas palavras de Nina Rodrigues é:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>A estilística.</t>
+  </si>
+  <si>
+    <t>A sinestesia.</t>
+  </si>
+  <si>
+    <t>O simbolismo.</t>
+  </si>
+  <si>
+    <t>A metáfora.</t>
+  </si>
+  <si>
+    <t>Em se tratando dos hemisférios cerebrais, na neurofisiologia o uso de símbolos mais que palavras é, portanto mais intuitivo, analógico, espacial, holístico, características mais presentes nos povos de raças e culturas orientais e suas religiões (Hinduísmo, Budismo, Xintoísmo, Taoismo). Este é um atributo do:
+Escolha uma opção:</t>
+  </si>
+  <si>
+    <t>Hemisfério Direito.</t>
+  </si>
+  <si>
+    <t>Hemisfério Esquerdo.</t>
+  </si>
+  <si>
+    <t>Inconsciente.</t>
   </si>
 </sst>
 </file>
@@ -2198,7 +4109,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2230,6 +4141,12 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2535,7 +4452,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="18.0"/>
     <col customWidth="1" min="2" max="2" width="53.63"/>
-    <col customWidth="1" min="3" max="3" width="22.88"/>
+    <col customWidth="1" min="3" max="3" width="29.13"/>
     <col customWidth="1" min="4" max="4" width="46.0"/>
     <col customWidth="1" min="5" max="5" width="49.5"/>
     <col customWidth="1" min="6" max="6" width="29.88"/>
@@ -8086,13 +10003,27 @@
       <c r="Z132" s="5"/>
     </row>
     <row r="133">
-      <c r="A133" s="5"/>
-      <c r="B133" s="5"/>
-      <c r="C133" s="5"/>
-      <c r="D133" s="5"/>
-      <c r="E133" s="5"/>
-      <c r="F133" s="5"/>
-      <c r="G133" s="5"/>
+      <c r="A133" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="F133" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
@@ -8114,13 +10045,27 @@
       <c r="Z133" s="5"/>
     </row>
     <row r="134">
-      <c r="A134" s="5"/>
-      <c r="B134" s="5"/>
-      <c r="C134" s="5"/>
-      <c r="D134" s="5"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="5"/>
-      <c r="G134" s="5"/>
+      <c r="A134" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="G134" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
@@ -8142,13 +10087,27 @@
       <c r="Z134" s="5"/>
     </row>
     <row r="135">
-      <c r="A135" s="5"/>
-      <c r="B135" s="5"/>
-      <c r="C135" s="5"/>
-      <c r="D135" s="5"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="5"/>
-      <c r="G135" s="5"/>
+      <c r="A135" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="G135" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
@@ -8170,13 +10129,27 @@
       <c r="Z135" s="5"/>
     </row>
     <row r="136">
-      <c r="A136" s="5"/>
-      <c r="B136" s="5"/>
-      <c r="C136" s="5"/>
-      <c r="D136" s="5"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="5"/>
-      <c r="G136" s="5"/>
+      <c r="A136" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
@@ -8198,13 +10171,27 @@
       <c r="Z136" s="5"/>
     </row>
     <row r="137">
-      <c r="A137" s="5"/>
-      <c r="B137" s="5"/>
-      <c r="C137" s="5"/>
-      <c r="D137" s="5"/>
-      <c r="E137" s="5"/>
-      <c r="F137" s="5"/>
-      <c r="G137" s="5"/>
+      <c r="A137" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
@@ -8226,13 +10213,27 @@
       <c r="Z137" s="5"/>
     </row>
     <row r="138">
-      <c r="A138" s="5"/>
-      <c r="B138" s="5"/>
-      <c r="C138" s="5"/>
-      <c r="D138" s="5"/>
-      <c r="E138" s="5"/>
-      <c r="F138" s="5"/>
-      <c r="G138" s="5"/>
+      <c r="A138" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="G138" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
@@ -8254,13 +10255,27 @@
       <c r="Z138" s="5"/>
     </row>
     <row r="139">
-      <c r="A139" s="5"/>
-      <c r="B139" s="5"/>
-      <c r="C139" s="5"/>
-      <c r="D139" s="5"/>
-      <c r="E139" s="5"/>
-      <c r="F139" s="5"/>
-      <c r="G139" s="5"/>
+      <c r="A139" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
@@ -8282,13 +10297,27 @@
       <c r="Z139" s="5"/>
     </row>
     <row r="140">
-      <c r="A140" s="5"/>
-      <c r="B140" s="5"/>
-      <c r="C140" s="5"/>
-      <c r="D140" s="5"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="5"/>
-      <c r="G140" s="5"/>
+      <c r="A140" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
@@ -8310,13 +10339,27 @@
       <c r="Z140" s="5"/>
     </row>
     <row r="141">
-      <c r="A141" s="5"/>
-      <c r="B141" s="5"/>
-      <c r="C141" s="5"/>
-      <c r="D141" s="5"/>
-      <c r="E141" s="5"/>
-      <c r="F141" s="5"/>
-      <c r="G141" s="5"/>
+      <c r="A141" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
@@ -8338,13 +10381,27 @@
       <c r="Z141" s="5"/>
     </row>
     <row r="142">
-      <c r="A142" s="5"/>
-      <c r="B142" s="5"/>
-      <c r="C142" s="5"/>
-      <c r="D142" s="5"/>
-      <c r="E142" s="5"/>
-      <c r="F142" s="5"/>
-      <c r="G142" s="5"/>
+      <c r="A142" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
@@ -8366,13 +10423,27 @@
       <c r="Z142" s="5"/>
     </row>
     <row r="143">
-      <c r="A143" s="5"/>
-      <c r="B143" s="5"/>
-      <c r="C143" s="5"/>
-      <c r="D143" s="5"/>
-      <c r="E143" s="5"/>
-      <c r="F143" s="5"/>
-      <c r="G143" s="5"/>
+      <c r="A143" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
@@ -8394,13 +10465,27 @@
       <c r="Z143" s="5"/>
     </row>
     <row r="144">
-      <c r="A144" s="5"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="5"/>
-      <c r="D144" s="5"/>
-      <c r="E144" s="5"/>
-      <c r="F144" s="5"/>
-      <c r="G144" s="5"/>
+      <c r="A144" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
@@ -8422,13 +10507,27 @@
       <c r="Z144" s="5"/>
     </row>
     <row r="145">
-      <c r="A145" s="5"/>
-      <c r="B145" s="5"/>
-      <c r="C145" s="5"/>
-      <c r="D145" s="5"/>
-      <c r="E145" s="5"/>
-      <c r="F145" s="5"/>
-      <c r="G145" s="5"/>
+      <c r="A145" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
@@ -8450,13 +10549,27 @@
       <c r="Z145" s="5"/>
     </row>
     <row r="146">
-      <c r="A146" s="5"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="5"/>
-      <c r="D146" s="5"/>
-      <c r="E146" s="5"/>
-      <c r="F146" s="5"/>
-      <c r="G146" s="5"/>
+      <c r="A146" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
@@ -8478,13 +10591,27 @@
       <c r="Z146" s="5"/>
     </row>
     <row r="147">
-      <c r="A147" s="5"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="5"/>
-      <c r="D147" s="5"/>
-      <c r="E147" s="5"/>
-      <c r="F147" s="5"/>
-      <c r="G147" s="5"/>
+      <c r="A147" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
@@ -8506,13 +10633,27 @@
       <c r="Z147" s="5"/>
     </row>
     <row r="148">
-      <c r="A148" s="5"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="5"/>
-      <c r="D148" s="5"/>
-      <c r="E148" s="5"/>
-      <c r="F148" s="5"/>
-      <c r="G148" s="5"/>
+      <c r="A148" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
@@ -8534,13 +10675,27 @@
       <c r="Z148" s="5"/>
     </row>
     <row r="149">
-      <c r="A149" s="5"/>
-      <c r="B149" s="5"/>
-      <c r="C149" s="5"/>
-      <c r="D149" s="5"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="5"/>
-      <c r="G149" s="5"/>
+      <c r="A149" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
@@ -8562,13 +10717,27 @@
       <c r="Z149" s="5"/>
     </row>
     <row r="150">
-      <c r="A150" s="5"/>
-      <c r="B150" s="5"/>
-      <c r="C150" s="5"/>
-      <c r="D150" s="5"/>
-      <c r="E150" s="5"/>
-      <c r="F150" s="5"/>
-      <c r="G150" s="5"/>
+      <c r="A150" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
@@ -8590,13 +10759,27 @@
       <c r="Z150" s="5"/>
     </row>
     <row r="151">
-      <c r="A151" s="5"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="5"/>
-      <c r="D151" s="5"/>
-      <c r="E151" s="5"/>
-      <c r="F151" s="5"/>
-      <c r="G151" s="5"/>
+      <c r="A151" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
@@ -8618,13 +10801,27 @@
       <c r="Z151" s="5"/>
     </row>
     <row r="152">
-      <c r="A152" s="5"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="5"/>
-      <c r="D152" s="5"/>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5"/>
-      <c r="G152" s="5"/>
+      <c r="A152" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="G152" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
@@ -8646,13 +10843,27 @@
       <c r="Z152" s="5"/>
     </row>
     <row r="153">
-      <c r="A153" s="5"/>
-      <c r="B153" s="5"/>
-      <c r="C153" s="5"/>
-      <c r="D153" s="5"/>
-      <c r="E153" s="5"/>
-      <c r="F153" s="5"/>
-      <c r="G153" s="5"/>
+      <c r="A153" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="G153" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
@@ -8674,13 +10885,27 @@
       <c r="Z153" s="5"/>
     </row>
     <row r="154">
-      <c r="A154" s="5"/>
-      <c r="B154" s="5"/>
-      <c r="C154" s="5"/>
-      <c r="D154" s="5"/>
-      <c r="E154" s="5"/>
-      <c r="F154" s="5"/>
-      <c r="G154" s="5"/>
+      <c r="A154" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>690</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
@@ -8702,13 +10927,27 @@
       <c r="Z154" s="5"/>
     </row>
     <row r="155">
-      <c r="A155" s="5"/>
-      <c r="B155" s="5"/>
-      <c r="C155" s="5"/>
-      <c r="D155" s="5"/>
-      <c r="E155" s="5"/>
-      <c r="F155" s="5"/>
-      <c r="G155" s="5"/>
+      <c r="A155" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="G155" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H155" s="5"/>
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
@@ -8730,13 +10969,27 @@
       <c r="Z155" s="5"/>
     </row>
     <row r="156">
-      <c r="A156" s="5"/>
-      <c r="B156" s="5"/>
-      <c r="C156" s="5"/>
-      <c r="D156" s="5"/>
-      <c r="E156" s="5"/>
-      <c r="F156" s="5"/>
-      <c r="G156" s="5"/>
+      <c r="A156" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H156" s="5"/>
       <c r="I156" s="5"/>
       <c r="J156" s="5"/>
@@ -8758,13 +11011,27 @@
       <c r="Z156" s="5"/>
     </row>
     <row r="157">
-      <c r="A157" s="5"/>
-      <c r="B157" s="5"/>
-      <c r="C157" s="5"/>
-      <c r="D157" s="5"/>
-      <c r="E157" s="5"/>
-      <c r="F157" s="5"/>
-      <c r="G157" s="5"/>
+      <c r="A157" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
@@ -8786,13 +11053,27 @@
       <c r="Z157" s="5"/>
     </row>
     <row r="158">
-      <c r="A158" s="5"/>
-      <c r="B158" s="5"/>
-      <c r="C158" s="5"/>
-      <c r="D158" s="5"/>
-      <c r="E158" s="5"/>
-      <c r="F158" s="5"/>
-      <c r="G158" s="5"/>
+      <c r="A158" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="G158" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H158" s="5"/>
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
@@ -8814,13 +11095,27 @@
       <c r="Z158" s="5"/>
     </row>
     <row r="159">
-      <c r="A159" s="5"/>
-      <c r="B159" s="5"/>
-      <c r="C159" s="5"/>
-      <c r="D159" s="5"/>
-      <c r="E159" s="5"/>
-      <c r="F159" s="5"/>
-      <c r="G159" s="5"/>
+      <c r="A159" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H159" s="5"/>
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
@@ -8842,13 +11137,27 @@
       <c r="Z159" s="5"/>
     </row>
     <row r="160">
-      <c r="A160" s="5"/>
-      <c r="B160" s="5"/>
-      <c r="C160" s="5"/>
-      <c r="D160" s="5"/>
-      <c r="E160" s="5"/>
-      <c r="F160" s="5"/>
-      <c r="G160" s="5"/>
+      <c r="A160" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="G160" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H160" s="5"/>
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
@@ -8870,13 +11179,27 @@
       <c r="Z160" s="5"/>
     </row>
     <row r="161">
-      <c r="A161" s="5"/>
-      <c r="B161" s="5"/>
-      <c r="C161" s="5"/>
-      <c r="D161" s="5"/>
-      <c r="E161" s="5"/>
-      <c r="F161" s="5"/>
-      <c r="G161" s="5"/>
+      <c r="A161" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H161" s="5"/>
       <c r="I161" s="5"/>
       <c r="J161" s="5"/>
@@ -8898,13 +11221,27 @@
       <c r="Z161" s="5"/>
     </row>
     <row r="162">
-      <c r="A162" s="5"/>
-      <c r="B162" s="5"/>
-      <c r="C162" s="5"/>
-      <c r="D162" s="5"/>
-      <c r="E162" s="5"/>
-      <c r="F162" s="5"/>
-      <c r="G162" s="5"/>
+      <c r="A162" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
       <c r="J162" s="5"/>
@@ -8926,13 +11263,27 @@
       <c r="Z162" s="5"/>
     </row>
     <row r="163">
-      <c r="A163" s="5"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="5"/>
-      <c r="D163" s="5"/>
-      <c r="E163" s="5"/>
-      <c r="F163" s="5"/>
-      <c r="G163" s="5"/>
+      <c r="A163" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H163" s="5"/>
       <c r="I163" s="5"/>
       <c r="J163" s="5"/>
@@ -8954,13 +11305,27 @@
       <c r="Z163" s="5"/>
     </row>
     <row r="164">
-      <c r="A164" s="5"/>
-      <c r="B164" s="5"/>
-      <c r="C164" s="5"/>
-      <c r="D164" s="5"/>
-      <c r="E164" s="5"/>
-      <c r="F164" s="5"/>
-      <c r="G164" s="5"/>
+      <c r="A164" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H164" s="5"/>
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
@@ -8982,13 +11347,27 @@
       <c r="Z164" s="5"/>
     </row>
     <row r="165">
-      <c r="A165" s="5"/>
-      <c r="B165" s="5"/>
-      <c r="C165" s="5"/>
-      <c r="D165" s="5"/>
-      <c r="E165" s="5"/>
-      <c r="F165" s="5"/>
-      <c r="G165" s="5"/>
+      <c r="A165" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="G165" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H165" s="5"/>
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
@@ -9010,13 +11389,27 @@
       <c r="Z165" s="5"/>
     </row>
     <row r="166">
-      <c r="A166" s="5"/>
-      <c r="B166" s="5"/>
-      <c r="C166" s="5"/>
-      <c r="D166" s="5"/>
-      <c r="E166" s="5"/>
-      <c r="F166" s="5"/>
-      <c r="G166" s="5"/>
+      <c r="A166" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="G166" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H166" s="5"/>
       <c r="I166" s="5"/>
       <c r="J166" s="5"/>
@@ -9038,13 +11431,27 @@
       <c r="Z166" s="5"/>
     </row>
     <row r="167">
-      <c r="A167" s="5"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="5"/>
-      <c r="D167" s="5"/>
-      <c r="E167" s="5"/>
-      <c r="F167" s="5"/>
-      <c r="G167" s="5"/>
+      <c r="A167" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="G167" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H167" s="5"/>
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
@@ -9066,13 +11473,27 @@
       <c r="Z167" s="5"/>
     </row>
     <row r="168">
-      <c r="A168" s="5"/>
-      <c r="B168" s="5"/>
-      <c r="C168" s="5"/>
-      <c r="D168" s="5"/>
-      <c r="E168" s="5"/>
-      <c r="F168" s="5"/>
-      <c r="G168" s="5"/>
+      <c r="A168" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="G168" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
@@ -9094,13 +11515,27 @@
       <c r="Z168" s="5"/>
     </row>
     <row r="169">
-      <c r="A169" s="5"/>
-      <c r="B169" s="5"/>
-      <c r="C169" s="5"/>
-      <c r="D169" s="5"/>
-      <c r="E169" s="5"/>
-      <c r="F169" s="5"/>
-      <c r="G169" s="5"/>
+      <c r="A169" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="G169" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H169" s="5"/>
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
@@ -9122,13 +11557,27 @@
       <c r="Z169" s="5"/>
     </row>
     <row r="170">
-      <c r="A170" s="5"/>
-      <c r="B170" s="5"/>
-      <c r="C170" s="5"/>
-      <c r="D170" s="5"/>
-      <c r="E170" s="5"/>
-      <c r="F170" s="5"/>
-      <c r="G170" s="5"/>
+      <c r="A170" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="G170" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
@@ -9150,13 +11599,27 @@
       <c r="Z170" s="5"/>
     </row>
     <row r="171">
-      <c r="A171" s="5"/>
-      <c r="B171" s="5"/>
-      <c r="C171" s="5"/>
-      <c r="D171" s="5"/>
-      <c r="E171" s="5"/>
-      <c r="F171" s="5"/>
-      <c r="G171" s="5"/>
+      <c r="A171" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="F171" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="G171" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
@@ -9178,13 +11641,27 @@
       <c r="Z171" s="5"/>
     </row>
     <row r="172">
-      <c r="A172" s="5"/>
-      <c r="B172" s="5"/>
-      <c r="C172" s="5"/>
-      <c r="D172" s="5"/>
-      <c r="E172" s="5"/>
-      <c r="F172" s="5"/>
-      <c r="G172" s="5"/>
+      <c r="A172" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="G172" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
@@ -9206,13 +11683,27 @@
       <c r="Z172" s="5"/>
     </row>
     <row r="173">
-      <c r="A173" s="5"/>
-      <c r="B173" s="5"/>
-      <c r="C173" s="5"/>
-      <c r="D173" s="5"/>
-      <c r="E173" s="5"/>
-      <c r="F173" s="5"/>
-      <c r="G173" s="5"/>
+      <c r="A173" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="G173" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
@@ -9234,13 +11725,27 @@
       <c r="Z173" s="5"/>
     </row>
     <row r="174">
-      <c r="A174" s="5"/>
-      <c r="B174" s="5"/>
-      <c r="C174" s="5"/>
-      <c r="D174" s="5"/>
-      <c r="E174" s="5"/>
-      <c r="F174" s="5"/>
-      <c r="G174" s="5"/>
+      <c r="A174" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="G174" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H174" s="5"/>
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
@@ -9262,13 +11767,27 @@
       <c r="Z174" s="5"/>
     </row>
     <row r="175">
-      <c r="A175" s="5"/>
-      <c r="B175" s="5"/>
-      <c r="C175" s="5"/>
-      <c r="D175" s="5"/>
-      <c r="E175" s="5"/>
-      <c r="F175" s="5"/>
-      <c r="G175" s="5"/>
+      <c r="A175" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="G175" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H175" s="5"/>
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
@@ -9290,13 +11809,27 @@
       <c r="Z175" s="5"/>
     </row>
     <row r="176">
-      <c r="A176" s="5"/>
-      <c r="B176" s="5"/>
-      <c r="C176" s="5"/>
-      <c r="D176" s="5"/>
-      <c r="E176" s="5"/>
-      <c r="F176" s="5"/>
-      <c r="G176" s="5"/>
+      <c r="A176" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="G176" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H176" s="5"/>
       <c r="I176" s="5"/>
       <c r="J176" s="5"/>
@@ -9318,13 +11851,27 @@
       <c r="Z176" s="5"/>
     </row>
     <row r="177">
-      <c r="A177" s="5"/>
-      <c r="B177" s="5"/>
-      <c r="C177" s="5"/>
-      <c r="D177" s="5"/>
-      <c r="E177" s="5"/>
-      <c r="F177" s="5"/>
-      <c r="G177" s="5"/>
+      <c r="A177" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="G177" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H177" s="5"/>
       <c r="I177" s="5"/>
       <c r="J177" s="5"/>
@@ -9346,13 +11893,27 @@
       <c r="Z177" s="5"/>
     </row>
     <row r="178">
-      <c r="A178" s="5"/>
-      <c r="B178" s="5"/>
-      <c r="C178" s="5"/>
-      <c r="D178" s="5"/>
-      <c r="E178" s="5"/>
-      <c r="F178" s="5"/>
-      <c r="G178" s="5"/>
+      <c r="A178" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="G178" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H178" s="5"/>
       <c r="I178" s="5"/>
       <c r="J178" s="5"/>
@@ -9374,13 +11935,27 @@
       <c r="Z178" s="5"/>
     </row>
     <row r="179">
-      <c r="A179" s="5"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="5"/>
-      <c r="D179" s="5"/>
-      <c r="E179" s="5"/>
-      <c r="F179" s="5"/>
-      <c r="G179" s="5"/>
+      <c r="A179" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="G179" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H179" s="5"/>
       <c r="I179" s="5"/>
       <c r="J179" s="5"/>
@@ -9402,13 +11977,27 @@
       <c r="Z179" s="5"/>
     </row>
     <row r="180">
-      <c r="A180" s="5"/>
-      <c r="B180" s="5"/>
-      <c r="C180" s="5"/>
-      <c r="D180" s="5"/>
-      <c r="E180" s="5"/>
-      <c r="F180" s="5"/>
-      <c r="G180" s="5"/>
+      <c r="A180" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="G180" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H180" s="5"/>
       <c r="I180" s="5"/>
       <c r="J180" s="5"/>
@@ -9430,13 +12019,27 @@
       <c r="Z180" s="5"/>
     </row>
     <row r="181">
-      <c r="A181" s="5"/>
-      <c r="B181" s="5"/>
-      <c r="C181" s="5"/>
-      <c r="D181" s="5"/>
-      <c r="E181" s="5"/>
-      <c r="F181" s="5"/>
-      <c r="G181" s="5"/>
+      <c r="A181" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="G181" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H181" s="5"/>
       <c r="I181" s="5"/>
       <c r="J181" s="5"/>
@@ -9458,13 +12061,27 @@
       <c r="Z181" s="5"/>
     </row>
     <row r="182">
-      <c r="A182" s="5"/>
-      <c r="B182" s="5"/>
-      <c r="C182" s="5"/>
-      <c r="D182" s="5"/>
-      <c r="E182" s="5"/>
-      <c r="F182" s="5"/>
-      <c r="G182" s="5"/>
+      <c r="A182" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="G182" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H182" s="5"/>
       <c r="I182" s="5"/>
       <c r="J182" s="5"/>
@@ -9486,13 +12103,27 @@
       <c r="Z182" s="5"/>
     </row>
     <row r="183">
-      <c r="A183" s="5"/>
-      <c r="B183" s="5"/>
-      <c r="C183" s="5"/>
-      <c r="D183" s="5"/>
-      <c r="E183" s="5"/>
-      <c r="F183" s="5"/>
-      <c r="G183" s="5"/>
+      <c r="A183" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="G183" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H183" s="5"/>
       <c r="I183" s="5"/>
       <c r="J183" s="5"/>
@@ -9514,13 +12145,27 @@
       <c r="Z183" s="5"/>
     </row>
     <row r="184">
-      <c r="A184" s="5"/>
-      <c r="B184" s="5"/>
-      <c r="C184" s="5"/>
-      <c r="D184" s="5"/>
-      <c r="E184" s="5"/>
-      <c r="F184" s="5"/>
-      <c r="G184" s="5"/>
+      <c r="A184" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="G184" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H184" s="5"/>
       <c r="I184" s="5"/>
       <c r="J184" s="5"/>
@@ -9542,13 +12187,27 @@
       <c r="Z184" s="5"/>
     </row>
     <row r="185">
-      <c r="A185" s="5"/>
-      <c r="B185" s="5"/>
-      <c r="C185" s="5"/>
-      <c r="D185" s="5"/>
-      <c r="E185" s="5"/>
-      <c r="F185" s="5"/>
-      <c r="G185" s="5"/>
+      <c r="A185" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>842</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="G185" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H185" s="5"/>
       <c r="I185" s="5"/>
       <c r="J185" s="5"/>
@@ -9570,13 +12229,27 @@
       <c r="Z185" s="5"/>
     </row>
     <row r="186">
-      <c r="A186" s="5"/>
-      <c r="B186" s="5"/>
-      <c r="C186" s="5"/>
-      <c r="D186" s="5"/>
-      <c r="E186" s="5"/>
-      <c r="F186" s="5"/>
-      <c r="G186" s="5"/>
+      <c r="A186" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="G186" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H186" s="5"/>
       <c r="I186" s="5"/>
       <c r="J186" s="5"/>
@@ -9598,14 +12271,28 @@
       <c r="Z186" s="5"/>
     </row>
     <row r="187">
-      <c r="A187" s="5"/>
-      <c r="B187" s="5"/>
-      <c r="C187" s="5"/>
-      <c r="D187" s="5"/>
-      <c r="E187" s="5"/>
-      <c r="F187" s="5"/>
-      <c r="G187" s="5"/>
-      <c r="H187" s="5"/>
+      <c r="A187" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="G187" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H187" s="6"/>
       <c r="I187" s="5"/>
       <c r="J187" s="5"/>
       <c r="K187" s="5"/>
@@ -9626,13 +12313,27 @@
       <c r="Z187" s="5"/>
     </row>
     <row r="188">
-      <c r="A188" s="5"/>
-      <c r="B188" s="5"/>
-      <c r="C188" s="5"/>
-      <c r="D188" s="5"/>
-      <c r="E188" s="5"/>
-      <c r="F188" s="5"/>
-      <c r="G188" s="5"/>
+      <c r="A188" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>856</v>
+      </c>
+      <c r="G188" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H188" s="5"/>
       <c r="I188" s="5"/>
       <c r="J188" s="5"/>
@@ -9654,13 +12355,27 @@
       <c r="Z188" s="5"/>
     </row>
     <row r="189">
-      <c r="A189" s="5"/>
-      <c r="B189" s="5"/>
-      <c r="C189" s="5"/>
-      <c r="D189" s="5"/>
-      <c r="E189" s="5"/>
-      <c r="F189" s="5"/>
-      <c r="G189" s="5"/>
+      <c r="A189" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="G189" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H189" s="5"/>
       <c r="I189" s="5"/>
       <c r="J189" s="5"/>
@@ -9682,13 +12397,27 @@
       <c r="Z189" s="5"/>
     </row>
     <row r="190">
-      <c r="A190" s="5"/>
-      <c r="B190" s="5"/>
-      <c r="C190" s="5"/>
-      <c r="D190" s="5"/>
-      <c r="E190" s="5"/>
-      <c r="F190" s="5"/>
-      <c r="G190" s="5"/>
+      <c r="A190" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>864</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>866</v>
+      </c>
+      <c r="G190" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H190" s="5"/>
       <c r="I190" s="5"/>
       <c r="J190" s="5"/>
@@ -9710,13 +12439,27 @@
       <c r="Z190" s="5"/>
     </row>
     <row r="191">
-      <c r="A191" s="5"/>
-      <c r="B191" s="5"/>
-      <c r="C191" s="5"/>
-      <c r="D191" s="5"/>
-      <c r="E191" s="5"/>
-      <c r="F191" s="5"/>
-      <c r="G191" s="5"/>
+      <c r="A191" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="G191" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H191" s="5"/>
       <c r="I191" s="5"/>
       <c r="J191" s="5"/>
@@ -9738,13 +12481,27 @@
       <c r="Z191" s="5"/>
     </row>
     <row r="192">
-      <c r="A192" s="5"/>
-      <c r="B192" s="5"/>
-      <c r="C192" s="5"/>
-      <c r="D192" s="5"/>
-      <c r="E192" s="5"/>
-      <c r="F192" s="5"/>
-      <c r="G192" s="5"/>
+      <c r="A192" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>876</v>
+      </c>
+      <c r="G192" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H192" s="5"/>
       <c r="I192" s="5"/>
       <c r="J192" s="5"/>
@@ -9766,13 +12523,27 @@
       <c r="Z192" s="5"/>
     </row>
     <row r="193">
-      <c r="A193" s="5"/>
-      <c r="B193" s="5"/>
-      <c r="C193" s="5"/>
-      <c r="D193" s="5"/>
-      <c r="E193" s="5"/>
-      <c r="F193" s="5"/>
-      <c r="G193" s="5"/>
+      <c r="A193" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>877</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>878</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>880</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>881</v>
+      </c>
+      <c r="G193" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H193" s="5"/>
       <c r="I193" s="5"/>
       <c r="J193" s="5"/>
@@ -9794,13 +12565,27 @@
       <c r="Z193" s="5"/>
     </row>
     <row r="194">
-      <c r="A194" s="5"/>
-      <c r="B194" s="5"/>
-      <c r="C194" s="5"/>
-      <c r="D194" s="5"/>
-      <c r="E194" s="5"/>
-      <c r="F194" s="5"/>
-      <c r="G194" s="5"/>
+      <c r="A194" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>882</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="G194" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H194" s="5"/>
       <c r="I194" s="5"/>
       <c r="J194" s="5"/>
@@ -9822,13 +12607,27 @@
       <c r="Z194" s="5"/>
     </row>
     <row r="195">
-      <c r="A195" s="5"/>
-      <c r="B195" s="5"/>
-      <c r="C195" s="5"/>
-      <c r="D195" s="5"/>
-      <c r="E195" s="5"/>
-      <c r="F195" s="5"/>
-      <c r="G195" s="5"/>
+      <c r="A195" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="F195" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="G195" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H195" s="5"/>
       <c r="I195" s="5"/>
       <c r="J195" s="5"/>
@@ -9850,13 +12649,27 @@
       <c r="Z195" s="5"/>
     </row>
     <row r="196">
-      <c r="A196" s="5"/>
-      <c r="B196" s="5"/>
-      <c r="C196" s="5"/>
-      <c r="D196" s="5"/>
-      <c r="E196" s="5"/>
-      <c r="F196" s="5"/>
-      <c r="G196" s="5"/>
+      <c r="A196" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="E196" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="G196" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H196" s="5"/>
       <c r="I196" s="5"/>
       <c r="J196" s="5"/>
@@ -9878,13 +12691,27 @@
       <c r="Z196" s="5"/>
     </row>
     <row r="197">
-      <c r="A197" s="5"/>
-      <c r="B197" s="5"/>
-      <c r="C197" s="5"/>
-      <c r="D197" s="5"/>
-      <c r="E197" s="5"/>
-      <c r="F197" s="5"/>
-      <c r="G197" s="5"/>
+      <c r="A197" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>896</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>898</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>899</v>
+      </c>
+      <c r="F197" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="G197" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H197" s="5"/>
       <c r="I197" s="5"/>
       <c r="J197" s="5"/>
@@ -9906,13 +12733,27 @@
       <c r="Z197" s="5"/>
     </row>
     <row r="198">
-      <c r="A198" s="5"/>
-      <c r="B198" s="5"/>
-      <c r="C198" s="5"/>
-      <c r="D198" s="5"/>
-      <c r="E198" s="5"/>
-      <c r="F198" s="5"/>
-      <c r="G198" s="5"/>
+      <c r="A198" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>902</v>
+      </c>
+      <c r="E198" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="F198" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="G198" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H198" s="5"/>
       <c r="I198" s="5"/>
       <c r="J198" s="5"/>
@@ -9934,13 +12775,27 @@
       <c r="Z198" s="5"/>
     </row>
     <row r="199">
-      <c r="A199" s="5"/>
-      <c r="B199" s="5"/>
-      <c r="C199" s="5"/>
-      <c r="D199" s="5"/>
-      <c r="E199" s="5"/>
-      <c r="F199" s="5"/>
-      <c r="G199" s="5"/>
+      <c r="A199" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="E199" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="F199" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="G199" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H199" s="5"/>
       <c r="I199" s="5"/>
       <c r="J199" s="5"/>
@@ -9962,13 +12817,27 @@
       <c r="Z199" s="5"/>
     </row>
     <row r="200">
-      <c r="A200" s="5"/>
-      <c r="B200" s="5"/>
-      <c r="C200" s="5"/>
-      <c r="D200" s="5"/>
-      <c r="E200" s="5"/>
-      <c r="F200" s="5"/>
-      <c r="G200" s="5"/>
+      <c r="A200" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="F200" s="6" t="s">
+        <v>914</v>
+      </c>
+      <c r="G200" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H200" s="5"/>
       <c r="I200" s="5"/>
       <c r="J200" s="5"/>
@@ -9990,13 +12859,27 @@
       <c r="Z200" s="5"/>
     </row>
     <row r="201">
-      <c r="A201" s="5"/>
-      <c r="B201" s="5"/>
-      <c r="C201" s="5"/>
-      <c r="D201" s="5"/>
-      <c r="E201" s="5"/>
-      <c r="F201" s="5"/>
-      <c r="G201" s="5"/>
+      <c r="A201" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="F201" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="G201" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H201" s="5"/>
       <c r="I201" s="5"/>
       <c r="J201" s="5"/>
@@ -10018,13 +12901,27 @@
       <c r="Z201" s="5"/>
     </row>
     <row r="202">
-      <c r="A202" s="5"/>
-      <c r="B202" s="5"/>
-      <c r="C202" s="5"/>
-      <c r="D202" s="5"/>
-      <c r="E202" s="5"/>
-      <c r="F202" s="5"/>
-      <c r="G202" s="5"/>
+      <c r="A202" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>920</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="F202" s="6" t="s">
+        <v>924</v>
+      </c>
+      <c r="G202" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H202" s="5"/>
       <c r="I202" s="5"/>
       <c r="J202" s="5"/>
@@ -10046,13 +12943,27 @@
       <c r="Z202" s="5"/>
     </row>
     <row r="203">
-      <c r="A203" s="5"/>
-      <c r="B203" s="5"/>
-      <c r="C203" s="5"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="5"/>
-      <c r="F203" s="5"/>
-      <c r="G203" s="5"/>
+      <c r="A203" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>926</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E203" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F203" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G203" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H203" s="5"/>
       <c r="I203" s="5"/>
       <c r="J203" s="5"/>
@@ -10074,13 +12985,27 @@
       <c r="Z203" s="5"/>
     </row>
     <row r="204">
-      <c r="A204" s="5"/>
-      <c r="B204" s="5"/>
-      <c r="C204" s="5"/>
-      <c r="D204" s="5"/>
-      <c r="E204" s="5"/>
-      <c r="F204" s="5"/>
-      <c r="G204" s="5"/>
+      <c r="A204" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E204" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F204" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G204" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H204" s="5"/>
       <c r="I204" s="5"/>
       <c r="J204" s="5"/>
@@ -10102,13 +13027,27 @@
       <c r="Z204" s="5"/>
     </row>
     <row r="205">
-      <c r="A205" s="5"/>
-      <c r="B205" s="5"/>
-      <c r="C205" s="5"/>
-      <c r="D205" s="5"/>
-      <c r="E205" s="5"/>
-      <c r="F205" s="5"/>
-      <c r="G205" s="5"/>
+      <c r="A205" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E205" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F205" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="G205" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H205" s="5"/>
       <c r="I205" s="5"/>
       <c r="J205" s="5"/>
@@ -10130,13 +13069,27 @@
       <c r="Z205" s="5"/>
     </row>
     <row r="206">
-      <c r="A206" s="5"/>
-      <c r="B206" s="5"/>
-      <c r="C206" s="5"/>
-      <c r="D206" s="5"/>
-      <c r="E206" s="5"/>
-      <c r="F206" s="5"/>
-      <c r="G206" s="5"/>
+      <c r="A206" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F206" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="G206" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H206" s="5"/>
       <c r="I206" s="5"/>
       <c r="J206" s="5"/>
@@ -10158,13 +13111,27 @@
       <c r="Z206" s="5"/>
     </row>
     <row r="207">
-      <c r="A207" s="5"/>
-      <c r="B207" s="5"/>
-      <c r="C207" s="5"/>
-      <c r="D207" s="5"/>
-      <c r="E207" s="5"/>
-      <c r="F207" s="5"/>
-      <c r="G207" s="5"/>
+      <c r="A207" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E207" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F207" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G207" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H207" s="5"/>
       <c r="I207" s="5"/>
       <c r="J207" s="5"/>
@@ -10186,13 +13153,27 @@
       <c r="Z207" s="5"/>
     </row>
     <row r="208">
-      <c r="A208" s="5"/>
-      <c r="B208" s="5"/>
-      <c r="C208" s="5"/>
-      <c r="D208" s="5"/>
-      <c r="E208" s="5"/>
-      <c r="F208" s="5"/>
-      <c r="G208" s="5"/>
+      <c r="A208" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="E208" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G208" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H208" s="5"/>
       <c r="I208" s="5"/>
       <c r="J208" s="5"/>
@@ -10214,13 +13195,27 @@
       <c r="Z208" s="5"/>
     </row>
     <row r="209">
-      <c r="A209" s="5"/>
-      <c r="B209" s="5"/>
-      <c r="C209" s="5"/>
-      <c r="D209" s="5"/>
-      <c r="E209" s="5"/>
-      <c r="F209" s="5"/>
-      <c r="G209" s="5"/>
+      <c r="A209" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E209" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F209" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G209" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H209" s="5"/>
       <c r="I209" s="5"/>
       <c r="J209" s="5"/>
@@ -10242,13 +13237,27 @@
       <c r="Z209" s="5"/>
     </row>
     <row r="210">
-      <c r="A210" s="5"/>
-      <c r="B210" s="5"/>
-      <c r="C210" s="5"/>
-      <c r="D210" s="5"/>
-      <c r="E210" s="5"/>
-      <c r="F210" s="5"/>
-      <c r="G210" s="5"/>
+      <c r="A210" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E210" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G210" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H210" s="5"/>
       <c r="I210" s="5"/>
       <c r="J210" s="5"/>
@@ -10270,13 +13279,27 @@
       <c r="Z210" s="5"/>
     </row>
     <row r="211">
-      <c r="A211" s="5"/>
-      <c r="B211" s="5"/>
-      <c r="C211" s="5"/>
-      <c r="D211" s="5"/>
-      <c r="E211" s="5"/>
-      <c r="F211" s="5"/>
-      <c r="G211" s="5"/>
+      <c r="A211" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>938</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="E211" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="F211" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G211" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H211" s="5"/>
       <c r="I211" s="5"/>
       <c r="J211" s="5"/>
@@ -10298,13 +13321,27 @@
       <c r="Z211" s="5"/>
     </row>
     <row r="212">
-      <c r="A212" s="5"/>
-      <c r="B212" s="5"/>
-      <c r="C212" s="5"/>
-      <c r="D212" s="5"/>
-      <c r="E212" s="5"/>
-      <c r="F212" s="5"/>
-      <c r="G212" s="5"/>
+      <c r="A212" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G212" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H212" s="5"/>
       <c r="I212" s="5"/>
       <c r="J212" s="5"/>
@@ -10326,13 +13363,27 @@
       <c r="Z212" s="5"/>
     </row>
     <row r="213">
-      <c r="A213" s="5"/>
-      <c r="B213" s="5"/>
-      <c r="C213" s="5"/>
-      <c r="D213" s="5"/>
-      <c r="E213" s="5"/>
-      <c r="F213" s="5"/>
-      <c r="G213" s="5"/>
+      <c r="A213" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E213" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F213" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G213" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H213" s="5"/>
       <c r="I213" s="5"/>
       <c r="J213" s="5"/>
@@ -10354,13 +13405,27 @@
       <c r="Z213" s="5"/>
     </row>
     <row r="214">
-      <c r="A214" s="5"/>
-      <c r="B214" s="5"/>
-      <c r="C214" s="5"/>
-      <c r="D214" s="5"/>
-      <c r="E214" s="5"/>
-      <c r="F214" s="5"/>
-      <c r="G214" s="5"/>
+      <c r="A214" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F214" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G214" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H214" s="5"/>
       <c r="I214" s="5"/>
       <c r="J214" s="5"/>
@@ -10382,13 +13447,27 @@
       <c r="Z214" s="5"/>
     </row>
     <row r="215">
-      <c r="A215" s="5"/>
-      <c r="B215" s="5"/>
-      <c r="C215" s="5"/>
-      <c r="D215" s="5"/>
-      <c r="E215" s="5"/>
-      <c r="F215" s="5"/>
-      <c r="G215" s="5"/>
+      <c r="A215" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F215" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G215" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H215" s="5"/>
       <c r="I215" s="5"/>
       <c r="J215" s="5"/>
@@ -10410,13 +13489,27 @@
       <c r="Z215" s="5"/>
     </row>
     <row r="216">
-      <c r="A216" s="5"/>
-      <c r="B216" s="5"/>
-      <c r="C216" s="5"/>
-      <c r="D216" s="5"/>
-      <c r="E216" s="5"/>
-      <c r="F216" s="5"/>
-      <c r="G216" s="5"/>
+      <c r="A216" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F216" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G216" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H216" s="5"/>
       <c r="I216" s="5"/>
       <c r="J216" s="5"/>
@@ -10438,13 +13531,27 @@
       <c r="Z216" s="5"/>
     </row>
     <row r="217">
-      <c r="A217" s="5"/>
-      <c r="B217" s="5"/>
-      <c r="C217" s="5"/>
-      <c r="D217" s="5"/>
-      <c r="E217" s="5"/>
-      <c r="F217" s="5"/>
-      <c r="G217" s="5"/>
+      <c r="A217" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F217" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G217" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H217" s="5"/>
       <c r="I217" s="5"/>
       <c r="J217" s="5"/>
@@ -10466,13 +13573,27 @@
       <c r="Z217" s="5"/>
     </row>
     <row r="218">
-      <c r="A218" s="5"/>
-      <c r="B218" s="5"/>
-      <c r="C218" s="5"/>
-      <c r="D218" s="5"/>
-      <c r="E218" s="5"/>
-      <c r="F218" s="5"/>
-      <c r="G218" s="5"/>
+      <c r="A218" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F218" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G218" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H218" s="5"/>
       <c r="I218" s="5"/>
       <c r="J218" s="5"/>
@@ -10494,13 +13615,27 @@
       <c r="Z218" s="5"/>
     </row>
     <row r="219">
-      <c r="A219" s="5"/>
-      <c r="B219" s="5"/>
-      <c r="C219" s="5"/>
-      <c r="D219" s="5"/>
-      <c r="E219" s="5"/>
-      <c r="F219" s="5"/>
-      <c r="G219" s="5"/>
+      <c r="A219" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E219" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F219" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G219" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H219" s="5"/>
       <c r="I219" s="5"/>
       <c r="J219" s="5"/>
@@ -10522,13 +13657,27 @@
       <c r="Z219" s="5"/>
     </row>
     <row r="220">
-      <c r="A220" s="5"/>
-      <c r="B220" s="5"/>
-      <c r="C220" s="5"/>
-      <c r="D220" s="5"/>
-      <c r="E220" s="5"/>
-      <c r="F220" s="5"/>
-      <c r="G220" s="5"/>
+      <c r="A220" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="F220" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G220" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H220" s="5"/>
       <c r="I220" s="5"/>
       <c r="J220" s="5"/>
@@ -10550,13 +13699,27 @@
       <c r="Z220" s="5"/>
     </row>
     <row r="221">
-      <c r="A221" s="5"/>
-      <c r="B221" s="5"/>
-      <c r="C221" s="5"/>
-      <c r="D221" s="5"/>
-      <c r="E221" s="5"/>
-      <c r="F221" s="5"/>
-      <c r="G221" s="5"/>
+      <c r="A221" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G221" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H221" s="5"/>
       <c r="I221" s="5"/>
       <c r="J221" s="5"/>
@@ -10578,13 +13741,27 @@
       <c r="Z221" s="5"/>
     </row>
     <row r="222">
-      <c r="A222" s="5"/>
-      <c r="B222" s="5"/>
-      <c r="C222" s="5"/>
-      <c r="D222" s="5"/>
-      <c r="E222" s="5"/>
-      <c r="F222" s="5"/>
-      <c r="G222" s="5"/>
+      <c r="A222" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F222" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="G222" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H222" s="5"/>
       <c r="I222" s="5"/>
       <c r="J222" s="5"/>
@@ -10606,13 +13783,27 @@
       <c r="Z222" s="5"/>
     </row>
     <row r="223">
-      <c r="A223" s="5"/>
-      <c r="B223" s="5"/>
-      <c r="C223" s="5"/>
-      <c r="D223" s="5"/>
-      <c r="E223" s="5"/>
-      <c r="F223" s="5"/>
-      <c r="G223" s="5"/>
+      <c r="A223" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E223" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G223" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H223" s="5"/>
       <c r="I223" s="5"/>
       <c r="J223" s="5"/>
@@ -10634,13 +13825,27 @@
       <c r="Z223" s="5"/>
     </row>
     <row r="224">
-      <c r="A224" s="5"/>
-      <c r="B224" s="5"/>
-      <c r="C224" s="5"/>
-      <c r="D224" s="5"/>
-      <c r="E224" s="5"/>
-      <c r="F224" s="5"/>
-      <c r="G224" s="5"/>
+      <c r="A224" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E224" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F224" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G224" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H224" s="5"/>
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
@@ -10662,13 +13867,27 @@
       <c r="Z224" s="5"/>
     </row>
     <row r="225">
-      <c r="A225" s="5"/>
-      <c r="B225" s="5"/>
-      <c r="C225" s="5"/>
-      <c r="D225" s="5"/>
-      <c r="E225" s="5"/>
-      <c r="F225" s="5"/>
-      <c r="G225" s="5"/>
+      <c r="A225" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E225" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F225" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="G225" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H225" s="5"/>
       <c r="I225" s="5"/>
       <c r="J225" s="5"/>
@@ -10690,13 +13909,27 @@
       <c r="Z225" s="5"/>
     </row>
     <row r="226">
-      <c r="A226" s="5"/>
-      <c r="B226" s="5"/>
-      <c r="C226" s="5"/>
-      <c r="D226" s="5"/>
-      <c r="E226" s="5"/>
-      <c r="F226" s="5"/>
-      <c r="G226" s="5"/>
+      <c r="A226" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>954</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F226" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G226" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H226" s="5"/>
       <c r="I226" s="5"/>
       <c r="J226" s="5"/>
@@ -10718,13 +13951,27 @@
       <c r="Z226" s="5"/>
     </row>
     <row r="227">
-      <c r="A227" s="5"/>
-      <c r="B227" s="5"/>
-      <c r="C227" s="5"/>
-      <c r="D227" s="5"/>
-      <c r="E227" s="5"/>
-      <c r="F227" s="5"/>
-      <c r="G227" s="5"/>
+      <c r="A227" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E227" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="F227" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G227" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H227" s="5"/>
       <c r="I227" s="5"/>
       <c r="J227" s="5"/>
@@ -10746,13 +13993,27 @@
       <c r="Z227" s="5"/>
     </row>
     <row r="228">
-      <c r="A228" s="5"/>
-      <c r="B228" s="5"/>
-      <c r="C228" s="5"/>
-      <c r="D228" s="5"/>
-      <c r="E228" s="5"/>
-      <c r="F228" s="5"/>
-      <c r="G228" s="5"/>
+      <c r="A228" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F228" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="G228" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H228" s="5"/>
       <c r="I228" s="5"/>
       <c r="J228" s="5"/>
@@ -10774,13 +14035,27 @@
       <c r="Z228" s="5"/>
     </row>
     <row r="229">
-      <c r="A229" s="5"/>
-      <c r="B229" s="5"/>
-      <c r="C229" s="5"/>
-      <c r="D229" s="5"/>
-      <c r="E229" s="5"/>
-      <c r="F229" s="5"/>
-      <c r="G229" s="5"/>
+      <c r="A229" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>957</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E229" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="F229" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="G229" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5"/>
       <c r="J229" s="5"/>
@@ -10802,13 +14077,27 @@
       <c r="Z229" s="5"/>
     </row>
     <row r="230">
-      <c r="A230" s="5"/>
-      <c r="B230" s="5"/>
-      <c r="C230" s="5"/>
-      <c r="D230" s="5"/>
-      <c r="E230" s="5"/>
-      <c r="F230" s="5"/>
-      <c r="G230" s="5"/>
+      <c r="A230" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>958</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D230" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E230" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F230" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="G230" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H230" s="5"/>
       <c r="I230" s="5"/>
       <c r="J230" s="5"/>
@@ -10830,13 +14119,27 @@
       <c r="Z230" s="5"/>
     </row>
     <row r="231">
-      <c r="A231" s="5"/>
-      <c r="B231" s="5"/>
-      <c r="C231" s="5"/>
-      <c r="D231" s="5"/>
-      <c r="E231" s="5"/>
-      <c r="F231" s="5"/>
-      <c r="G231" s="5"/>
+      <c r="A231" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D231" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E231" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F231" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G231" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H231" s="5"/>
       <c r="I231" s="5"/>
       <c r="J231" s="5"/>
@@ -10858,13 +14161,27 @@
       <c r="Z231" s="5"/>
     </row>
     <row r="232">
-      <c r="A232" s="5"/>
-      <c r="B232" s="5"/>
-      <c r="C232" s="5"/>
-      <c r="D232" s="5"/>
-      <c r="E232" s="5"/>
-      <c r="F232" s="5"/>
-      <c r="G232" s="5"/>
+      <c r="A232" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E232" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G232" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H232" s="5"/>
       <c r="I232" s="5"/>
       <c r="J232" s="5"/>
@@ -10886,13 +14203,27 @@
       <c r="Z232" s="5"/>
     </row>
     <row r="233">
-      <c r="A233" s="5"/>
-      <c r="B233" s="5"/>
-      <c r="C233" s="5"/>
-      <c r="D233" s="5"/>
-      <c r="E233" s="5"/>
-      <c r="F233" s="5"/>
-      <c r="G233" s="5"/>
+      <c r="A233" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>962</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>964</v>
+      </c>
+      <c r="E233" s="6" t="s">
+        <v>965</v>
+      </c>
+      <c r="F233" s="6" t="s">
+        <v>966</v>
+      </c>
+      <c r="G233" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H233" s="5"/>
       <c r="I233" s="5"/>
       <c r="J233" s="5"/>
@@ -10914,13 +14245,27 @@
       <c r="Z233" s="5"/>
     </row>
     <row r="234">
-      <c r="A234" s="5"/>
-      <c r="B234" s="5"/>
-      <c r="C234" s="5"/>
-      <c r="D234" s="5"/>
-      <c r="E234" s="5"/>
-      <c r="F234" s="5"/>
-      <c r="G234" s="5"/>
+      <c r="A234" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>968</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="E234" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="F234" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G234" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H234" s="5"/>
       <c r="I234" s="5"/>
       <c r="J234" s="5"/>
@@ -10942,13 +14287,27 @@
       <c r="Z234" s="5"/>
     </row>
     <row r="235">
-      <c r="A235" s="5"/>
-      <c r="B235" s="5"/>
-      <c r="C235" s="5"/>
-      <c r="D235" s="5"/>
-      <c r="E235" s="5"/>
-      <c r="F235" s="5"/>
-      <c r="G235" s="5"/>
+      <c r="A235" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>971</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="E235" s="6" t="s">
+        <v>974</v>
+      </c>
+      <c r="F235" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="G235" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H235" s="5"/>
       <c r="I235" s="5"/>
       <c r="J235" s="5"/>
@@ -10970,13 +14329,27 @@
       <c r="Z235" s="5"/>
     </row>
     <row r="236">
-      <c r="A236" s="5"/>
-      <c r="B236" s="5"/>
-      <c r="C236" s="5"/>
-      <c r="D236" s="5"/>
-      <c r="E236" s="5"/>
-      <c r="F236" s="5"/>
-      <c r="G236" s="5"/>
+      <c r="A236" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>975</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>976</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="E236" s="6" t="s">
+        <v>978</v>
+      </c>
+      <c r="F236" s="6" t="s">
+        <v>979</v>
+      </c>
+      <c r="G236" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H236" s="5"/>
       <c r="I236" s="5"/>
       <c r="J236" s="5"/>
@@ -10998,13 +14371,27 @@
       <c r="Z236" s="5"/>
     </row>
     <row r="237">
-      <c r="A237" s="5"/>
-      <c r="B237" s="5"/>
-      <c r="C237" s="5"/>
-      <c r="D237" s="5"/>
-      <c r="E237" s="5"/>
-      <c r="F237" s="5"/>
-      <c r="G237" s="5"/>
+      <c r="A237" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>980</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>981</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="E237" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="F237" s="6" t="s">
+        <v>984</v>
+      </c>
+      <c r="G237" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H237" s="5"/>
       <c r="I237" s="5"/>
       <c r="J237" s="5"/>
@@ -11026,13 +14413,27 @@
       <c r="Z237" s="5"/>
     </row>
     <row r="238">
-      <c r="A238" s="5"/>
-      <c r="B238" s="5"/>
-      <c r="C238" s="5"/>
-      <c r="D238" s="5"/>
-      <c r="E238" s="5"/>
-      <c r="F238" s="5"/>
-      <c r="G238" s="5"/>
+      <c r="A238" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>985</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="E238" s="6" t="s">
+        <v>988</v>
+      </c>
+      <c r="F238" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="G238" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H238" s="5"/>
       <c r="I238" s="5"/>
       <c r="J238" s="5"/>
@@ -11054,13 +14455,27 @@
       <c r="Z238" s="5"/>
     </row>
     <row r="239">
-      <c r="A239" s="5"/>
-      <c r="B239" s="5"/>
-      <c r="C239" s="5"/>
-      <c r="D239" s="5"/>
-      <c r="E239" s="5"/>
-      <c r="F239" s="5"/>
-      <c r="G239" s="5"/>
+      <c r="A239" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>989</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>990</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>991</v>
+      </c>
+      <c r="E239" s="6" t="s">
+        <v>992</v>
+      </c>
+      <c r="F239" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="G239" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H239" s="5"/>
       <c r="I239" s="5"/>
       <c r="J239" s="5"/>
@@ -11082,13 +14497,27 @@
       <c r="Z239" s="5"/>
     </row>
     <row r="240">
-      <c r="A240" s="5"/>
-      <c r="B240" s="5"/>
-      <c r="C240" s="5"/>
-      <c r="D240" s="5"/>
-      <c r="E240" s="5"/>
-      <c r="F240" s="5"/>
-      <c r="G240" s="5"/>
+      <c r="A240" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>994</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>995</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="E240" s="6" t="s">
+        <v>997</v>
+      </c>
+      <c r="F240" s="6" t="s">
+        <v>998</v>
+      </c>
+      <c r="G240" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H240" s="5"/>
       <c r="I240" s="5"/>
       <c r="J240" s="5"/>
@@ -11110,13 +14539,27 @@
       <c r="Z240" s="5"/>
     </row>
     <row r="241">
-      <c r="A241" s="5"/>
-      <c r="B241" s="5"/>
-      <c r="C241" s="5"/>
-      <c r="D241" s="5"/>
-      <c r="E241" s="5"/>
-      <c r="F241" s="5"/>
-      <c r="G241" s="5"/>
+      <c r="A241" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D241" s="6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E241" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F241" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G241" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H241" s="5"/>
       <c r="I241" s="5"/>
       <c r="J241" s="5"/>
@@ -11138,13 +14581,27 @@
       <c r="Z241" s="5"/>
     </row>
     <row r="242">
-      <c r="A242" s="5"/>
-      <c r="B242" s="5"/>
-      <c r="C242" s="5"/>
-      <c r="D242" s="5"/>
-      <c r="E242" s="5"/>
-      <c r="F242" s="5"/>
-      <c r="G242" s="5"/>
+      <c r="A242" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D242" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E242" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F242" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="G242" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H242" s="5"/>
       <c r="I242" s="5"/>
       <c r="J242" s="5"/>
@@ -11166,13 +14623,27 @@
       <c r="Z242" s="5"/>
     </row>
     <row r="243">
-      <c r="A243" s="5"/>
-      <c r="B243" s="5"/>
-      <c r="C243" s="5"/>
-      <c r="D243" s="5"/>
-      <c r="E243" s="5"/>
-      <c r="F243" s="5"/>
-      <c r="G243" s="5"/>
+      <c r="A243" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D243" s="6" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E243" s="6" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F243" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="G243" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H243" s="5"/>
       <c r="I243" s="5"/>
       <c r="J243" s="5"/>
@@ -11194,13 +14665,27 @@
       <c r="Z243" s="5"/>
     </row>
     <row r="244">
-      <c r="A244" s="5"/>
-      <c r="B244" s="5"/>
-      <c r="C244" s="5"/>
-      <c r="D244" s="5"/>
-      <c r="E244" s="5"/>
-      <c r="F244" s="5"/>
-      <c r="G244" s="5"/>
+      <c r="A244" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D244" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E244" s="6" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F244" s="6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G244" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H244" s="5"/>
       <c r="I244" s="5"/>
       <c r="J244" s="5"/>
@@ -11222,13 +14707,27 @@
       <c r="Z244" s="5"/>
     </row>
     <row r="245">
-      <c r="A245" s="5"/>
-      <c r="B245" s="5"/>
-      <c r="C245" s="5"/>
-      <c r="D245" s="5"/>
-      <c r="E245" s="5"/>
-      <c r="F245" s="5"/>
-      <c r="G245" s="5"/>
+      <c r="A245" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D245" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E245" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F245" s="6" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G245" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H245" s="5"/>
       <c r="I245" s="5"/>
       <c r="J245" s="5"/>
@@ -11250,13 +14749,27 @@
       <c r="Z245" s="5"/>
     </row>
     <row r="246">
-      <c r="A246" s="5"/>
-      <c r="B246" s="5"/>
-      <c r="C246" s="5"/>
-      <c r="D246" s="5"/>
-      <c r="E246" s="5"/>
-      <c r="F246" s="5"/>
-      <c r="G246" s="5"/>
+      <c r="A246" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D246" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E246" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F246" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="G246" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H246" s="5"/>
       <c r="I246" s="5"/>
       <c r="J246" s="5"/>
@@ -11278,13 +14791,27 @@
       <c r="Z246" s="5"/>
     </row>
     <row r="247">
-      <c r="A247" s="5"/>
-      <c r="B247" s="5"/>
-      <c r="C247" s="5"/>
-      <c r="D247" s="5"/>
-      <c r="E247" s="5"/>
-      <c r="F247" s="5"/>
-      <c r="G247" s="5"/>
+      <c r="A247" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D247" s="6" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E247" s="6" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F247" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G247" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H247" s="5"/>
       <c r="I247" s="5"/>
       <c r="J247" s="5"/>
@@ -11306,13 +14833,27 @@
       <c r="Z247" s="5"/>
     </row>
     <row r="248">
-      <c r="A248" s="5"/>
-      <c r="B248" s="5"/>
-      <c r="C248" s="5"/>
-      <c r="D248" s="5"/>
-      <c r="E248" s="5"/>
-      <c r="F248" s="5"/>
-      <c r="G248" s="5"/>
+      <c r="A248" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D248" s="6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E248" s="6" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F248" s="6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G248" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H248" s="5"/>
       <c r="I248" s="5"/>
       <c r="J248" s="5"/>
@@ -11334,13 +14875,27 @@
       <c r="Z248" s="5"/>
     </row>
     <row r="249">
-      <c r="A249" s="5"/>
-      <c r="B249" s="5"/>
-      <c r="C249" s="5"/>
-      <c r="D249" s="5"/>
-      <c r="E249" s="5"/>
-      <c r="F249" s="5"/>
-      <c r="G249" s="5"/>
+      <c r="A249" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D249" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E249" s="6" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F249" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G249" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H249" s="5"/>
       <c r="I249" s="5"/>
       <c r="J249" s="5"/>
@@ -11362,13 +14917,27 @@
       <c r="Z249" s="5"/>
     </row>
     <row r="250">
-      <c r="A250" s="5"/>
-      <c r="B250" s="5"/>
-      <c r="C250" s="5"/>
-      <c r="D250" s="5"/>
-      <c r="E250" s="5"/>
-      <c r="F250" s="5"/>
-      <c r="G250" s="5"/>
+      <c r="A250" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D250" s="6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E250" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F250" s="6" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G250" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H250" s="5"/>
       <c r="I250" s="5"/>
       <c r="J250" s="5"/>
@@ -11390,13 +14959,27 @@
       <c r="Z250" s="5"/>
     </row>
     <row r="251">
-      <c r="A251" s="5"/>
-      <c r="B251" s="5"/>
-      <c r="C251" s="5"/>
-      <c r="D251" s="5"/>
-      <c r="E251" s="5"/>
-      <c r="F251" s="5"/>
-      <c r="G251" s="5"/>
+      <c r="A251" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D251" s="6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E251" s="6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F251" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G251" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H251" s="5"/>
       <c r="I251" s="5"/>
       <c r="J251" s="5"/>
@@ -11418,13 +15001,27 @@
       <c r="Z251" s="5"/>
     </row>
     <row r="252">
-      <c r="A252" s="5"/>
-      <c r="B252" s="5"/>
-      <c r="C252" s="5"/>
-      <c r="D252" s="5"/>
-      <c r="E252" s="5"/>
-      <c r="F252" s="5"/>
-      <c r="G252" s="5"/>
+      <c r="A252" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D252" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E252" s="6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F252" s="6" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G252" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H252" s="5"/>
       <c r="I252" s="5"/>
       <c r="J252" s="5"/>
@@ -11446,13 +15043,27 @@
       <c r="Z252" s="5"/>
     </row>
     <row r="253">
-      <c r="A253" s="5"/>
-      <c r="B253" s="5"/>
-      <c r="C253" s="5"/>
-      <c r="D253" s="5"/>
-      <c r="E253" s="5"/>
-      <c r="F253" s="5"/>
-      <c r="G253" s="5"/>
+      <c r="A253" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D253" s="6" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E253" s="6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F253" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G253" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H253" s="5"/>
       <c r="I253" s="5"/>
       <c r="J253" s="5"/>
@@ -11474,13 +15085,27 @@
       <c r="Z253" s="5"/>
     </row>
     <row r="254">
-      <c r="A254" s="5"/>
-      <c r="B254" s="5"/>
-      <c r="C254" s="5"/>
-      <c r="D254" s="5"/>
-      <c r="E254" s="5"/>
-      <c r="F254" s="5"/>
-      <c r="G254" s="5"/>
+      <c r="A254" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D254" s="6" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E254" s="6" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F254" s="6" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G254" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H254" s="5"/>
       <c r="I254" s="5"/>
       <c r="J254" s="5"/>
@@ -11502,13 +15127,27 @@
       <c r="Z254" s="5"/>
     </row>
     <row r="255">
-      <c r="A255" s="5"/>
-      <c r="B255" s="5"/>
-      <c r="C255" s="5"/>
-      <c r="D255" s="5"/>
-      <c r="E255" s="5"/>
-      <c r="F255" s="5"/>
-      <c r="G255" s="5"/>
+      <c r="A255" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D255" s="6" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E255" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F255" s="6" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G255" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H255" s="5"/>
       <c r="I255" s="5"/>
       <c r="J255" s="5"/>
@@ -11530,13 +15169,27 @@
       <c r="Z255" s="5"/>
     </row>
     <row r="256">
-      <c r="A256" s="5"/>
-      <c r="B256" s="5"/>
-      <c r="C256" s="5"/>
-      <c r="D256" s="5"/>
-      <c r="E256" s="5"/>
-      <c r="F256" s="5"/>
-      <c r="G256" s="5"/>
+      <c r="A256" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D256" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E256" s="6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F256" s="6" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G256" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H256" s="5"/>
       <c r="I256" s="5"/>
       <c r="J256" s="5"/>
@@ -11558,13 +15211,27 @@
       <c r="Z256" s="5"/>
     </row>
     <row r="257">
-      <c r="A257" s="5"/>
-      <c r="B257" s="5"/>
-      <c r="C257" s="5"/>
-      <c r="D257" s="5"/>
-      <c r="E257" s="5"/>
-      <c r="F257" s="5"/>
-      <c r="G257" s="5"/>
+      <c r="A257" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D257" s="6" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E257" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F257" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="G257" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H257" s="5"/>
       <c r="I257" s="5"/>
       <c r="J257" s="5"/>
@@ -11586,13 +15253,27 @@
       <c r="Z257" s="5"/>
     </row>
     <row r="258">
-      <c r="A258" s="5"/>
-      <c r="B258" s="5"/>
-      <c r="C258" s="5"/>
-      <c r="D258" s="5"/>
-      <c r="E258" s="5"/>
-      <c r="F258" s="5"/>
-      <c r="G258" s="5"/>
+      <c r="A258" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D258" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E258" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F258" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="G258" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H258" s="5"/>
       <c r="I258" s="5"/>
       <c r="J258" s="5"/>
@@ -11614,13 +15295,27 @@
       <c r="Z258" s="5"/>
     </row>
     <row r="259">
-      <c r="A259" s="5"/>
-      <c r="B259" s="5"/>
-      <c r="C259" s="5"/>
-      <c r="D259" s="5"/>
-      <c r="E259" s="5"/>
-      <c r="F259" s="5"/>
-      <c r="G259" s="5"/>
+      <c r="A259" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D259" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E259" s="6" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F259" s="6" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G259" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="H259" s="5"/>
       <c r="I259" s="5"/>
       <c r="J259" s="5"/>
@@ -11642,13 +15337,27 @@
       <c r="Z259" s="5"/>
     </row>
     <row r="260">
-      <c r="A260" s="5"/>
-      <c r="B260" s="5"/>
-      <c r="C260" s="5"/>
-      <c r="D260" s="5"/>
-      <c r="E260" s="5"/>
-      <c r="F260" s="5"/>
-      <c r="G260" s="5"/>
+      <c r="A260" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D260" s="6" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E260" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F260" s="6" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G260" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="H260" s="5"/>
       <c r="I260" s="5"/>
       <c r="J260" s="5"/>
@@ -11670,13 +15379,27 @@
       <c r="Z260" s="5"/>
     </row>
     <row r="261">
-      <c r="A261" s="5"/>
-      <c r="B261" s="5"/>
-      <c r="C261" s="5"/>
-      <c r="D261" s="5"/>
-      <c r="E261" s="5"/>
-      <c r="F261" s="5"/>
-      <c r="G261" s="5"/>
+      <c r="A261" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D261" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F261" s="6" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G261" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="H261" s="5"/>
       <c r="I261" s="5"/>
       <c r="J261" s="5"/>
@@ -11698,13 +15421,27 @@
       <c r="Z261" s="5"/>
     </row>
     <row r="262">
-      <c r="A262" s="5"/>
-      <c r="B262" s="5"/>
-      <c r="C262" s="5"/>
-      <c r="D262" s="5"/>
-      <c r="E262" s="5"/>
-      <c r="F262" s="5"/>
-      <c r="G262" s="5"/>
+      <c r="A262" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D262" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F262" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="G262" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="H262" s="5"/>
       <c r="I262" s="5"/>
       <c r="J262" s="5"/>
